--- a/Finsighters_Investor_Dashboard_R5.xlsx
+++ b/Finsighters_Investor_Dashboard_R5.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DC0D1C-527E-43FC-8984-50AB1FA55BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0. Investment Committee" sheetId="1" r:id="rId1"/>
@@ -10551,89 +10551,17 @@
     <xf numFmtId="49" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10647,15 +10575,87 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21790,45 +21790,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
     </row>
     <row r="3" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
     </row>
     <row r="4" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
     </row>
     <row r="5" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="149" t="s">
+      <c r="B6" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
+      <c r="C6" s="152"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="152"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="152"/>
     </row>
     <row r="7" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
@@ -21915,25 +21915,25 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="148" t="s">
+      <c r="B12" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="148"/>
-      <c r="D12" s="148"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="148"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
     </row>
     <row r="13" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="149" t="s">
+      <c r="B14" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
     </row>
     <row r="15" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
@@ -22142,14 +22142,14 @@
     <row r="24" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152"/>
     </row>
     <row r="27" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
@@ -22324,25 +22324,25 @@
       </c>
     </row>
     <row r="35" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="148" t="s">
+      <c r="B35" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="148"/>
-      <c r="D35" s="148"/>
-      <c r="E35" s="148"/>
-      <c r="F35" s="148"/>
-      <c r="G35" s="148"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="153"/>
     </row>
     <row r="36" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="37" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="149" t="s">
+      <c r="B37" s="152" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="149"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
+      <c r="C37" s="152"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
     </row>
     <row r="38" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
@@ -22464,14 +22464,14 @@
     </row>
     <row r="45" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="46" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="149" t="s">
+      <c r="B46" s="152" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="149"/>
-      <c r="D46" s="149"/>
-      <c r="E46" s="149"/>
-      <c r="F46" s="149"/>
-      <c r="G46" s="149"/>
+      <c r="C46" s="152"/>
+      <c r="D46" s="152"/>
+      <c r="E46" s="152"/>
+      <c r="F46" s="152"/>
+      <c r="G46" s="152"/>
     </row>
     <row r="47" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
@@ -22652,28 +22652,28 @@
     </row>
     <row r="59" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="148" t="s">
+      <c r="B60" s="153" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="148"/>
-      <c r="D60" s="148"/>
-      <c r="E60" s="148"/>
-      <c r="F60" s="148"/>
-      <c r="G60" s="148"/>
+      <c r="C60" s="153"/>
+      <c r="D60" s="153"/>
+      <c r="E60" s="153"/>
+      <c r="F60" s="153"/>
+      <c r="G60" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B12:G12"/>
     <mergeCell ref="B60:G60"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22703,14 +22703,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>1705</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
     </row>
     <row r="3" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -22729,14 +22729,14 @@
     </row>
     <row r="6" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="186" t="s">
+      <c r="B7" s="148" t="s">
         <v>1709</v>
       </c>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
     </row>
     <row r="8" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="60" t="s">
@@ -23312,14 +23312,14 @@
       </c>
     </row>
     <row r="31" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="186" t="s">
+      <c r="B31" s="148" t="s">
         <v>1831</v>
       </c>
-      <c r="C31" s="186"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="186"/>
-      <c r="G31" s="186"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="148"/>
     </row>
     <row r="32" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="58" t="s">
@@ -24288,14 +24288,14 @@
     </row>
     <row r="63" spans="2:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="2:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="186" t="s">
+      <c r="B64" s="148" t="s">
         <v>1922</v>
       </c>
-      <c r="C64" s="186"/>
-      <c r="D64" s="186"/>
-      <c r="E64" s="186"/>
-      <c r="F64" s="186"/>
-      <c r="G64" s="186"/>
+      <c r="C64" s="148"/>
+      <c r="D64" s="148"/>
+      <c r="E64" s="148"/>
+      <c r="F64" s="148"/>
+      <c r="G64" s="148"/>
     </row>
     <row r="65" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="60" t="s">
@@ -24398,14 +24398,14 @@
     </row>
     <row r="74" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="186" t="s">
+      <c r="B75" s="148" t="s">
         <v>1949</v>
       </c>
-      <c r="C75" s="186"/>
-      <c r="D75" s="186"/>
-      <c r="E75" s="186"/>
-      <c r="F75" s="186"/>
-      <c r="G75" s="186"/>
+      <c r="C75" s="148"/>
+      <c r="D75" s="148"/>
+      <c r="E75" s="148"/>
+      <c r="F75" s="148"/>
+      <c r="G75" s="148"/>
     </row>
     <row r="76" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="62" t="s">
@@ -24465,14 +24465,14 @@
     </row>
     <row r="83" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="186" t="s">
+      <c r="B84" s="148" t="s">
         <v>1958</v>
       </c>
-      <c r="C84" s="186"/>
-      <c r="D84" s="186"/>
-      <c r="E84" s="186"/>
-      <c r="F84" s="186"/>
-      <c r="G84" s="186"/>
+      <c r="C84" s="148"/>
+      <c r="D84" s="148"/>
+      <c r="E84" s="148"/>
+      <c r="F84" s="148"/>
+      <c r="G84" s="148"/>
     </row>
     <row r="85" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="58" t="s">
@@ -24663,13 +24663,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>1999</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
     </row>
     <row r="3" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -24678,13 +24678,13 @@
     </row>
     <row r="4" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="186" t="s">
+      <c r="B5" s="148" t="s">
         <v>2001</v>
       </c>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
     </row>
     <row r="6" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -24842,13 +24842,13 @@
     </row>
     <row r="15" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="186" t="s">
+      <c r="B16" s="148" t="s">
         <v>2019</v>
       </c>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
     </row>
     <row r="17" spans="2:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
@@ -25360,13 +25360,13 @@
     </row>
     <row r="32" spans="2:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="186" t="s">
+      <c r="B33" s="148" t="s">
         <v>2053</v>
       </c>
-      <c r="C33" s="186"/>
-      <c r="D33" s="186"/>
-      <c r="E33" s="186"/>
-      <c r="F33" s="186"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="148"/>
     </row>
     <row r="34" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -25455,13 +25455,13 @@
     </row>
     <row r="45" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="186" t="s">
+      <c r="B46" s="148" t="s">
         <v>2065</v>
       </c>
-      <c r="C46" s="186"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="186"/>
+      <c r="C46" s="148"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="148"/>
+      <c r="F46" s="148"/>
     </row>
     <row r="47" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -25499,13 +25499,13 @@
     <row r="56" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="186" t="s">
+      <c r="B58" s="148" t="s">
         <v>2072</v>
       </c>
-      <c r="C58" s="186"/>
-      <c r="D58" s="186"/>
-      <c r="E58" s="186"/>
-      <c r="F58" s="186"/>
+      <c r="C58" s="148"/>
+      <c r="D58" s="148"/>
+      <c r="E58" s="148"/>
+      <c r="F58" s="148"/>
     </row>
     <row r="59" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="58" t="s">
@@ -26089,13 +26089,13 @@
     </row>
     <row r="85" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="86" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="186" t="s">
+      <c r="B86" s="148" t="s">
         <v>2171</v>
       </c>
-      <c r="C86" s="186"/>
-      <c r="D86" s="186"/>
-      <c r="E86" s="186"/>
-      <c r="F86" s="186"/>
+      <c r="C86" s="148"/>
+      <c r="D86" s="148"/>
+      <c r="E86" s="148"/>
+      <c r="F86" s="148"/>
     </row>
     <row r="87" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="58" t="s">
@@ -26177,13 +26177,13 @@
     </row>
     <row r="99" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="100" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="186" t="s">
+      <c r="B100" s="148" t="s">
         <v>2186</v>
       </c>
-      <c r="C100" s="186"/>
-      <c r="D100" s="186"/>
-      <c r="E100" s="186"/>
-      <c r="F100" s="186"/>
+      <c r="C100" s="148"/>
+      <c r="D100" s="148"/>
+      <c r="E100" s="148"/>
+      <c r="F100" s="148"/>
     </row>
     <row r="101" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="58" t="s">
@@ -26338,13 +26338,13 @@
     </row>
     <row r="114" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="186" t="s">
+      <c r="B115" s="148" t="s">
         <v>2219</v>
       </c>
-      <c r="C115" s="186"/>
-      <c r="D115" s="186"/>
-      <c r="E115" s="186"/>
-      <c r="F115" s="186"/>
+      <c r="C115" s="148"/>
+      <c r="D115" s="148"/>
+      <c r="E115" s="148"/>
+      <c r="F115" s="148"/>
     </row>
     <row r="116" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="58" t="s">
@@ -26395,10 +26395,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>2223</v>
       </c>
-      <c r="C2" s="186"/>
+      <c r="C2" s="148"/>
     </row>
     <row r="3" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -26422,10 +26422,10 @@
     </row>
     <row r="7" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="186" t="s">
+      <c r="B8" s="148" t="s">
         <v>2228</v>
       </c>
-      <c r="C8" s="186"/>
+      <c r="C8" s="148"/>
     </row>
     <row r="9" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="58" t="s">
@@ -26596,10 +26596,10 @@
     </row>
     <row r="32" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="186" t="s">
+      <c r="B33" s="148" t="s">
         <v>2260</v>
       </c>
-      <c r="C33" s="186"/>
+      <c r="C33" s="148"/>
     </row>
     <row r="34" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="58" t="s">
@@ -26851,10 +26851,10 @@
     </row>
     <row r="68" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="186" t="s">
+      <c r="B69" s="148" t="s">
         <v>2293</v>
       </c>
-      <c r="C69" s="186"/>
+      <c r="C69" s="148"/>
     </row>
     <row r="70" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="58" t="s">
@@ -26944,10 +26944,10 @@
     </row>
     <row r="82" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="186" t="s">
+      <c r="B83" s="148" t="s">
         <v>2305</v>
       </c>
-      <c r="C83" s="186"/>
+      <c r="C83" s="148"/>
     </row>
     <row r="84" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="58" t="s">
@@ -27280,10 +27280,10 @@
     </row>
     <row r="129" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="130" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="186" t="s">
+      <c r="B130" s="148" t="s">
         <v>2348</v>
       </c>
-      <c r="C130" s="186"/>
+      <c r="C130" s="148"/>
     </row>
     <row r="131" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="58" t="s">
@@ -27454,10 +27454,10 @@
     </row>
     <row r="154" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="155" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="186" t="s">
+      <c r="B155" s="148" t="s">
         <v>2370</v>
       </c>
-      <c r="C155" s="186"/>
+      <c r="C155" s="148"/>
     </row>
     <row r="156" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B156" s="58" t="s">
@@ -27547,10 +27547,10 @@
     </row>
     <row r="168" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="169" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="186" t="s">
+      <c r="B169" s="148" t="s">
         <v>2382</v>
       </c>
-      <c r="C169" s="186"/>
+      <c r="C169" s="148"/>
     </row>
     <row r="170" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="58" t="s">
@@ -27802,10 +27802,10 @@
     </row>
     <row r="204" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="205" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="186" t="s">
+      <c r="B205" s="148" t="s">
         <v>2414</v>
       </c>
-      <c r="C205" s="186"/>
+      <c r="C205" s="148"/>
     </row>
     <row r="206" spans="2:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="58" t="s">
@@ -27930,13 +27930,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>2426</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
     </row>
     <row r="3" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -27960,13 +27960,13 @@
     </row>
     <row r="7" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="186" t="s">
+      <c r="B8" s="148" t="s">
         <v>2431</v>
       </c>
-      <c r="C8" s="186"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
     </row>
     <row r="9" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="60" t="s">
@@ -28140,13 +28140,13 @@
     </row>
     <row r="19" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="186" t="s">
+      <c r="B20" s="148" t="s">
         <v>2471</v>
       </c>
-      <c r="C20" s="186"/>
-      <c r="D20" s="186"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="186"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="148"/>
     </row>
     <row r="21" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
@@ -28200,13 +28200,13 @@
     </row>
     <row r="27" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="186" t="s">
+      <c r="B28" s="148" t="s">
         <v>2484</v>
       </c>
-      <c r="C28" s="186"/>
-      <c r="D28" s="186"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186"/>
+      <c r="C28" s="148"/>
+      <c r="D28" s="148"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
     </row>
     <row r="29" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="60" t="s">
@@ -28287,13 +28287,13 @@
     </row>
     <row r="36" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="186" t="s">
+      <c r="B37" s="148" t="s">
         <v>2502</v>
       </c>
-      <c r="C37" s="186"/>
-      <c r="D37" s="186"/>
-      <c r="E37" s="186"/>
-      <c r="F37" s="186"/>
+      <c r="C37" s="148"/>
+      <c r="D37" s="148"/>
+      <c r="E37" s="148"/>
+      <c r="F37" s="148"/>
     </row>
     <row r="38" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="60" t="s">
@@ -28361,13 +28361,13 @@
     </row>
     <row r="46" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="186" t="s">
+      <c r="B47" s="148" t="s">
         <v>2518</v>
       </c>
-      <c r="C47" s="186"/>
-      <c r="D47" s="186"/>
-      <c r="E47" s="186"/>
-      <c r="F47" s="186"/>
+      <c r="C47" s="148"/>
+      <c r="D47" s="148"/>
+      <c r="E47" s="148"/>
+      <c r="F47" s="148"/>
     </row>
     <row r="48" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="58" t="s">
@@ -28442,13 +28442,13 @@
     </row>
     <row r="55" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="186" t="s">
+      <c r="B56" s="148" t="s">
         <v>2537</v>
       </c>
-      <c r="C56" s="186"/>
-      <c r="D56" s="186"/>
-      <c r="E56" s="186"/>
-      <c r="F56" s="186"/>
+      <c r="C56" s="148"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="148"/>
+      <c r="F56" s="148"/>
     </row>
     <row r="57" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="60" t="s">
@@ -28571,12 +28571,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>2558</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
     </row>
     <row r="3" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -28600,12 +28600,12 @@
     </row>
     <row r="7" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="186" t="s">
+      <c r="B8" s="148" t="s">
         <v>2563</v>
       </c>
-      <c r="C8" s="186"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
     </row>
     <row r="9" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="60" t="s">
@@ -28697,12 +28697,12 @@
     </row>
     <row r="17" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="186" t="s">
+      <c r="B18" s="148" t="s">
         <v>2587</v>
       </c>
-      <c r="C18" s="186"/>
-      <c r="D18" s="186"/>
-      <c r="E18" s="186"/>
+      <c r="C18" s="148"/>
+      <c r="D18" s="148"/>
+      <c r="E18" s="148"/>
     </row>
     <row r="19" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="58" t="s">
@@ -28846,12 +28846,12 @@
     </row>
     <row r="37" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="186" t="s">
+      <c r="B38" s="148" t="s">
         <v>2620</v>
       </c>
-      <c r="C38" s="186"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
+      <c r="C38" s="148"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
     </row>
     <row r="39" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="58" t="s">
@@ -29214,12 +29214,12 @@
     </row>
     <row r="76" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="186" t="s">
+      <c r="B77" s="148" t="s">
         <v>2690</v>
       </c>
-      <c r="C77" s="186"/>
-      <c r="D77" s="186"/>
-      <c r="E77" s="186"/>
+      <c r="C77" s="148"/>
+      <c r="D77" s="148"/>
+      <c r="E77" s="148"/>
     </row>
     <row r="78" spans="2:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="58" t="s">
@@ -29338,12 +29338,12 @@
     </row>
     <row r="94" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="186" t="s">
+      <c r="B95" s="148" t="s">
         <v>2718</v>
       </c>
-      <c r="C95" s="186"/>
-      <c r="D95" s="186"/>
-      <c r="E95" s="186"/>
+      <c r="C95" s="148"/>
+      <c r="D95" s="148"/>
+      <c r="E95" s="148"/>
     </row>
     <row r="96" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="58" t="s">
@@ -29800,12 +29800,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B95:E95"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B95:E95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -29834,14 +29834,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>2804</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
     </row>
     <row r="3" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -29865,14 +29865,14 @@
     </row>
     <row r="7" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="186" t="s">
+      <c r="B8" s="148" t="s">
         <v>2809</v>
       </c>
-      <c r="C8" s="186"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="186"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
     </row>
     <row r="9" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="60" t="s">
@@ -30371,14 +30371,14 @@
     </row>
     <row r="37" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="186" t="s">
+      <c r="B38" s="148" t="s">
         <v>2868</v>
       </c>
-      <c r="C38" s="186"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="186"/>
+      <c r="C38" s="148"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
+      <c r="F38" s="148"/>
+      <c r="G38" s="148"/>
     </row>
     <row r="39" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
@@ -30552,14 +30552,14 @@
     </row>
     <row r="49" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="186" t="s">
+      <c r="B50" s="148" t="s">
         <v>2915</v>
       </c>
-      <c r="C50" s="186"/>
-      <c r="D50" s="186"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="186"/>
+      <c r="C50" s="148"/>
+      <c r="D50" s="148"/>
+      <c r="E50" s="148"/>
+      <c r="F50" s="148"/>
+      <c r="G50" s="148"/>
     </row>
     <row r="51" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="60" t="s">
@@ -30716,14 +30716,14 @@
     </row>
     <row r="66" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="186" t="s">
+      <c r="B67" s="148" t="s">
         <v>2950</v>
       </c>
-      <c r="C67" s="186"/>
-      <c r="D67" s="186"/>
-      <c r="E67" s="186"/>
-      <c r="F67" s="186"/>
-      <c r="G67" s="186"/>
+      <c r="C67" s="148"/>
+      <c r="D67" s="148"/>
+      <c r="E67" s="148"/>
+      <c r="F67" s="148"/>
+      <c r="G67" s="148"/>
     </row>
     <row r="68" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="58" t="s">
@@ -31062,14 +31062,14 @@
     </row>
     <row r="95" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="186" t="s">
+      <c r="B96" s="148" t="s">
         <v>3021</v>
       </c>
-      <c r="C96" s="186"/>
-      <c r="D96" s="186"/>
-      <c r="E96" s="186"/>
-      <c r="F96" s="186"/>
-      <c r="G96" s="186"/>
+      <c r="C96" s="148"/>
+      <c r="D96" s="148"/>
+      <c r="E96" s="148"/>
+      <c r="F96" s="148"/>
+      <c r="G96" s="148"/>
     </row>
     <row r="97" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="60" t="s">
@@ -31164,14 +31164,14 @@
     </row>
     <row r="104" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="186" t="s">
+      <c r="B105" s="148" t="s">
         <v>3043</v>
       </c>
-      <c r="C105" s="186"/>
-      <c r="D105" s="186"/>
-      <c r="E105" s="186"/>
-      <c r="F105" s="186"/>
-      <c r="G105" s="186"/>
+      <c r="C105" s="148"/>
+      <c r="D105" s="148"/>
+      <c r="E105" s="148"/>
+      <c r="F105" s="148"/>
+      <c r="G105" s="148"/>
     </row>
     <row r="106" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="58" t="s">
@@ -31280,14 +31280,14 @@
     </row>
     <row r="119" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="186" t="s">
+      <c r="B120" s="148" t="s">
         <v>3062</v>
       </c>
-      <c r="C120" s="186"/>
-      <c r="D120" s="186"/>
-      <c r="E120" s="186"/>
-      <c r="F120" s="186"/>
-      <c r="G120" s="186"/>
+      <c r="C120" s="148"/>
+      <c r="D120" s="148"/>
+      <c r="E120" s="148"/>
+      <c r="F120" s="148"/>
+      <c r="G120" s="148"/>
     </row>
     <row r="121" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="60" t="s">
@@ -32160,12 +32160,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="148" t="s">
         <v>302</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
     </row>
     <row r="3" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -32184,12 +32184,12 @@
     </row>
     <row r="6" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="186" t="s">
+      <c r="B7" s="148" t="s">
         <v>306</v>
       </c>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
     </row>
     <row r="8" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="60" t="s">
@@ -32318,12 +32318,12 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="186" t="s">
+      <c r="B17" s="148" t="s">
         <v>343</v>
       </c>
-      <c r="C17" s="186"/>
-      <c r="D17" s="186"/>
-      <c r="E17" s="186"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="148"/>
     </row>
     <row r="18" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
@@ -32411,12 +32411,12 @@
     </row>
     <row r="24" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="186" t="s">
+      <c r="B25" s="148" t="s">
         <v>364</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="186"/>
-      <c r="E25" s="186"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
     </row>
     <row r="26" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="62" t="s">
@@ -32468,12 +32468,12 @@
     </row>
     <row r="32" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="186" t="s">
+      <c r="B33" s="148" t="s">
         <v>377</v>
       </c>
-      <c r="C33" s="186"/>
-      <c r="D33" s="186"/>
-      <c r="E33" s="186"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
     </row>
     <row r="34" spans="2:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="62" t="s">
@@ -32580,65 +32580,65 @@
   <sheetData>
     <row r="1" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="178"/>
-      <c r="L2" s="178"/>
-      <c r="M2" s="178"/>
-      <c r="N2" s="178"/>
-      <c r="O2" s="178"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="154"/>
       <c r="R2" s="5"/>
-      <c r="S2" s="178" t="s">
+      <c r="S2" s="154" t="s">
         <v>143</v>
       </c>
-      <c r="T2" s="178"/>
-      <c r="U2" s="178"/>
-      <c r="V2" s="178"/>
-      <c r="W2" s="178"/>
-      <c r="X2" s="178"/>
-      <c r="Y2" s="178"/>
-      <c r="Z2" s="178"/>
-      <c r="AA2" s="178"/>
-      <c r="AB2" s="178"/>
-      <c r="AC2" s="178"/>
-      <c r="AD2" s="178"/>
-      <c r="AE2" s="178"/>
-      <c r="AF2" s="178"/>
-      <c r="AG2" s="178"/>
-      <c r="AH2" s="178"/>
-      <c r="AI2" s="178"/>
-      <c r="AJ2" s="178"/>
-      <c r="AK2" s="178"/>
-      <c r="AL2" s="178"/>
-      <c r="AM2" s="178"/>
-      <c r="AN2" s="178"/>
-      <c r="AO2" s="178"/>
-      <c r="AP2" s="178"/>
-      <c r="AQ2" s="178"/>
-      <c r="AR2" s="178"/>
-      <c r="AS2" s="178"/>
-      <c r="AT2" s="178"/>
-      <c r="AU2" s="178"/>
-      <c r="AV2" s="178"/>
-      <c r="AW2" s="178"/>
-      <c r="AX2" s="178"/>
-      <c r="AY2" s="178"/>
-      <c r="AZ2" s="178"/>
-      <c r="BA2" s="178"/>
-      <c r="BB2" s="178"/>
-      <c r="BC2" s="178"/>
-      <c r="BD2" s="178"/>
-      <c r="BE2" s="178"/>
-      <c r="BF2" s="178"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="154"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="154"/>
+      <c r="AE2" s="154"/>
+      <c r="AF2" s="154"/>
+      <c r="AG2" s="154"/>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="154"/>
+      <c r="AJ2" s="154"/>
+      <c r="AK2" s="154"/>
+      <c r="AL2" s="154"/>
+      <c r="AM2" s="154"/>
+      <c r="AN2" s="154"/>
+      <c r="AO2" s="154"/>
+      <c r="AP2" s="154"/>
+      <c r="AQ2" s="154"/>
+      <c r="AR2" s="154"/>
+      <c r="AS2" s="154"/>
+      <c r="AT2" s="154"/>
+      <c r="AU2" s="154"/>
+      <c r="AV2" s="154"/>
+      <c r="AW2" s="154"/>
+      <c r="AX2" s="154"/>
+      <c r="AY2" s="154"/>
+      <c r="AZ2" s="154"/>
+      <c r="BA2" s="154"/>
+      <c r="BB2" s="154"/>
+      <c r="BC2" s="154"/>
+      <c r="BD2" s="154"/>
+      <c r="BE2" s="154"/>
+      <c r="BF2" s="154"/>
       <c r="BG2" s="6"/>
       <c r="BH2" s="6"/>
       <c r="BI2" s="6"/>
@@ -32664,154 +32664,154 @@
       </c>
     </row>
     <row r="3" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
-      <c r="P3" s="178"/>
-      <c r="Q3" s="178"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
+      <c r="O3" s="154"/>
+      <c r="P3" s="154"/>
+      <c r="Q3" s="154"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="178"/>
-      <c r="T3" s="178"/>
-      <c r="U3" s="178"/>
-      <c r="V3" s="178"/>
-      <c r="W3" s="178"/>
-      <c r="X3" s="178"/>
-      <c r="Y3" s="178"/>
-      <c r="Z3" s="178"/>
-      <c r="AA3" s="178"/>
-      <c r="AB3" s="178"/>
-      <c r="AC3" s="178"/>
-      <c r="AD3" s="178"/>
-      <c r="AE3" s="178"/>
-      <c r="AF3" s="178"/>
-      <c r="AG3" s="178"/>
-      <c r="AH3" s="178"/>
-      <c r="AI3" s="178"/>
-      <c r="AJ3" s="178"/>
-      <c r="AK3" s="178"/>
-      <c r="AL3" s="178"/>
-      <c r="AM3" s="178"/>
-      <c r="AN3" s="178"/>
-      <c r="AO3" s="178"/>
-      <c r="AP3" s="178"/>
-      <c r="AQ3" s="178"/>
-      <c r="AR3" s="178"/>
-      <c r="AS3" s="178"/>
-      <c r="AT3" s="178"/>
-      <c r="AU3" s="178"/>
-      <c r="AV3" s="178"/>
-      <c r="AW3" s="178"/>
-      <c r="AX3" s="178"/>
-      <c r="AY3" s="178"/>
-      <c r="AZ3" s="178"/>
-      <c r="BA3" s="178"/>
-      <c r="BB3" s="178"/>
-      <c r="BC3" s="178"/>
-      <c r="BD3" s="178"/>
-      <c r="BE3" s="178"/>
-      <c r="BF3" s="178"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="154"/>
+      <c r="V3" s="154"/>
+      <c r="W3" s="154"/>
+      <c r="X3" s="154"/>
+      <c r="Y3" s="154"/>
+      <c r="Z3" s="154"/>
+      <c r="AA3" s="154"/>
+      <c r="AB3" s="154"/>
+      <c r="AC3" s="154"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="154"/>
+      <c r="AF3" s="154"/>
+      <c r="AG3" s="154"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="154"/>
+      <c r="AJ3" s="154"/>
+      <c r="AK3" s="154"/>
+      <c r="AL3" s="154"/>
+      <c r="AM3" s="154"/>
+      <c r="AN3" s="154"/>
+      <c r="AO3" s="154"/>
+      <c r="AP3" s="154"/>
+      <c r="AQ3" s="154"/>
+      <c r="AR3" s="154"/>
+      <c r="AS3" s="154"/>
+      <c r="AT3" s="154"/>
+      <c r="AU3" s="154"/>
+      <c r="AV3" s="154"/>
+      <c r="AW3" s="154"/>
+      <c r="AX3" s="154"/>
+      <c r="AY3" s="154"/>
+      <c r="AZ3" s="154"/>
+      <c r="BA3" s="154"/>
+      <c r="BB3" s="154"/>
+      <c r="BC3" s="154"/>
+      <c r="BD3" s="154"/>
+      <c r="BE3" s="154"/>
+      <c r="BF3" s="154"/>
       <c r="BG3" s="6"/>
-      <c r="BH3" s="179" t="s">
+      <c r="BH3" s="155" t="s">
         <v>148</v>
       </c>
-      <c r="BI3" s="179"/>
-      <c r="BJ3" s="179"/>
-      <c r="BK3" s="179"/>
-      <c r="BL3" s="179"/>
-      <c r="BM3" s="179"/>
-      <c r="BN3" s="179"/>
-      <c r="BO3" s="179"/>
-      <c r="BP3" s="179"/>
-      <c r="BQ3" s="179"/>
-      <c r="BR3" s="179"/>
-      <c r="BS3" s="179"/>
-      <c r="BT3" s="179"/>
-      <c r="BU3" s="179"/>
+      <c r="BI3" s="155"/>
+      <c r="BJ3" s="155"/>
+      <c r="BK3" s="155"/>
+      <c r="BL3" s="155"/>
+      <c r="BM3" s="155"/>
+      <c r="BN3" s="155"/>
+      <c r="BO3" s="155"/>
+      <c r="BP3" s="155"/>
+      <c r="BQ3" s="155"/>
+      <c r="BR3" s="155"/>
+      <c r="BS3" s="155"/>
+      <c r="BT3" s="155"/>
+      <c r="BU3" s="155"/>
       <c r="CO3" s="8"/>
       <c r="CZ3" s="9"/>
     </row>
     <row r="4" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="178"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="178"/>
-      <c r="Q4" s="178"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="154"/>
+      <c r="P4" s="154"/>
+      <c r="Q4" s="154"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="178"/>
-      <c r="T4" s="178"/>
-      <c r="U4" s="178"/>
-      <c r="V4" s="178"/>
-      <c r="W4" s="178"/>
-      <c r="X4" s="178"/>
-      <c r="Y4" s="178"/>
-      <c r="Z4" s="178"/>
-      <c r="AA4" s="178"/>
-      <c r="AB4" s="178"/>
-      <c r="AC4" s="178"/>
-      <c r="AD4" s="178"/>
-      <c r="AE4" s="178"/>
-      <c r="AF4" s="178"/>
-      <c r="AG4" s="178"/>
-      <c r="AH4" s="178"/>
-      <c r="AI4" s="178"/>
-      <c r="AJ4" s="178"/>
-      <c r="AK4" s="178"/>
-      <c r="AL4" s="178"/>
-      <c r="AM4" s="178"/>
-      <c r="AN4" s="178"/>
-      <c r="AO4" s="178"/>
-      <c r="AP4" s="178"/>
-      <c r="AQ4" s="178"/>
-      <c r="AR4" s="178"/>
-      <c r="AS4" s="178"/>
-      <c r="AT4" s="178"/>
-      <c r="AU4" s="178"/>
-      <c r="AV4" s="178"/>
-      <c r="AW4" s="178"/>
-      <c r="AX4" s="178"/>
-      <c r="AY4" s="178"/>
-      <c r="AZ4" s="178"/>
-      <c r="BA4" s="178"/>
-      <c r="BB4" s="178"/>
-      <c r="BC4" s="178"/>
-      <c r="BD4" s="178"/>
-      <c r="BE4" s="178"/>
-      <c r="BF4" s="178"/>
+      <c r="S4" s="154"/>
+      <c r="T4" s="154"/>
+      <c r="U4" s="154"/>
+      <c r="V4" s="154"/>
+      <c r="W4" s="154"/>
+      <c r="X4" s="154"/>
+      <c r="Y4" s="154"/>
+      <c r="Z4" s="154"/>
+      <c r="AA4" s="154"/>
+      <c r="AB4" s="154"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="154"/>
+      <c r="AE4" s="154"/>
+      <c r="AF4" s="154"/>
+      <c r="AG4" s="154"/>
+      <c r="AH4" s="154"/>
+      <c r="AI4" s="154"/>
+      <c r="AJ4" s="154"/>
+      <c r="AK4" s="154"/>
+      <c r="AL4" s="154"/>
+      <c r="AM4" s="154"/>
+      <c r="AN4" s="154"/>
+      <c r="AO4" s="154"/>
+      <c r="AP4" s="154"/>
+      <c r="AQ4" s="154"/>
+      <c r="AR4" s="154"/>
+      <c r="AS4" s="154"/>
+      <c r="AT4" s="154"/>
+      <c r="AU4" s="154"/>
+      <c r="AV4" s="154"/>
+      <c r="AW4" s="154"/>
+      <c r="AX4" s="154"/>
+      <c r="AY4" s="154"/>
+      <c r="AZ4" s="154"/>
+      <c r="BA4" s="154"/>
+      <c r="BB4" s="154"/>
+      <c r="BC4" s="154"/>
+      <c r="BD4" s="154"/>
+      <c r="BE4" s="154"/>
+      <c r="BF4" s="154"/>
       <c r="BG4" s="6"/>
-      <c r="BH4" s="180" t="s">
+      <c r="BH4" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="BI4" s="180"/>
-      <c r="BJ4" s="180"/>
-      <c r="BK4" s="180"/>
-      <c r="BL4" s="180"/>
-      <c r="BM4" s="180"/>
-      <c r="BN4" s="180"/>
-      <c r="BO4" s="180"/>
-      <c r="BP4" s="180"/>
-      <c r="BQ4" s="180"/>
-      <c r="BR4" s="180"/>
-      <c r="BS4" s="180"/>
-      <c r="BT4" s="180"/>
-      <c r="BU4" s="180"/>
+      <c r="BI4" s="156"/>
+      <c r="BJ4" s="156"/>
+      <c r="BK4" s="156"/>
+      <c r="BL4" s="156"/>
+      <c r="BM4" s="156"/>
+      <c r="BN4" s="156"/>
+      <c r="BO4" s="156"/>
+      <c r="BP4" s="156"/>
+      <c r="BQ4" s="156"/>
+      <c r="BR4" s="156"/>
+      <c r="BS4" s="156"/>
+      <c r="BT4" s="156"/>
+      <c r="BU4" s="156"/>
       <c r="CA4" s="8"/>
       <c r="CB4" s="8"/>
       <c r="CC4" s="8"/>
@@ -32841,77 +32841,77 @@
       </c>
     </row>
     <row r="5" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="181" t="s">
+      <c r="D5" s="157" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="181"/>
-      <c r="P5" s="181"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="5"/>
-      <c r="S5" s="181" t="s">
+      <c r="S5" s="157" t="s">
         <v>154</v>
       </c>
-      <c r="T5" s="181"/>
-      <c r="U5" s="181"/>
-      <c r="V5" s="181"/>
-      <c r="W5" s="181"/>
-      <c r="X5" s="181"/>
-      <c r="Y5" s="181"/>
-      <c r="Z5" s="181"/>
-      <c r="AA5" s="181"/>
-      <c r="AB5" s="181"/>
-      <c r="AC5" s="181"/>
-      <c r="AD5" s="181"/>
-      <c r="AE5" s="181"/>
-      <c r="AF5" s="181"/>
-      <c r="AG5" s="181"/>
-      <c r="AH5" s="181"/>
-      <c r="AI5" s="181"/>
-      <c r="AJ5" s="181"/>
-      <c r="AK5" s="181"/>
-      <c r="AL5" s="181"/>
-      <c r="AM5" s="181"/>
-      <c r="AN5" s="181"/>
-      <c r="AO5" s="181"/>
-      <c r="AP5" s="181"/>
-      <c r="AQ5" s="181"/>
-      <c r="AR5" s="181"/>
-      <c r="AS5" s="181"/>
-      <c r="AT5" s="181"/>
-      <c r="AU5" s="181"/>
-      <c r="AV5" s="181"/>
-      <c r="AW5" s="181"/>
-      <c r="AX5" s="181"/>
-      <c r="AY5" s="181"/>
-      <c r="AZ5" s="181"/>
-      <c r="BA5" s="181"/>
-      <c r="BB5" s="181"/>
-      <c r="BC5" s="181"/>
-      <c r="BD5" s="181"/>
-      <c r="BH5" s="180"/>
-      <c r="BI5" s="180"/>
-      <c r="BJ5" s="180"/>
-      <c r="BK5" s="180"/>
-      <c r="BL5" s="180"/>
-      <c r="BM5" s="180"/>
-      <c r="BN5" s="180"/>
-      <c r="BO5" s="180"/>
-      <c r="BP5" s="180"/>
-      <c r="BQ5" s="180"/>
-      <c r="BR5" s="180"/>
-      <c r="BS5" s="180"/>
-      <c r="BT5" s="180"/>
-      <c r="BU5" s="180"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="157"/>
+      <c r="W5" s="157"/>
+      <c r="X5" s="157"/>
+      <c r="Y5" s="157"/>
+      <c r="Z5" s="157"/>
+      <c r="AA5" s="157"/>
+      <c r="AB5" s="157"/>
+      <c r="AC5" s="157"/>
+      <c r="AD5" s="157"/>
+      <c r="AE5" s="157"/>
+      <c r="AF5" s="157"/>
+      <c r="AG5" s="157"/>
+      <c r="AH5" s="157"/>
+      <c r="AI5" s="157"/>
+      <c r="AJ5" s="157"/>
+      <c r="AK5" s="157"/>
+      <c r="AL5" s="157"/>
+      <c r="AM5" s="157"/>
+      <c r="AN5" s="157"/>
+      <c r="AO5" s="157"/>
+      <c r="AP5" s="157"/>
+      <c r="AQ5" s="157"/>
+      <c r="AR5" s="157"/>
+      <c r="AS5" s="157"/>
+      <c r="AT5" s="157"/>
+      <c r="AU5" s="157"/>
+      <c r="AV5" s="157"/>
+      <c r="AW5" s="157"/>
+      <c r="AX5" s="157"/>
+      <c r="AY5" s="157"/>
+      <c r="AZ5" s="157"/>
+      <c r="BA5" s="157"/>
+      <c r="BB5" s="157"/>
+      <c r="BC5" s="157"/>
+      <c r="BD5" s="157"/>
+      <c r="BH5" s="156"/>
+      <c r="BI5" s="156"/>
+      <c r="BJ5" s="156"/>
+      <c r="BK5" s="156"/>
+      <c r="BL5" s="156"/>
+      <c r="BM5" s="156"/>
+      <c r="BN5" s="156"/>
+      <c r="BO5" s="156"/>
+      <c r="BP5" s="156"/>
+      <c r="BQ5" s="156"/>
+      <c r="BR5" s="156"/>
+      <c r="BS5" s="156"/>
+      <c r="BT5" s="156"/>
+      <c r="BU5" s="156"/>
       <c r="CA5" s="8"/>
       <c r="CB5" s="8"/>
       <c r="CC5" s="8"/>
@@ -33172,108 +33172,108 @@
     </row>
     <row r="10" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="22"/>
-      <c r="D10" s="176" t="str">
+      <c r="D10" s="158" t="str">
         <f>IF((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))&gt;=1000000000,TEXT((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))/1000000000,"0.0")&amp;"B Claims",IF((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))&gt;=1000000,TEXT((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))/1000000,"0.0")&amp;"M Claims",IF((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))&gt;=1000,TEXT((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))/1000,"0.0")&amp;"K Claims",TEXT((INDEX('3. Workings'!$D$13:$F$13,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0))),"0.0")&amp;" Claims")))</f>
         <v>274.3K Claims</v>
       </c>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="176"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="176"/>
-      <c r="N10" s="176"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="158"/>
+      <c r="K10" s="158"/>
+      <c r="L10" s="158"/>
+      <c r="M10" s="158"/>
+      <c r="N10" s="158"/>
       <c r="O10" s="23"/>
       <c r="R10" s="22"/>
-      <c r="S10" s="176" t="str">
+      <c r="S10" s="158" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$22:$F$22,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)),"0.0")&amp;" Days"</f>
         <v>9.8 Days</v>
       </c>
-      <c r="T10" s="176"/>
-      <c r="U10" s="176"/>
-      <c r="V10" s="176"/>
-      <c r="W10" s="176"/>
-      <c r="X10" s="176"/>
-      <c r="Y10" s="176"/>
-      <c r="Z10" s="176"/>
-      <c r="AB10" s="176" t="str">
+      <c r="T10" s="158"/>
+      <c r="U10" s="158"/>
+      <c r="V10" s="158"/>
+      <c r="W10" s="158"/>
+      <c r="X10" s="158"/>
+      <c r="Y10" s="158"/>
+      <c r="Z10" s="158"/>
+      <c r="AB10" s="158" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$24:$F$24,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)),"0.0")&amp;" Days"</f>
         <v>2.7 Days</v>
       </c>
-      <c r="AC10" s="176"/>
-      <c r="AD10" s="176"/>
-      <c r="AE10" s="176"/>
-      <c r="AF10" s="176"/>
-      <c r="AG10" s="176"/>
-      <c r="AH10" s="176"/>
-      <c r="AI10" s="176"/>
+      <c r="AC10" s="158"/>
+      <c r="AD10" s="158"/>
+      <c r="AE10" s="158"/>
+      <c r="AF10" s="158"/>
+      <c r="AG10" s="158"/>
+      <c r="AH10" s="158"/>
+      <c r="AI10" s="158"/>
       <c r="AJ10" s="23"/>
       <c r="AM10" s="22"/>
-      <c r="AN10" s="176" t="str">
+      <c r="AN10" s="158" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$26:$F$26,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)),"0.0%")</f>
         <v>72.3%</v>
       </c>
-      <c r="AO10" s="176"/>
-      <c r="AP10" s="176"/>
-      <c r="AQ10" s="176"/>
-      <c r="AR10" s="176"/>
-      <c r="AS10" s="176"/>
-      <c r="AT10" s="176"/>
-      <c r="AU10" s="176"/>
-      <c r="AV10" s="176"/>
-      <c r="AW10" s="176"/>
-      <c r="AX10" s="176"/>
+      <c r="AO10" s="158"/>
+      <c r="AP10" s="158"/>
+      <c r="AQ10" s="158"/>
+      <c r="AR10" s="158"/>
+      <c r="AS10" s="158"/>
+      <c r="AT10" s="158"/>
+      <c r="AU10" s="158"/>
+      <c r="AV10" s="158"/>
+      <c r="AW10" s="158"/>
+      <c r="AX10" s="158"/>
       <c r="AY10" s="23"/>
       <c r="BB10" s="22"/>
-      <c r="BC10" s="176" t="str">
+      <c r="BC10" s="158" t="str">
         <f>"₹"&amp;TEXT(INDEX('3. Workings'!$D$71:$F$71,MATCH($BH$4,'3. Workings'!$D$68:$F$68,0)),"0.0")&amp;" Cr"</f>
         <v>₹75.3 Cr</v>
       </c>
-      <c r="BD10" s="176"/>
-      <c r="BE10" s="176"/>
-      <c r="BF10" s="176"/>
-      <c r="BG10" s="176"/>
-      <c r="BH10" s="176"/>
-      <c r="BI10" s="176"/>
-      <c r="BJ10" s="176"/>
-      <c r="BK10" s="176"/>
-      <c r="BL10" s="176"/>
-      <c r="BM10" s="176"/>
+      <c r="BD10" s="158"/>
+      <c r="BE10" s="158"/>
+      <c r="BF10" s="158"/>
+      <c r="BG10" s="158"/>
+      <c r="BH10" s="158"/>
+      <c r="BI10" s="158"/>
+      <c r="BJ10" s="158"/>
+      <c r="BK10" s="158"/>
+      <c r="BL10" s="158"/>
+      <c r="BM10" s="158"/>
       <c r="BN10" s="23"/>
       <c r="BQ10" s="22"/>
-      <c r="BR10" s="176" t="str">
+      <c r="BR10" s="158" t="str">
         <f>TEXT(INDEX('4. Forecast'!$D$50:$F$50,MATCH($BH$4,'4. Forecast'!$D$45:$F$45,0)),"0.0")&amp;" Months"</f>
         <v>13.8 Months</v>
       </c>
-      <c r="BS10" s="176"/>
-      <c r="BT10" s="176"/>
-      <c r="BU10" s="176"/>
-      <c r="BV10" s="176"/>
-      <c r="BW10" s="176"/>
-      <c r="BX10" s="176"/>
-      <c r="BY10" s="176"/>
-      <c r="BZ10" s="176"/>
-      <c r="CA10" s="176"/>
-      <c r="CB10" s="176"/>
+      <c r="BS10" s="158"/>
+      <c r="BT10" s="158"/>
+      <c r="BU10" s="158"/>
+      <c r="BV10" s="158"/>
+      <c r="BW10" s="158"/>
+      <c r="BX10" s="158"/>
+      <c r="BY10" s="158"/>
+      <c r="BZ10" s="158"/>
+      <c r="CA10" s="158"/>
+      <c r="CB10" s="158"/>
       <c r="CC10" s="23"/>
       <c r="CF10" s="22"/>
-      <c r="CG10" s="176" t="str">
+      <c r="CG10" s="158" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$82:$F$82,MATCH($BH$4,'3. Workings'!$D$77:$F$77,0)),"0.0")&amp;" pp"</f>
         <v>4.5 pp</v>
       </c>
-      <c r="CH10" s="176"/>
-      <c r="CI10" s="176"/>
-      <c r="CJ10" s="176"/>
-      <c r="CK10" s="176"/>
-      <c r="CL10" s="176"/>
-      <c r="CM10" s="176"/>
-      <c r="CN10" s="176"/>
-      <c r="CO10" s="176"/>
-      <c r="CP10" s="176"/>
-      <c r="CQ10" s="176"/>
+      <c r="CH10" s="158"/>
+      <c r="CI10" s="158"/>
+      <c r="CJ10" s="158"/>
+      <c r="CK10" s="158"/>
+      <c r="CL10" s="158"/>
+      <c r="CM10" s="158"/>
+      <c r="CN10" s="158"/>
+      <c r="CO10" s="158"/>
+      <c r="CP10" s="158"/>
+      <c r="CQ10" s="158"/>
       <c r="CR10" s="23"/>
       <c r="CZ10" s="10" t="s">
         <v>175</v>
@@ -33302,87 +33302,87 @@
     </row>
     <row r="11" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="176"/>
-      <c r="M11" s="176"/>
-      <c r="N11" s="176"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="158"/>
+      <c r="M11" s="158"/>
+      <c r="N11" s="158"/>
       <c r="O11" s="23"/>
       <c r="R11" s="22"/>
-      <c r="S11" s="176"/>
-      <c r="T11" s="176"/>
-      <c r="U11" s="176"/>
-      <c r="V11" s="176"/>
-      <c r="W11" s="176"/>
-      <c r="X11" s="176"/>
-      <c r="Y11" s="176"/>
-      <c r="Z11" s="176"/>
-      <c r="AB11" s="176"/>
-      <c r="AC11" s="176"/>
-      <c r="AD11" s="176"/>
-      <c r="AE11" s="176"/>
-      <c r="AF11" s="176"/>
-      <c r="AG11" s="176"/>
-      <c r="AH11" s="176"/>
-      <c r="AI11" s="176"/>
+      <c r="S11" s="158"/>
+      <c r="T11" s="158"/>
+      <c r="U11" s="158"/>
+      <c r="V11" s="158"/>
+      <c r="W11" s="158"/>
+      <c r="X11" s="158"/>
+      <c r="Y11" s="158"/>
+      <c r="Z11" s="158"/>
+      <c r="AB11" s="158"/>
+      <c r="AC11" s="158"/>
+      <c r="AD11" s="158"/>
+      <c r="AE11" s="158"/>
+      <c r="AF11" s="158"/>
+      <c r="AG11" s="158"/>
+      <c r="AH11" s="158"/>
+      <c r="AI11" s="158"/>
       <c r="AJ11" s="23"/>
       <c r="AM11" s="22"/>
-      <c r="AN11" s="176"/>
-      <c r="AO11" s="176"/>
-      <c r="AP11" s="176"/>
-      <c r="AQ11" s="176"/>
-      <c r="AR11" s="176"/>
-      <c r="AS11" s="176"/>
-      <c r="AT11" s="176"/>
-      <c r="AU11" s="176"/>
-      <c r="AV11" s="176"/>
-      <c r="AW11" s="176"/>
-      <c r="AX11" s="176"/>
+      <c r="AN11" s="158"/>
+      <c r="AO11" s="158"/>
+      <c r="AP11" s="158"/>
+      <c r="AQ11" s="158"/>
+      <c r="AR11" s="158"/>
+      <c r="AS11" s="158"/>
+      <c r="AT11" s="158"/>
+      <c r="AU11" s="158"/>
+      <c r="AV11" s="158"/>
+      <c r="AW11" s="158"/>
+      <c r="AX11" s="158"/>
       <c r="AY11" s="23"/>
       <c r="BB11" s="22"/>
-      <c r="BC11" s="176"/>
-      <c r="BD11" s="176"/>
-      <c r="BE11" s="176"/>
-      <c r="BF11" s="176"/>
-      <c r="BG11" s="176"/>
-      <c r="BH11" s="176"/>
-      <c r="BI11" s="176"/>
-      <c r="BJ11" s="176"/>
-      <c r="BK11" s="176"/>
-      <c r="BL11" s="176"/>
-      <c r="BM11" s="176"/>
+      <c r="BC11" s="158"/>
+      <c r="BD11" s="158"/>
+      <c r="BE11" s="158"/>
+      <c r="BF11" s="158"/>
+      <c r="BG11" s="158"/>
+      <c r="BH11" s="158"/>
+      <c r="BI11" s="158"/>
+      <c r="BJ11" s="158"/>
+      <c r="BK11" s="158"/>
+      <c r="BL11" s="158"/>
+      <c r="BM11" s="158"/>
       <c r="BN11" s="23"/>
       <c r="BQ11" s="22"/>
-      <c r="BR11" s="176"/>
-      <c r="BS11" s="176"/>
-      <c r="BT11" s="176"/>
-      <c r="BU11" s="176"/>
-      <c r="BV11" s="176"/>
-      <c r="BW11" s="176"/>
-      <c r="BX11" s="176"/>
-      <c r="BY11" s="176"/>
-      <c r="BZ11" s="176"/>
-      <c r="CA11" s="176"/>
-      <c r="CB11" s="176"/>
+      <c r="BR11" s="158"/>
+      <c r="BS11" s="158"/>
+      <c r="BT11" s="158"/>
+      <c r="BU11" s="158"/>
+      <c r="BV11" s="158"/>
+      <c r="BW11" s="158"/>
+      <c r="BX11" s="158"/>
+      <c r="BY11" s="158"/>
+      <c r="BZ11" s="158"/>
+      <c r="CA11" s="158"/>
+      <c r="CB11" s="158"/>
       <c r="CC11" s="23"/>
       <c r="CF11" s="22"/>
-      <c r="CG11" s="176"/>
-      <c r="CH11" s="176"/>
-      <c r="CI11" s="176"/>
-      <c r="CJ11" s="176"/>
-      <c r="CK11" s="176"/>
-      <c r="CL11" s="176"/>
-      <c r="CM11" s="176"/>
-      <c r="CN11" s="176"/>
-      <c r="CO11" s="176"/>
-      <c r="CP11" s="176"/>
-      <c r="CQ11" s="176"/>
+      <c r="CG11" s="158"/>
+      <c r="CH11" s="158"/>
+      <c r="CI11" s="158"/>
+      <c r="CJ11" s="158"/>
+      <c r="CK11" s="158"/>
+      <c r="CL11" s="158"/>
+      <c r="CM11" s="158"/>
+      <c r="CN11" s="158"/>
+      <c r="CO11" s="158"/>
+      <c r="CP11" s="158"/>
+      <c r="CQ11" s="158"/>
       <c r="CR11" s="23"/>
       <c r="CZ11" s="12" t="s">
         <v>155</v>
@@ -33417,101 +33417,101 @@
     </row>
     <row r="12" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="22"/>
-      <c r="D12" s="177" t="s">
+      <c r="D12" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="E12" s="177"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="177"/>
-      <c r="K12" s="177"/>
-      <c r="L12" s="177"/>
-      <c r="M12" s="177"/>
-      <c r="N12" s="177"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="159"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="159"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="159"/>
+      <c r="L12" s="159"/>
+      <c r="M12" s="159"/>
+      <c r="N12" s="159"/>
       <c r="O12" s="23"/>
       <c r="R12" s="22"/>
-      <c r="S12" s="177" t="s">
+      <c r="S12" s="159" t="s">
         <v>162</v>
       </c>
-      <c r="T12" s="177"/>
-      <c r="U12" s="177"/>
-      <c r="V12" s="177"/>
-      <c r="W12" s="177"/>
-      <c r="X12" s="177"/>
-      <c r="Y12" s="177"/>
-      <c r="Z12" s="177"/>
-      <c r="AB12" s="177" t="s">
+      <c r="T12" s="159"/>
+      <c r="U12" s="159"/>
+      <c r="V12" s="159"/>
+      <c r="W12" s="159"/>
+      <c r="X12" s="159"/>
+      <c r="Y12" s="159"/>
+      <c r="Z12" s="159"/>
+      <c r="AB12" s="159" t="s">
         <v>182</v>
       </c>
-      <c r="AC12" s="177"/>
-      <c r="AD12" s="177"/>
-      <c r="AE12" s="177"/>
-      <c r="AF12" s="177"/>
-      <c r="AG12" s="177"/>
-      <c r="AH12" s="177"/>
-      <c r="AI12" s="177"/>
+      <c r="AC12" s="159"/>
+      <c r="AD12" s="159"/>
+      <c r="AE12" s="159"/>
+      <c r="AF12" s="159"/>
+      <c r="AG12" s="159"/>
+      <c r="AH12" s="159"/>
+      <c r="AI12" s="159"/>
       <c r="AJ12" s="23"/>
       <c r="AM12" s="22"/>
-      <c r="AN12" s="177" t="s">
+      <c r="AN12" s="159" t="s">
         <v>183</v>
       </c>
-      <c r="AO12" s="177"/>
-      <c r="AP12" s="177"/>
-      <c r="AQ12" s="177"/>
-      <c r="AR12" s="177"/>
-      <c r="AS12" s="177"/>
-      <c r="AT12" s="177"/>
-      <c r="AU12" s="177"/>
-      <c r="AV12" s="177"/>
-      <c r="AW12" s="177"/>
-      <c r="AX12" s="177"/>
+      <c r="AO12" s="159"/>
+      <c r="AP12" s="159"/>
+      <c r="AQ12" s="159"/>
+      <c r="AR12" s="159"/>
+      <c r="AS12" s="159"/>
+      <c r="AT12" s="159"/>
+      <c r="AU12" s="159"/>
+      <c r="AV12" s="159"/>
+      <c r="AW12" s="159"/>
+      <c r="AX12" s="159"/>
       <c r="AY12" s="23"/>
       <c r="BB12" s="22"/>
-      <c r="BC12" s="177" t="s">
+      <c r="BC12" s="159" t="s">
         <v>184</v>
       </c>
-      <c r="BD12" s="177"/>
-      <c r="BE12" s="177"/>
-      <c r="BF12" s="177"/>
-      <c r="BG12" s="177"/>
-      <c r="BH12" s="177"/>
-      <c r="BI12" s="177"/>
-      <c r="BJ12" s="177"/>
-      <c r="BK12" s="177"/>
-      <c r="BL12" s="177"/>
-      <c r="BM12" s="177"/>
+      <c r="BD12" s="159"/>
+      <c r="BE12" s="159"/>
+      <c r="BF12" s="159"/>
+      <c r="BG12" s="159"/>
+      <c r="BH12" s="159"/>
+      <c r="BI12" s="159"/>
+      <c r="BJ12" s="159"/>
+      <c r="BK12" s="159"/>
+      <c r="BL12" s="159"/>
+      <c r="BM12" s="159"/>
       <c r="BN12" s="23"/>
       <c r="BQ12" s="22"/>
-      <c r="BR12" s="177" t="s">
+      <c r="BR12" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="BS12" s="177"/>
-      <c r="BT12" s="177"/>
-      <c r="BU12" s="177"/>
-      <c r="BV12" s="177"/>
-      <c r="BW12" s="177"/>
-      <c r="BX12" s="177"/>
-      <c r="BY12" s="177"/>
-      <c r="BZ12" s="177"/>
-      <c r="CA12" s="177"/>
-      <c r="CB12" s="177"/>
+      <c r="BS12" s="159"/>
+      <c r="BT12" s="159"/>
+      <c r="BU12" s="159"/>
+      <c r="BV12" s="159"/>
+      <c r="BW12" s="159"/>
+      <c r="BX12" s="159"/>
+      <c r="BY12" s="159"/>
+      <c r="BZ12" s="159"/>
+      <c r="CA12" s="159"/>
+      <c r="CB12" s="159"/>
       <c r="CC12" s="23"/>
       <c r="CF12" s="22"/>
-      <c r="CG12" s="177" t="s">
+      <c r="CG12" s="159" t="s">
         <v>186</v>
       </c>
-      <c r="CH12" s="177"/>
-      <c r="CI12" s="177"/>
-      <c r="CJ12" s="177"/>
-      <c r="CK12" s="177"/>
-      <c r="CL12" s="177"/>
-      <c r="CM12" s="177"/>
-      <c r="CN12" s="177"/>
-      <c r="CO12" s="177"/>
-      <c r="CP12" s="177"/>
-      <c r="CQ12" s="177"/>
+      <c r="CH12" s="159"/>
+      <c r="CI12" s="159"/>
+      <c r="CJ12" s="159"/>
+      <c r="CK12" s="159"/>
+      <c r="CL12" s="159"/>
+      <c r="CM12" s="159"/>
+      <c r="CN12" s="159"/>
+      <c r="CO12" s="159"/>
+      <c r="CP12" s="159"/>
+      <c r="CQ12" s="159"/>
       <c r="CR12" s="23"/>
       <c r="CZ12" s="9" t="s">
         <v>187</v>
@@ -33855,17 +33855,17 @@
       <c r="CI16" s="31"/>
       <c r="CJ16" s="31"/>
       <c r="CK16" s="31"/>
-      <c r="CL16" s="163" t="str">
+      <c r="CL16" s="160" t="str">
         <f>"Selected scenario: "&amp;$BH$4</f>
         <v>Selected scenario: Aggressive</v>
       </c>
-      <c r="CM16" s="163"/>
-      <c r="CN16" s="163"/>
-      <c r="CO16" s="163"/>
-      <c r="CP16" s="163"/>
-      <c r="CQ16" s="163"/>
-      <c r="CR16" s="163"/>
-      <c r="CS16" s="163"/>
+      <c r="CM16" s="160"/>
+      <c r="CN16" s="160"/>
+      <c r="CO16" s="160"/>
+      <c r="CP16" s="160"/>
+      <c r="CQ16" s="160"/>
+      <c r="CR16" s="160"/>
+      <c r="CS16" s="160"/>
       <c r="CZ16" s="10" t="s">
         <v>194</v>
       </c>
@@ -33935,14 +33935,14 @@
       <c r="CI17" s="29"/>
       <c r="CJ17" s="29"/>
       <c r="CK17" s="29"/>
-      <c r="CL17" s="163"/>
-      <c r="CM17" s="163"/>
-      <c r="CN17" s="163"/>
-      <c r="CO17" s="163"/>
-      <c r="CP17" s="163"/>
-      <c r="CQ17" s="163"/>
-      <c r="CR17" s="163"/>
-      <c r="CS17" s="163"/>
+      <c r="CL17" s="160"/>
+      <c r="CM17" s="160"/>
+      <c r="CN17" s="160"/>
+      <c r="CO17" s="160"/>
+      <c r="CP17" s="160"/>
+      <c r="CQ17" s="160"/>
+      <c r="CR17" s="160"/>
+      <c r="CS17" s="160"/>
       <c r="CZ17" s="12" t="s">
         <v>155</v>
       </c>
@@ -33959,99 +33959,99 @@
     </row>
     <row r="18" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="34"/>
-      <c r="D18" s="164" t="str">
+      <c r="D18" s="161" t="str">
         <f>"WHERE THE GROSS BENEFIT LANDS  ·  ₹"&amp;TEXT(DI6+DI7+DI8,"0.0")&amp;" Cr"</f>
         <v>WHERE THE GROSS BENEFIT LANDS  ·  ₹80.6 Cr</v>
       </c>
-      <c r="E18" s="164"/>
-      <c r="F18" s="164"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="164"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="164"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="164"/>
-      <c r="P18" s="164"/>
-      <c r="Q18" s="164"/>
-      <c r="R18" s="164"/>
-      <c r="S18" s="164"/>
-      <c r="T18" s="164"/>
-      <c r="U18" s="164"/>
-      <c r="V18" s="164"/>
-      <c r="W18" s="164"/>
-      <c r="X18" s="164"/>
-      <c r="Y18" s="164"/>
-      <c r="Z18" s="164"/>
-      <c r="AA18" s="164"/>
-      <c r="AB18" s="164"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="161"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="161"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="161"/>
+      <c r="M18" s="161"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="161"/>
+      <c r="P18" s="161"/>
+      <c r="Q18" s="161"/>
+      <c r="R18" s="161"/>
+      <c r="S18" s="161"/>
+      <c r="T18" s="161"/>
+      <c r="U18" s="161"/>
+      <c r="V18" s="161"/>
+      <c r="W18" s="161"/>
+      <c r="X18" s="161"/>
+      <c r="Y18" s="161"/>
+      <c r="Z18" s="161"/>
+      <c r="AA18" s="161"/>
+      <c r="AB18" s="161"/>
       <c r="AD18" s="35"/>
-      <c r="AG18" s="164" t="s">
+      <c r="AG18" s="161" t="s">
         <v>199</v>
       </c>
-      <c r="AH18" s="164"/>
-      <c r="AI18" s="164"/>
-      <c r="AJ18" s="164"/>
-      <c r="AK18" s="164"/>
-      <c r="AL18" s="164"/>
-      <c r="AM18" s="164"/>
-      <c r="AN18" s="164"/>
-      <c r="AO18" s="164"/>
-      <c r="AP18" s="164"/>
-      <c r="AQ18" s="164"/>
-      <c r="AR18" s="164"/>
-      <c r="AS18" s="164"/>
-      <c r="AT18" s="164"/>
-      <c r="AU18" s="164"/>
-      <c r="AV18" s="164"/>
-      <c r="AW18" s="164"/>
-      <c r="AX18" s="164"/>
-      <c r="AY18" s="164"/>
-      <c r="AZ18" s="164"/>
-      <c r="BA18" s="164"/>
-      <c r="BB18" s="164"/>
-      <c r="BC18" s="164"/>
-      <c r="BD18" s="164"/>
+      <c r="AH18" s="161"/>
+      <c r="AI18" s="161"/>
+      <c r="AJ18" s="161"/>
+      <c r="AK18" s="161"/>
+      <c r="AL18" s="161"/>
+      <c r="AM18" s="161"/>
+      <c r="AN18" s="161"/>
+      <c r="AO18" s="161"/>
+      <c r="AP18" s="161"/>
+      <c r="AQ18" s="161"/>
+      <c r="AR18" s="161"/>
+      <c r="AS18" s="161"/>
+      <c r="AT18" s="161"/>
+      <c r="AU18" s="161"/>
+      <c r="AV18" s="161"/>
+      <c r="AW18" s="161"/>
+      <c r="AX18" s="161"/>
+      <c r="AY18" s="161"/>
+      <c r="AZ18" s="161"/>
+      <c r="BA18" s="161"/>
+      <c r="BB18" s="161"/>
+      <c r="BC18" s="161"/>
+      <c r="BD18" s="161"/>
       <c r="BF18" s="35"/>
-      <c r="BI18" s="164" t="s">
+      <c r="BI18" s="161" t="s">
         <v>200</v>
       </c>
-      <c r="BJ18" s="164"/>
-      <c r="BK18" s="164"/>
-      <c r="BL18" s="164"/>
-      <c r="BM18" s="164"/>
-      <c r="BN18" s="164"/>
-      <c r="BO18" s="164"/>
-      <c r="BP18" s="164"/>
-      <c r="BQ18" s="164"/>
-      <c r="BR18" s="164"/>
-      <c r="BS18" s="164"/>
-      <c r="BT18" s="164"/>
-      <c r="BU18" s="164"/>
-      <c r="BV18" s="164"/>
-      <c r="BW18" s="164"/>
-      <c r="BX18" s="164"/>
-      <c r="BY18" s="164"/>
-      <c r="BZ18" s="164"/>
-      <c r="CA18" s="164"/>
-      <c r="CB18" s="164"/>
-      <c r="CC18" s="164"/>
-      <c r="CD18" s="164"/>
-      <c r="CE18" s="164"/>
-      <c r="CF18" s="164"/>
-      <c r="CG18" s="164"/>
-      <c r="CH18" s="164"/>
-      <c r="CI18" s="164"/>
-      <c r="CJ18" s="164"/>
-      <c r="CK18" s="164"/>
-      <c r="CL18" s="164"/>
-      <c r="CM18" s="164"/>
-      <c r="CN18" s="164"/>
-      <c r="CO18" s="164"/>
-      <c r="CP18" s="164"/>
-      <c r="CQ18" s="164"/>
+      <c r="BJ18" s="161"/>
+      <c r="BK18" s="161"/>
+      <c r="BL18" s="161"/>
+      <c r="BM18" s="161"/>
+      <c r="BN18" s="161"/>
+      <c r="BO18" s="161"/>
+      <c r="BP18" s="161"/>
+      <c r="BQ18" s="161"/>
+      <c r="BR18" s="161"/>
+      <c r="BS18" s="161"/>
+      <c r="BT18" s="161"/>
+      <c r="BU18" s="161"/>
+      <c r="BV18" s="161"/>
+      <c r="BW18" s="161"/>
+      <c r="BX18" s="161"/>
+      <c r="BY18" s="161"/>
+      <c r="BZ18" s="161"/>
+      <c r="CA18" s="161"/>
+      <c r="CB18" s="161"/>
+      <c r="CC18" s="161"/>
+      <c r="CD18" s="161"/>
+      <c r="CE18" s="161"/>
+      <c r="CF18" s="161"/>
+      <c r="CG18" s="161"/>
+      <c r="CH18" s="161"/>
+      <c r="CI18" s="161"/>
+      <c r="CJ18" s="161"/>
+      <c r="CK18" s="161"/>
+      <c r="CL18" s="161"/>
+      <c r="CM18" s="161"/>
+      <c r="CN18" s="161"/>
+      <c r="CO18" s="161"/>
+      <c r="CP18" s="161"/>
+      <c r="CQ18" s="161"/>
       <c r="CS18" s="36"/>
       <c r="CZ18" s="9" t="s">
         <v>201</v>
@@ -34176,32 +34176,32 @@
       <c r="Y20" s="29"/>
       <c r="Z20" s="29"/>
       <c r="AD20" s="35"/>
-      <c r="AH20" s="175" t="str">
+      <c r="AH20" s="162" t="str">
         <f>TEXT(DI12/100000,"0.0")&amp;" lakh claimant-days returned"</f>
         <v>19.4 lakh claimant-days returned</v>
       </c>
-      <c r="AI20" s="175"/>
-      <c r="AJ20" s="175"/>
-      <c r="AK20" s="175"/>
-      <c r="AL20" s="175"/>
-      <c r="AM20" s="175"/>
-      <c r="AN20" s="175"/>
-      <c r="AO20" s="175"/>
-      <c r="AP20" s="175"/>
-      <c r="AQ20" s="175"/>
-      <c r="AR20" s="175"/>
-      <c r="AS20" s="175"/>
-      <c r="AT20" s="175"/>
-      <c r="AU20" s="175"/>
-      <c r="AV20" s="175"/>
-      <c r="AW20" s="175"/>
-      <c r="AX20" s="175"/>
-      <c r="AY20" s="175"/>
-      <c r="AZ20" s="175"/>
-      <c r="BA20" s="175"/>
-      <c r="BB20" s="175"/>
-      <c r="BC20" s="175"/>
-      <c r="BD20" s="175"/>
+      <c r="AI20" s="162"/>
+      <c r="AJ20" s="162"/>
+      <c r="AK20" s="162"/>
+      <c r="AL20" s="162"/>
+      <c r="AM20" s="162"/>
+      <c r="AN20" s="162"/>
+      <c r="AO20" s="162"/>
+      <c r="AP20" s="162"/>
+      <c r="AQ20" s="162"/>
+      <c r="AR20" s="162"/>
+      <c r="AS20" s="162"/>
+      <c r="AT20" s="162"/>
+      <c r="AU20" s="162"/>
+      <c r="AV20" s="162"/>
+      <c r="AW20" s="162"/>
+      <c r="AX20" s="162"/>
+      <c r="AY20" s="162"/>
+      <c r="AZ20" s="162"/>
+      <c r="BA20" s="162"/>
+      <c r="BB20" s="162"/>
+      <c r="BC20" s="162"/>
+      <c r="BD20" s="162"/>
       <c r="BF20" s="35"/>
       <c r="BM20" s="29"/>
       <c r="BN20" s="29"/>
@@ -34268,29 +34268,29 @@
       <c r="Y21" s="29"/>
       <c r="Z21" s="29"/>
       <c r="AD21" s="35"/>
-      <c r="AH21" s="175"/>
-      <c r="AI21" s="175"/>
-      <c r="AJ21" s="175"/>
-      <c r="AK21" s="175"/>
-      <c r="AL21" s="175"/>
-      <c r="AM21" s="175"/>
-      <c r="AN21" s="175"/>
-      <c r="AO21" s="175"/>
-      <c r="AP21" s="175"/>
-      <c r="AQ21" s="175"/>
-      <c r="AR21" s="175"/>
-      <c r="AS21" s="175"/>
-      <c r="AT21" s="175"/>
-      <c r="AU21" s="175"/>
-      <c r="AV21" s="175"/>
-      <c r="AW21" s="175"/>
-      <c r="AX21" s="175"/>
-      <c r="AY21" s="175"/>
-      <c r="AZ21" s="175"/>
-      <c r="BA21" s="175"/>
-      <c r="BB21" s="175"/>
-      <c r="BC21" s="175"/>
-      <c r="BD21" s="175"/>
+      <c r="AH21" s="162"/>
+      <c r="AI21" s="162"/>
+      <c r="AJ21" s="162"/>
+      <c r="AK21" s="162"/>
+      <c r="AL21" s="162"/>
+      <c r="AM21" s="162"/>
+      <c r="AN21" s="162"/>
+      <c r="AO21" s="162"/>
+      <c r="AP21" s="162"/>
+      <c r="AQ21" s="162"/>
+      <c r="AR21" s="162"/>
+      <c r="AS21" s="162"/>
+      <c r="AT21" s="162"/>
+      <c r="AU21" s="162"/>
+      <c r="AV21" s="162"/>
+      <c r="AW21" s="162"/>
+      <c r="AX21" s="162"/>
+      <c r="AY21" s="162"/>
+      <c r="AZ21" s="162"/>
+      <c r="BA21" s="162"/>
+      <c r="BB21" s="162"/>
+      <c r="BC21" s="162"/>
+      <c r="BD21" s="162"/>
       <c r="BF21" s="35"/>
       <c r="BM21" s="29"/>
       <c r="BN21" s="29"/>
@@ -35245,32 +35245,32 @@
     <row r="34" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="34"/>
       <c r="D34" s="29"/>
-      <c r="E34" s="159" t="s">
+      <c r="E34" s="163" t="s">
         <v>235</v>
       </c>
-      <c r="F34" s="159"/>
-      <c r="G34" s="159"/>
-      <c r="H34" s="159"/>
-      <c r="I34" s="159"/>
-      <c r="J34" s="159"/>
-      <c r="K34" s="159"/>
-      <c r="L34" s="159"/>
-      <c r="M34" s="159"/>
-      <c r="N34" s="159"/>
-      <c r="O34" s="159"/>
-      <c r="P34" s="159"/>
-      <c r="Q34" s="159"/>
-      <c r="R34" s="159"/>
-      <c r="S34" s="159"/>
-      <c r="T34" s="159"/>
-      <c r="U34" s="159"/>
-      <c r="V34" s="159"/>
-      <c r="W34" s="159"/>
-      <c r="X34" s="159"/>
-      <c r="Y34" s="159"/>
-      <c r="Z34" s="159"/>
-      <c r="AA34" s="159"/>
-      <c r="AB34" s="159"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="163"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="163"/>
+      <c r="O34" s="163"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="163"/>
+      <c r="S34" s="163"/>
+      <c r="T34" s="163"/>
+      <c r="U34" s="163"/>
+      <c r="V34" s="163"/>
+      <c r="W34" s="163"/>
+      <c r="X34" s="163"/>
+      <c r="Y34" s="163"/>
+      <c r="Z34" s="163"/>
+      <c r="AA34" s="163"/>
+      <c r="AB34" s="163"/>
       <c r="AD34" s="35"/>
       <c r="AM34" s="29"/>
       <c r="AN34" s="29"/>
@@ -35287,43 +35287,43 @@
       <c r="BD34" s="29"/>
       <c r="BF34" s="35"/>
       <c r="BI34" s="29"/>
-      <c r="BJ34" s="159" t="str">
+      <c r="BJ34" s="163" t="str">
         <f>"At the "&amp;$BH$4&amp;" rollout, ClaimPulse releases "&amp;TEXT(DI22,"0")&amp;" FTE of claims-handling capacity and lets the same team clear "&amp;TEXT(DI23,"0.0")&amp;"x the claims it handles today."</f>
         <v>At the Aggressive rollout, ClaimPulse releases 293 FTE of claims-handling capacity and lets the same team clear 5.7x the claims it handles today.</v>
       </c>
-      <c r="BK34" s="159"/>
-      <c r="BL34" s="159"/>
-      <c r="BM34" s="159"/>
-      <c r="BN34" s="159"/>
-      <c r="BO34" s="159"/>
-      <c r="BP34" s="159"/>
-      <c r="BQ34" s="159"/>
-      <c r="BR34" s="159"/>
-      <c r="BS34" s="159"/>
-      <c r="BT34" s="159"/>
-      <c r="BU34" s="159"/>
-      <c r="BV34" s="159"/>
-      <c r="BW34" s="159"/>
-      <c r="BX34" s="159"/>
-      <c r="BY34" s="159"/>
-      <c r="BZ34" s="159"/>
-      <c r="CA34" s="159"/>
-      <c r="CB34" s="159"/>
-      <c r="CC34" s="159"/>
-      <c r="CD34" s="159"/>
-      <c r="CE34" s="159"/>
-      <c r="CF34" s="159"/>
-      <c r="CG34" s="159"/>
-      <c r="CH34" s="159"/>
-      <c r="CI34" s="159"/>
-      <c r="CJ34" s="159"/>
-      <c r="CK34" s="159"/>
-      <c r="CL34" s="159"/>
-      <c r="CM34" s="159"/>
-      <c r="CN34" s="159"/>
-      <c r="CO34" s="159"/>
-      <c r="CP34" s="159"/>
-      <c r="CQ34" s="159"/>
+      <c r="BK34" s="163"/>
+      <c r="BL34" s="163"/>
+      <c r="BM34" s="163"/>
+      <c r="BN34" s="163"/>
+      <c r="BO34" s="163"/>
+      <c r="BP34" s="163"/>
+      <c r="BQ34" s="163"/>
+      <c r="BR34" s="163"/>
+      <c r="BS34" s="163"/>
+      <c r="BT34" s="163"/>
+      <c r="BU34" s="163"/>
+      <c r="BV34" s="163"/>
+      <c r="BW34" s="163"/>
+      <c r="BX34" s="163"/>
+      <c r="BY34" s="163"/>
+      <c r="BZ34" s="163"/>
+      <c r="CA34" s="163"/>
+      <c r="CB34" s="163"/>
+      <c r="CC34" s="163"/>
+      <c r="CD34" s="163"/>
+      <c r="CE34" s="163"/>
+      <c r="CF34" s="163"/>
+      <c r="CG34" s="163"/>
+      <c r="CH34" s="163"/>
+      <c r="CI34" s="163"/>
+      <c r="CJ34" s="163"/>
+      <c r="CK34" s="163"/>
+      <c r="CL34" s="163"/>
+      <c r="CM34" s="163"/>
+      <c r="CN34" s="163"/>
+      <c r="CO34" s="163"/>
+      <c r="CP34" s="163"/>
+      <c r="CQ34" s="163"/>
       <c r="CS34" s="36"/>
       <c r="DB34" s="14" t="s">
         <v>224</v>
@@ -35343,30 +35343,30 @@
     <row r="35" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="34"/>
       <c r="D35" s="29"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="159"/>
-      <c r="G35" s="159"/>
-      <c r="H35" s="159"/>
-      <c r="I35" s="159"/>
-      <c r="J35" s="159"/>
-      <c r="K35" s="159"/>
-      <c r="L35" s="159"/>
-      <c r="M35" s="159"/>
-      <c r="N35" s="159"/>
-      <c r="O35" s="159"/>
-      <c r="P35" s="159"/>
-      <c r="Q35" s="159"/>
-      <c r="R35" s="159"/>
-      <c r="S35" s="159"/>
-      <c r="T35" s="159"/>
-      <c r="U35" s="159"/>
-      <c r="V35" s="159"/>
-      <c r="W35" s="159"/>
-      <c r="X35" s="159"/>
-      <c r="Y35" s="159"/>
-      <c r="Z35" s="159"/>
-      <c r="AA35" s="159"/>
-      <c r="AB35" s="159"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="163"/>
+      <c r="M35" s="163"/>
+      <c r="N35" s="163"/>
+      <c r="O35" s="163"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="163"/>
+      <c r="S35" s="163"/>
+      <c r="T35" s="163"/>
+      <c r="U35" s="163"/>
+      <c r="V35" s="163"/>
+      <c r="W35" s="163"/>
+      <c r="X35" s="163"/>
+      <c r="Y35" s="163"/>
+      <c r="Z35" s="163"/>
+      <c r="AA35" s="163"/>
+      <c r="AB35" s="163"/>
       <c r="AD35" s="35"/>
       <c r="AM35" s="29"/>
       <c r="AN35" s="29"/>
@@ -35386,40 +35386,40 @@
       <c r="BG35" s="39"/>
       <c r="BH35" s="39"/>
       <c r="BI35" s="39"/>
-      <c r="BJ35" s="159"/>
-      <c r="BK35" s="159"/>
-      <c r="BL35" s="159"/>
-      <c r="BM35" s="159"/>
-      <c r="BN35" s="159"/>
-      <c r="BO35" s="159"/>
-      <c r="BP35" s="159"/>
-      <c r="BQ35" s="159"/>
-      <c r="BR35" s="159"/>
-      <c r="BS35" s="159"/>
-      <c r="BT35" s="159"/>
-      <c r="BU35" s="159"/>
-      <c r="BV35" s="159"/>
-      <c r="BW35" s="159"/>
-      <c r="BX35" s="159"/>
-      <c r="BY35" s="159"/>
-      <c r="BZ35" s="159"/>
-      <c r="CA35" s="159"/>
-      <c r="CB35" s="159"/>
-      <c r="CC35" s="159"/>
-      <c r="CD35" s="159"/>
-      <c r="CE35" s="159"/>
-      <c r="CF35" s="159"/>
-      <c r="CG35" s="159"/>
-      <c r="CH35" s="159"/>
-      <c r="CI35" s="159"/>
-      <c r="CJ35" s="159"/>
-      <c r="CK35" s="159"/>
-      <c r="CL35" s="159"/>
-      <c r="CM35" s="159"/>
-      <c r="CN35" s="159"/>
-      <c r="CO35" s="159"/>
-      <c r="CP35" s="159"/>
-      <c r="CQ35" s="159"/>
+      <c r="BJ35" s="163"/>
+      <c r="BK35" s="163"/>
+      <c r="BL35" s="163"/>
+      <c r="BM35" s="163"/>
+      <c r="BN35" s="163"/>
+      <c r="BO35" s="163"/>
+      <c r="BP35" s="163"/>
+      <c r="BQ35" s="163"/>
+      <c r="BR35" s="163"/>
+      <c r="BS35" s="163"/>
+      <c r="BT35" s="163"/>
+      <c r="BU35" s="163"/>
+      <c r="BV35" s="163"/>
+      <c r="BW35" s="163"/>
+      <c r="BX35" s="163"/>
+      <c r="BY35" s="163"/>
+      <c r="BZ35" s="163"/>
+      <c r="CA35" s="163"/>
+      <c r="CB35" s="163"/>
+      <c r="CC35" s="163"/>
+      <c r="CD35" s="163"/>
+      <c r="CE35" s="163"/>
+      <c r="CF35" s="163"/>
+      <c r="CG35" s="163"/>
+      <c r="CH35" s="163"/>
+      <c r="CI35" s="163"/>
+      <c r="CJ35" s="163"/>
+      <c r="CK35" s="163"/>
+      <c r="CL35" s="163"/>
+      <c r="CM35" s="163"/>
+      <c r="CN35" s="163"/>
+      <c r="CO35" s="163"/>
+      <c r="CP35" s="163"/>
+      <c r="CQ35" s="163"/>
       <c r="CS35" s="36"/>
       <c r="DB35" s="14" t="s">
         <v>226</v>
@@ -35504,100 +35504,100 @@
       <c r="C37" s="34"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
-      <c r="F37" s="164" t="s">
+      <c r="F37" s="161" t="s">
         <v>239</v>
       </c>
-      <c r="G37" s="164"/>
-      <c r="H37" s="164"/>
-      <c r="I37" s="164"/>
-      <c r="J37" s="164"/>
-      <c r="K37" s="164"/>
-      <c r="L37" s="164"/>
-      <c r="M37" s="164"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="164"/>
-      <c r="P37" s="164"/>
-      <c r="Q37" s="164"/>
-      <c r="R37" s="164"/>
-      <c r="S37" s="164"/>
-      <c r="T37" s="164"/>
-      <c r="U37" s="164"/>
-      <c r="V37" s="164"/>
-      <c r="W37" s="164"/>
-      <c r="X37" s="164"/>
-      <c r="Y37" s="164"/>
-      <c r="Z37" s="164"/>
-      <c r="AA37" s="164"/>
-      <c r="AB37" s="164"/>
-      <c r="AC37" s="164"/>
-      <c r="AD37" s="164"/>
-      <c r="AE37" s="164"/>
-      <c r="AF37" s="164"/>
-      <c r="AG37" s="164"/>
-      <c r="AH37" s="164"/>
-      <c r="AI37" s="164"/>
-      <c r="AJ37" s="164"/>
-      <c r="AK37" s="164"/>
-      <c r="AL37" s="164"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="161"/>
+      <c r="P37" s="161"/>
+      <c r="Q37" s="161"/>
+      <c r="R37" s="161"/>
+      <c r="S37" s="161"/>
+      <c r="T37" s="161"/>
+      <c r="U37" s="161"/>
+      <c r="V37" s="161"/>
+      <c r="W37" s="161"/>
+      <c r="X37" s="161"/>
+      <c r="Y37" s="161"/>
+      <c r="Z37" s="161"/>
+      <c r="AA37" s="161"/>
+      <c r="AB37" s="161"/>
+      <c r="AC37" s="161"/>
+      <c r="AD37" s="161"/>
+      <c r="AE37" s="161"/>
+      <c r="AF37" s="161"/>
+      <c r="AG37" s="161"/>
+      <c r="AH37" s="161"/>
+      <c r="AI37" s="161"/>
+      <c r="AJ37" s="161"/>
+      <c r="AK37" s="161"/>
+      <c r="AL37" s="161"/>
       <c r="AM37" s="29"/>
       <c r="AN37" s="41"/>
       <c r="AO37" s="29"/>
       <c r="AP37" s="29"/>
-      <c r="AQ37" s="164" t="s">
+      <c r="AQ37" s="161" t="s">
         <v>240</v>
       </c>
-      <c r="AR37" s="164"/>
-      <c r="AS37" s="164"/>
-      <c r="AT37" s="164"/>
-      <c r="AU37" s="164"/>
-      <c r="AV37" s="164"/>
-      <c r="AW37" s="164"/>
-      <c r="AX37" s="164"/>
-      <c r="AY37" s="164"/>
-      <c r="AZ37" s="164"/>
-      <c r="BA37" s="164"/>
-      <c r="BB37" s="164"/>
-      <c r="BC37" s="164"/>
-      <c r="BD37" s="164"/>
-      <c r="BE37" s="164"/>
-      <c r="BF37" s="164"/>
-      <c r="BG37" s="164"/>
+      <c r="AR37" s="161"/>
+      <c r="AS37" s="161"/>
+      <c r="AT37" s="161"/>
+      <c r="AU37" s="161"/>
+      <c r="AV37" s="161"/>
+      <c r="AW37" s="161"/>
+      <c r="AX37" s="161"/>
+      <c r="AY37" s="161"/>
+      <c r="AZ37" s="161"/>
+      <c r="BA37" s="161"/>
+      <c r="BB37" s="161"/>
+      <c r="BC37" s="161"/>
+      <c r="BD37" s="161"/>
+      <c r="BE37" s="161"/>
+      <c r="BF37" s="161"/>
+      <c r="BG37" s="161"/>
       <c r="BI37" s="42"/>
-      <c r="BL37" s="164" t="str">
+      <c r="BL37" s="161" t="str">
         <f>"WHAT THE BUILD BUYS THE REGULATOR  ·  "&amp;TEXT(DI37,"0.0%")&amp;" OF THE BUILD"</f>
         <v>WHAT THE BUILD BUYS THE REGULATOR  ·  29.5% OF THE BUILD</v>
       </c>
-      <c r="BM37" s="164"/>
-      <c r="BN37" s="164"/>
-      <c r="BO37" s="164"/>
-      <c r="BP37" s="164"/>
-      <c r="BQ37" s="164"/>
-      <c r="BR37" s="164"/>
-      <c r="BS37" s="164"/>
-      <c r="BT37" s="164"/>
-      <c r="BU37" s="164"/>
-      <c r="BV37" s="164"/>
-      <c r="BW37" s="164"/>
-      <c r="BX37" s="164"/>
-      <c r="BY37" s="164"/>
-      <c r="BZ37" s="164"/>
-      <c r="CA37" s="164"/>
-      <c r="CB37" s="164"/>
-      <c r="CC37" s="164"/>
-      <c r="CD37" s="164"/>
-      <c r="CE37" s="164"/>
-      <c r="CF37" s="164"/>
-      <c r="CG37" s="164"/>
-      <c r="CH37" s="164"/>
-      <c r="CI37" s="164"/>
-      <c r="CJ37" s="164"/>
-      <c r="CK37" s="164"/>
-      <c r="CL37" s="164"/>
-      <c r="CM37" s="164"/>
-      <c r="CN37" s="164"/>
-      <c r="CO37" s="164"/>
-      <c r="CP37" s="164"/>
-      <c r="CQ37" s="164"/>
+      <c r="BM37" s="161"/>
+      <c r="BN37" s="161"/>
+      <c r="BO37" s="161"/>
+      <c r="BP37" s="161"/>
+      <c r="BQ37" s="161"/>
+      <c r="BR37" s="161"/>
+      <c r="BS37" s="161"/>
+      <c r="BT37" s="161"/>
+      <c r="BU37" s="161"/>
+      <c r="BV37" s="161"/>
+      <c r="BW37" s="161"/>
+      <c r="BX37" s="161"/>
+      <c r="BY37" s="161"/>
+      <c r="BZ37" s="161"/>
+      <c r="CA37" s="161"/>
+      <c r="CB37" s="161"/>
+      <c r="CC37" s="161"/>
+      <c r="CD37" s="161"/>
+      <c r="CE37" s="161"/>
+      <c r="CF37" s="161"/>
+      <c r="CG37" s="161"/>
+      <c r="CH37" s="161"/>
+      <c r="CI37" s="161"/>
+      <c r="CJ37" s="161"/>
+      <c r="CK37" s="161"/>
+      <c r="CL37" s="161"/>
+      <c r="CM37" s="161"/>
+      <c r="CN37" s="161"/>
+      <c r="CO37" s="161"/>
+      <c r="CP37" s="161"/>
+      <c r="CQ37" s="161"/>
       <c r="CS37" s="36"/>
       <c r="DH37" s="14" t="s">
         <v>241</v>
@@ -35662,45 +35662,45 @@
       <c r="C39" s="34"/>
       <c r="D39" s="29"/>
       <c r="E39" s="29"/>
-      <c r="F39" s="171" t="s">
+      <c r="F39" s="164" t="s">
         <v>242</v>
       </c>
-      <c r="G39" s="171"/>
-      <c r="H39" s="171"/>
-      <c r="I39" s="171"/>
-      <c r="J39" s="171"/>
-      <c r="K39" s="171"/>
-      <c r="L39" s="171"/>
-      <c r="M39" s="171"/>
-      <c r="N39" s="171"/>
-      <c r="O39" s="171"/>
-      <c r="P39" s="171"/>
-      <c r="Q39" s="171" t="s">
+      <c r="G39" s="164"/>
+      <c r="H39" s="164"/>
+      <c r="I39" s="164"/>
+      <c r="J39" s="164"/>
+      <c r="K39" s="164"/>
+      <c r="L39" s="164"/>
+      <c r="M39" s="164"/>
+      <c r="N39" s="164"/>
+      <c r="O39" s="164"/>
+      <c r="P39" s="164"/>
+      <c r="Q39" s="164" t="s">
         <v>243</v>
       </c>
-      <c r="R39" s="171"/>
-      <c r="S39" s="171"/>
-      <c r="T39" s="171"/>
-      <c r="U39" s="171"/>
-      <c r="V39" s="171"/>
-      <c r="W39" s="171"/>
-      <c r="X39" s="171"/>
-      <c r="Y39" s="171"/>
-      <c r="Z39" s="171"/>
-      <c r="AA39" s="171"/>
-      <c r="AB39" s="172" t="s">
+      <c r="R39" s="164"/>
+      <c r="S39" s="164"/>
+      <c r="T39" s="164"/>
+      <c r="U39" s="164"/>
+      <c r="V39" s="164"/>
+      <c r="W39" s="164"/>
+      <c r="X39" s="164"/>
+      <c r="Y39" s="164"/>
+      <c r="Z39" s="164"/>
+      <c r="AA39" s="164"/>
+      <c r="AB39" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="AC39" s="172"/>
-      <c r="AD39" s="172"/>
-      <c r="AE39" s="172"/>
-      <c r="AF39" s="172"/>
-      <c r="AG39" s="172"/>
-      <c r="AH39" s="172"/>
-      <c r="AI39" s="172"/>
-      <c r="AJ39" s="172"/>
-      <c r="AK39" s="172"/>
-      <c r="AL39" s="172"/>
+      <c r="AC39" s="165"/>
+      <c r="AD39" s="165"/>
+      <c r="AE39" s="165"/>
+      <c r="AF39" s="165"/>
+      <c r="AG39" s="165"/>
+      <c r="AH39" s="165"/>
+      <c r="AI39" s="165"/>
+      <c r="AJ39" s="165"/>
+      <c r="AK39" s="165"/>
+      <c r="AL39" s="165"/>
       <c r="AM39" s="29"/>
       <c r="AN39" s="41"/>
       <c r="AO39" s="29"/>
@@ -35739,39 +35739,39 @@
       <c r="C40" s="34"/>
       <c r="D40" s="29"/>
       <c r="E40" s="29"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="171"/>
-      <c r="I40" s="171"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="171"/>
-      <c r="L40" s="171"/>
-      <c r="M40" s="171"/>
-      <c r="N40" s="171"/>
-      <c r="O40" s="171"/>
-      <c r="P40" s="171"/>
-      <c r="Q40" s="171"/>
-      <c r="R40" s="171"/>
-      <c r="S40" s="171"/>
-      <c r="T40" s="171"/>
-      <c r="U40" s="171"/>
-      <c r="V40" s="171"/>
-      <c r="W40" s="171"/>
-      <c r="X40" s="171"/>
-      <c r="Y40" s="171"/>
-      <c r="Z40" s="171"/>
-      <c r="AA40" s="171"/>
-      <c r="AB40" s="172"/>
-      <c r="AC40" s="172"/>
-      <c r="AD40" s="172"/>
-      <c r="AE40" s="172"/>
-      <c r="AF40" s="172"/>
-      <c r="AG40" s="172"/>
-      <c r="AH40" s="172"/>
-      <c r="AI40" s="172"/>
-      <c r="AJ40" s="172"/>
-      <c r="AK40" s="172"/>
-      <c r="AL40" s="172"/>
+      <c r="F40" s="164"/>
+      <c r="G40" s="164"/>
+      <c r="H40" s="164"/>
+      <c r="I40" s="164"/>
+      <c r="J40" s="164"/>
+      <c r="K40" s="164"/>
+      <c r="L40" s="164"/>
+      <c r="M40" s="164"/>
+      <c r="N40" s="164"/>
+      <c r="O40" s="164"/>
+      <c r="P40" s="164"/>
+      <c r="Q40" s="164"/>
+      <c r="R40" s="164"/>
+      <c r="S40" s="164"/>
+      <c r="T40" s="164"/>
+      <c r="U40" s="164"/>
+      <c r="V40" s="164"/>
+      <c r="W40" s="164"/>
+      <c r="X40" s="164"/>
+      <c r="Y40" s="164"/>
+      <c r="Z40" s="164"/>
+      <c r="AA40" s="164"/>
+      <c r="AB40" s="165"/>
+      <c r="AC40" s="165"/>
+      <c r="AD40" s="165"/>
+      <c r="AE40" s="165"/>
+      <c r="AF40" s="165"/>
+      <c r="AG40" s="165"/>
+      <c r="AH40" s="165"/>
+      <c r="AI40" s="165"/>
+      <c r="AJ40" s="165"/>
+      <c r="AK40" s="165"/>
+      <c r="AL40" s="165"/>
       <c r="AM40" s="29"/>
       <c r="AN40" s="41"/>
       <c r="AO40" s="29"/>
@@ -35849,20 +35849,20 @@
       <c r="Y41" s="166"/>
       <c r="Z41" s="166"/>
       <c r="AA41" s="166"/>
-      <c r="AB41" s="173">
+      <c r="AB41" s="167">
         <f>DI12</f>
         <v>1944839.3920119114</v>
       </c>
-      <c r="AC41" s="173"/>
-      <c r="AD41" s="173"/>
-      <c r="AE41" s="173"/>
-      <c r="AF41" s="173"/>
-      <c r="AG41" s="173"/>
-      <c r="AH41" s="173"/>
-      <c r="AI41" s="173"/>
-      <c r="AJ41" s="173"/>
-      <c r="AK41" s="173"/>
-      <c r="AL41" s="173"/>
+      <c r="AC41" s="167"/>
+      <c r="AD41" s="167"/>
+      <c r="AE41" s="167"/>
+      <c r="AF41" s="167"/>
+      <c r="AG41" s="167"/>
+      <c r="AH41" s="167"/>
+      <c r="AI41" s="167"/>
+      <c r="AJ41" s="167"/>
+      <c r="AK41" s="167"/>
+      <c r="AL41" s="167"/>
       <c r="AM41" s="29"/>
       <c r="AN41" s="41"/>
       <c r="AO41" s="29"/>
@@ -35938,17 +35938,17 @@
       <c r="Y42" s="166"/>
       <c r="Z42" s="166"/>
       <c r="AA42" s="166"/>
-      <c r="AB42" s="173"/>
-      <c r="AC42" s="173"/>
-      <c r="AD42" s="173"/>
-      <c r="AE42" s="173"/>
-      <c r="AF42" s="173"/>
-      <c r="AG42" s="173"/>
-      <c r="AH42" s="173"/>
-      <c r="AI42" s="173"/>
-      <c r="AJ42" s="173"/>
-      <c r="AK42" s="173"/>
-      <c r="AL42" s="173"/>
+      <c r="AB42" s="167"/>
+      <c r="AC42" s="167"/>
+      <c r="AD42" s="167"/>
+      <c r="AE42" s="167"/>
+      <c r="AF42" s="167"/>
+      <c r="AG42" s="167"/>
+      <c r="AH42" s="167"/>
+      <c r="AI42" s="167"/>
+      <c r="AJ42" s="167"/>
+      <c r="AK42" s="167"/>
+      <c r="AL42" s="167"/>
       <c r="AM42" s="29"/>
       <c r="AN42" s="41"/>
       <c r="AO42" s="29"/>
@@ -36028,20 +36028,20 @@
       <c r="Y43" s="166"/>
       <c r="Z43" s="166"/>
       <c r="AA43" s="166"/>
-      <c r="AB43" s="174">
+      <c r="AB43" s="168">
         <f>DI22</f>
         <v>293.10252551608232</v>
       </c>
-      <c r="AC43" s="174"/>
-      <c r="AD43" s="174"/>
-      <c r="AE43" s="174"/>
-      <c r="AF43" s="174"/>
-      <c r="AG43" s="174"/>
-      <c r="AH43" s="174"/>
-      <c r="AI43" s="174"/>
-      <c r="AJ43" s="174"/>
-      <c r="AK43" s="174"/>
-      <c r="AL43" s="174"/>
+      <c r="AC43" s="168"/>
+      <c r="AD43" s="168"/>
+      <c r="AE43" s="168"/>
+      <c r="AF43" s="168"/>
+      <c r="AG43" s="168"/>
+      <c r="AH43" s="168"/>
+      <c r="AI43" s="168"/>
+      <c r="AJ43" s="168"/>
+      <c r="AK43" s="168"/>
+      <c r="AL43" s="168"/>
       <c r="AM43" s="29"/>
       <c r="AN43" s="41"/>
       <c r="AO43" s="29"/>
@@ -36117,17 +36117,17 @@
       <c r="Y44" s="166"/>
       <c r="Z44" s="166"/>
       <c r="AA44" s="166"/>
-      <c r="AB44" s="174"/>
-      <c r="AC44" s="174"/>
-      <c r="AD44" s="174"/>
-      <c r="AE44" s="174"/>
-      <c r="AF44" s="174"/>
-      <c r="AG44" s="174"/>
-      <c r="AH44" s="174"/>
-      <c r="AI44" s="174"/>
-      <c r="AJ44" s="174"/>
-      <c r="AK44" s="174"/>
-      <c r="AL44" s="174"/>
+      <c r="AB44" s="168"/>
+      <c r="AC44" s="168"/>
+      <c r="AD44" s="168"/>
+      <c r="AE44" s="168"/>
+      <c r="AF44" s="168"/>
+      <c r="AG44" s="168"/>
+      <c r="AH44" s="168"/>
+      <c r="AI44" s="168"/>
+      <c r="AJ44" s="168"/>
+      <c r="AK44" s="168"/>
+      <c r="AL44" s="168"/>
       <c r="AM44" s="29"/>
       <c r="AN44" s="41"/>
       <c r="AO44" s="29"/>
@@ -36207,20 +36207,20 @@
       <c r="Y45" s="166"/>
       <c r="Z45" s="166"/>
       <c r="AA45" s="166"/>
-      <c r="AB45" s="170">
+      <c r="AB45" s="169">
         <f>DE22</f>
         <v>4.491377252428979</v>
       </c>
-      <c r="AC45" s="170"/>
-      <c r="AD45" s="170"/>
-      <c r="AE45" s="170"/>
-      <c r="AF45" s="170"/>
-      <c r="AG45" s="170"/>
-      <c r="AH45" s="170"/>
-      <c r="AI45" s="170"/>
-      <c r="AJ45" s="170"/>
-      <c r="AK45" s="170"/>
-      <c r="AL45" s="170"/>
+      <c r="AC45" s="169"/>
+      <c r="AD45" s="169"/>
+      <c r="AE45" s="169"/>
+      <c r="AF45" s="169"/>
+      <c r="AG45" s="169"/>
+      <c r="AH45" s="169"/>
+      <c r="AI45" s="169"/>
+      <c r="AJ45" s="169"/>
+      <c r="AK45" s="169"/>
+      <c r="AL45" s="169"/>
       <c r="AM45" s="29"/>
       <c r="AN45" s="41"/>
       <c r="AO45" s="29"/>
@@ -36289,17 +36289,17 @@
       <c r="Y46" s="166"/>
       <c r="Z46" s="166"/>
       <c r="AA46" s="166"/>
-      <c r="AB46" s="170"/>
-      <c r="AC46" s="170"/>
-      <c r="AD46" s="170"/>
-      <c r="AE46" s="170"/>
-      <c r="AF46" s="170"/>
-      <c r="AG46" s="170"/>
-      <c r="AH46" s="170"/>
-      <c r="AI46" s="170"/>
-      <c r="AJ46" s="170"/>
-      <c r="AK46" s="170"/>
-      <c r="AL46" s="170"/>
+      <c r="AB46" s="169"/>
+      <c r="AC46" s="169"/>
+      <c r="AD46" s="169"/>
+      <c r="AE46" s="169"/>
+      <c r="AF46" s="169"/>
+      <c r="AG46" s="169"/>
+      <c r="AH46" s="169"/>
+      <c r="AI46" s="169"/>
+      <c r="AJ46" s="169"/>
+      <c r="AK46" s="169"/>
+      <c r="AL46" s="169"/>
       <c r="AM46" s="29"/>
       <c r="AN46" s="41"/>
       <c r="AO46" s="29"/>
@@ -36375,20 +36375,20 @@
       <c r="Y47" s="166"/>
       <c r="Z47" s="166"/>
       <c r="AA47" s="166"/>
-      <c r="AB47" s="169">
+      <c r="AB47" s="170">
         <f>DI8</f>
         <v>0.96007586347555574</v>
       </c>
-      <c r="AC47" s="169"/>
-      <c r="AD47" s="169"/>
-      <c r="AE47" s="169"/>
-      <c r="AF47" s="169"/>
-      <c r="AG47" s="169"/>
-      <c r="AH47" s="169"/>
-      <c r="AI47" s="169"/>
-      <c r="AJ47" s="169"/>
-      <c r="AK47" s="169"/>
-      <c r="AL47" s="169"/>
+      <c r="AC47" s="170"/>
+      <c r="AD47" s="170"/>
+      <c r="AE47" s="170"/>
+      <c r="AF47" s="170"/>
+      <c r="AG47" s="170"/>
+      <c r="AH47" s="170"/>
+      <c r="AI47" s="170"/>
+      <c r="AJ47" s="170"/>
+      <c r="AK47" s="170"/>
+      <c r="AL47" s="170"/>
       <c r="AM47" s="29"/>
       <c r="AN47" s="41"/>
       <c r="AO47" s="29"/>
@@ -36463,17 +36463,17 @@
       <c r="Y48" s="166"/>
       <c r="Z48" s="166"/>
       <c r="AA48" s="166"/>
-      <c r="AB48" s="169"/>
-      <c r="AC48" s="169"/>
-      <c r="AD48" s="169"/>
-      <c r="AE48" s="169"/>
-      <c r="AF48" s="169"/>
-      <c r="AG48" s="169"/>
-      <c r="AH48" s="169"/>
-      <c r="AI48" s="169"/>
-      <c r="AJ48" s="169"/>
-      <c r="AK48" s="169"/>
-      <c r="AL48" s="169"/>
+      <c r="AB48" s="170"/>
+      <c r="AC48" s="170"/>
+      <c r="AD48" s="170"/>
+      <c r="AE48" s="170"/>
+      <c r="AF48" s="170"/>
+      <c r="AG48" s="170"/>
+      <c r="AH48" s="170"/>
+      <c r="AI48" s="170"/>
+      <c r="AJ48" s="170"/>
+      <c r="AK48" s="170"/>
+      <c r="AL48" s="170"/>
       <c r="AM48" s="29"/>
       <c r="AN48" s="41"/>
       <c r="AO48" s="29"/>
@@ -36553,20 +36553,20 @@
       <c r="Y49" s="166"/>
       <c r="Z49" s="166"/>
       <c r="AA49" s="166"/>
-      <c r="AB49" s="169">
+      <c r="AB49" s="170">
         <f>DI44</f>
         <v>75.277513711775029</v>
       </c>
-      <c r="AC49" s="169"/>
-      <c r="AD49" s="169"/>
-      <c r="AE49" s="169"/>
-      <c r="AF49" s="169"/>
-      <c r="AG49" s="169"/>
-      <c r="AH49" s="169"/>
-      <c r="AI49" s="169"/>
-      <c r="AJ49" s="169"/>
-      <c r="AK49" s="169"/>
-      <c r="AL49" s="169"/>
+      <c r="AC49" s="170"/>
+      <c r="AD49" s="170"/>
+      <c r="AE49" s="170"/>
+      <c r="AF49" s="170"/>
+      <c r="AG49" s="170"/>
+      <c r="AH49" s="170"/>
+      <c r="AI49" s="170"/>
+      <c r="AJ49" s="170"/>
+      <c r="AK49" s="170"/>
+      <c r="AL49" s="170"/>
       <c r="AM49" s="29"/>
       <c r="AN49" s="41"/>
       <c r="AO49" s="29"/>
@@ -36642,17 +36642,17 @@
       <c r="Y50" s="166"/>
       <c r="Z50" s="166"/>
       <c r="AA50" s="166"/>
-      <c r="AB50" s="169"/>
-      <c r="AC50" s="169"/>
-      <c r="AD50" s="169"/>
-      <c r="AE50" s="169"/>
-      <c r="AF50" s="169"/>
-      <c r="AG50" s="169"/>
-      <c r="AH50" s="169"/>
-      <c r="AI50" s="169"/>
-      <c r="AJ50" s="169"/>
-      <c r="AK50" s="169"/>
-      <c r="AL50" s="169"/>
+      <c r="AB50" s="170"/>
+      <c r="AC50" s="170"/>
+      <c r="AD50" s="170"/>
+      <c r="AE50" s="170"/>
+      <c r="AF50" s="170"/>
+      <c r="AG50" s="170"/>
+      <c r="AH50" s="170"/>
+      <c r="AI50" s="170"/>
+      <c r="AJ50" s="170"/>
+      <c r="AK50" s="170"/>
+      <c r="AL50" s="170"/>
       <c r="AM50" s="29"/>
       <c r="AN50" s="41"/>
       <c r="AO50" s="29"/>
@@ -36732,20 +36732,20 @@
       <c r="Y51" s="166"/>
       <c r="Z51" s="166"/>
       <c r="AA51" s="166"/>
-      <c r="AB51" s="167">
+      <c r="AB51" s="171">
         <f>DI29</f>
         <v>123438.32530400004</v>
       </c>
-      <c r="AC51" s="167"/>
-      <c r="AD51" s="167"/>
-      <c r="AE51" s="167"/>
-      <c r="AF51" s="167"/>
-      <c r="AG51" s="167"/>
-      <c r="AH51" s="167"/>
-      <c r="AI51" s="167"/>
-      <c r="AJ51" s="167"/>
-      <c r="AK51" s="167"/>
-      <c r="AL51" s="167"/>
+      <c r="AC51" s="171"/>
+      <c r="AD51" s="171"/>
+      <c r="AE51" s="171"/>
+      <c r="AF51" s="171"/>
+      <c r="AG51" s="171"/>
+      <c r="AH51" s="171"/>
+      <c r="AI51" s="171"/>
+      <c r="AJ51" s="171"/>
+      <c r="AK51" s="171"/>
+      <c r="AL51" s="171"/>
       <c r="AM51" s="29"/>
       <c r="AN51" s="41"/>
       <c r="AO51" s="29"/>
@@ -36814,17 +36814,17 @@
       <c r="Y52" s="166"/>
       <c r="Z52" s="166"/>
       <c r="AA52" s="166"/>
-      <c r="AB52" s="167"/>
-      <c r="AC52" s="167"/>
-      <c r="AD52" s="167"/>
-      <c r="AE52" s="167"/>
-      <c r="AF52" s="167"/>
-      <c r="AG52" s="167"/>
-      <c r="AH52" s="167"/>
-      <c r="AI52" s="167"/>
-      <c r="AJ52" s="167"/>
-      <c r="AK52" s="167"/>
-      <c r="AL52" s="167"/>
+      <c r="AB52" s="171"/>
+      <c r="AC52" s="171"/>
+      <c r="AD52" s="171"/>
+      <c r="AE52" s="171"/>
+      <c r="AF52" s="171"/>
+      <c r="AG52" s="171"/>
+      <c r="AH52" s="171"/>
+      <c r="AI52" s="171"/>
+      <c r="AJ52" s="171"/>
+      <c r="AK52" s="171"/>
+      <c r="AL52" s="171"/>
       <c r="AM52" s="29"/>
       <c r="AN52" s="41"/>
       <c r="AO52" s="29"/>
@@ -36900,20 +36900,20 @@
       <c r="Y53" s="166"/>
       <c r="Z53" s="166"/>
       <c r="AA53" s="166"/>
-      <c r="AB53" s="168">
+      <c r="AB53" s="172">
         <f>INDEX('3. Workings'!$D$118:$F$118,MATCH($BH$4,'3. Workings'!$D$100:$F$100,0))</f>
         <v>3</v>
       </c>
-      <c r="AC53" s="168"/>
-      <c r="AD53" s="168"/>
-      <c r="AE53" s="168"/>
-      <c r="AF53" s="168"/>
-      <c r="AG53" s="168"/>
-      <c r="AH53" s="168"/>
-      <c r="AI53" s="168"/>
-      <c r="AJ53" s="168"/>
-      <c r="AK53" s="168"/>
-      <c r="AL53" s="168"/>
+      <c r="AC53" s="172"/>
+      <c r="AD53" s="172"/>
+      <c r="AE53" s="172"/>
+      <c r="AF53" s="172"/>
+      <c r="AG53" s="172"/>
+      <c r="AH53" s="172"/>
+      <c r="AI53" s="172"/>
+      <c r="AJ53" s="172"/>
+      <c r="AK53" s="172"/>
+      <c r="AL53" s="172"/>
       <c r="AM53" s="29"/>
       <c r="AN53" s="41"/>
       <c r="AO53" s="29"/>
@@ -36988,17 +36988,17 @@
       <c r="Y54" s="166"/>
       <c r="Z54" s="166"/>
       <c r="AA54" s="166"/>
-      <c r="AB54" s="168"/>
-      <c r="AC54" s="168"/>
-      <c r="AD54" s="168"/>
-      <c r="AE54" s="168"/>
-      <c r="AF54" s="168"/>
-      <c r="AG54" s="168"/>
-      <c r="AH54" s="168"/>
-      <c r="AI54" s="168"/>
-      <c r="AJ54" s="168"/>
-      <c r="AK54" s="168"/>
-      <c r="AL54" s="168"/>
+      <c r="AB54" s="172"/>
+      <c r="AC54" s="172"/>
+      <c r="AD54" s="172"/>
+      <c r="AE54" s="172"/>
+      <c r="AF54" s="172"/>
+      <c r="AG54" s="172"/>
+      <c r="AH54" s="172"/>
+      <c r="AI54" s="172"/>
+      <c r="AJ54" s="172"/>
+      <c r="AK54" s="172"/>
+      <c r="AL54" s="172"/>
       <c r="AM54" s="29"/>
       <c r="AN54" s="41"/>
       <c r="AO54" s="29"/>
@@ -37078,20 +37078,20 @@
       <c r="Y55" s="166"/>
       <c r="Z55" s="166"/>
       <c r="AA55" s="166"/>
-      <c r="AB55" s="169">
+      <c r="AB55" s="170">
         <f>DI34</f>
         <v>1.0013452</v>
       </c>
-      <c r="AC55" s="169"/>
-      <c r="AD55" s="169"/>
-      <c r="AE55" s="169"/>
-      <c r="AF55" s="169"/>
-      <c r="AG55" s="169"/>
-      <c r="AH55" s="169"/>
-      <c r="AI55" s="169"/>
-      <c r="AJ55" s="169"/>
-      <c r="AK55" s="169"/>
-      <c r="AL55" s="169"/>
+      <c r="AC55" s="170"/>
+      <c r="AD55" s="170"/>
+      <c r="AE55" s="170"/>
+      <c r="AF55" s="170"/>
+      <c r="AG55" s="170"/>
+      <c r="AH55" s="170"/>
+      <c r="AI55" s="170"/>
+      <c r="AJ55" s="170"/>
+      <c r="AK55" s="170"/>
+      <c r="AL55" s="170"/>
       <c r="AM55" s="29"/>
       <c r="AN55" s="41"/>
       <c r="AO55" s="29"/>
@@ -37167,17 +37167,17 @@
       <c r="Y56" s="166"/>
       <c r="Z56" s="166"/>
       <c r="AA56" s="166"/>
-      <c r="AB56" s="169"/>
-      <c r="AC56" s="169"/>
-      <c r="AD56" s="169"/>
-      <c r="AE56" s="169"/>
-      <c r="AF56" s="169"/>
-      <c r="AG56" s="169"/>
-      <c r="AH56" s="169"/>
-      <c r="AI56" s="169"/>
-      <c r="AJ56" s="169"/>
-      <c r="AK56" s="169"/>
-      <c r="AL56" s="169"/>
+      <c r="AB56" s="170"/>
+      <c r="AC56" s="170"/>
+      <c r="AD56" s="170"/>
+      <c r="AE56" s="170"/>
+      <c r="AF56" s="170"/>
+      <c r="AG56" s="170"/>
+      <c r="AH56" s="170"/>
+      <c r="AI56" s="170"/>
+      <c r="AJ56" s="170"/>
+      <c r="AK56" s="170"/>
+      <c r="AL56" s="170"/>
       <c r="AM56" s="29"/>
       <c r="AN56" s="41"/>
       <c r="AO56" s="29"/>
@@ -37451,17 +37451,17 @@
       <c r="AR61" s="32"/>
       <c r="AS61" s="32"/>
       <c r="AT61" s="32"/>
-      <c r="AU61" s="163" t="str">
+      <c r="AU61" s="160" t="str">
         <f>"Selected scenario: "&amp;$BH$4</f>
         <v>Selected scenario: Aggressive</v>
       </c>
-      <c r="AV61" s="163"/>
-      <c r="AW61" s="163"/>
-      <c r="AX61" s="163"/>
-      <c r="AY61" s="163"/>
-      <c r="AZ61" s="163"/>
-      <c r="BA61" s="163"/>
-      <c r="BB61" s="163"/>
+      <c r="AV61" s="160"/>
+      <c r="AW61" s="160"/>
+      <c r="AX61" s="160"/>
+      <c r="AY61" s="160"/>
+      <c r="AZ61" s="160"/>
+      <c r="BA61" s="160"/>
+      <c r="BB61" s="160"/>
       <c r="BD61" s="47"/>
       <c r="BE61" s="32"/>
       <c r="BF61" s="32"/>
@@ -37496,17 +37496,17 @@
       <c r="CI61" s="32"/>
       <c r="CJ61" s="32"/>
       <c r="CK61" s="32"/>
-      <c r="CL61" s="163" t="str">
+      <c r="CL61" s="160" t="str">
         <f>"Selected scenario: "&amp;$BH$4</f>
         <v>Selected scenario: Aggressive</v>
       </c>
-      <c r="CM61" s="163"/>
-      <c r="CN61" s="163"/>
-      <c r="CO61" s="163"/>
-      <c r="CP61" s="163"/>
-      <c r="CQ61" s="163"/>
-      <c r="CR61" s="163"/>
-      <c r="CS61" s="163"/>
+      <c r="CM61" s="160"/>
+      <c r="CN61" s="160"/>
+      <c r="CO61" s="160"/>
+      <c r="CP61" s="160"/>
+      <c r="CQ61" s="160"/>
+      <c r="CR61" s="160"/>
+      <c r="CS61" s="160"/>
       <c r="DH61" s="14" t="s">
         <v>272</v>
       </c>
@@ -37517,123 +37517,123 @@
     </row>
     <row r="62" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="48"/>
-      <c r="AU62" s="163"/>
-      <c r="AV62" s="163"/>
-      <c r="AW62" s="163"/>
-      <c r="AX62" s="163"/>
-      <c r="AY62" s="163"/>
-      <c r="AZ62" s="163"/>
-      <c r="BA62" s="163"/>
-      <c r="BB62" s="163"/>
+      <c r="AU62" s="160"/>
+      <c r="AV62" s="160"/>
+      <c r="AW62" s="160"/>
+      <c r="AX62" s="160"/>
+      <c r="AY62" s="160"/>
+      <c r="AZ62" s="160"/>
+      <c r="BA62" s="160"/>
+      <c r="BB62" s="160"/>
       <c r="BD62" s="48"/>
-      <c r="CL62" s="163"/>
-      <c r="CM62" s="163"/>
-      <c r="CN62" s="163"/>
-      <c r="CO62" s="163"/>
-      <c r="CP62" s="163"/>
-      <c r="CQ62" s="163"/>
-      <c r="CR62" s="163"/>
-      <c r="CS62" s="163"/>
+      <c r="CL62" s="160"/>
+      <c r="CM62" s="160"/>
+      <c r="CN62" s="160"/>
+      <c r="CO62" s="160"/>
+      <c r="CP62" s="160"/>
+      <c r="CQ62" s="160"/>
+      <c r="CR62" s="160"/>
+      <c r="CS62" s="160"/>
     </row>
     <row r="63" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="48"/>
-      <c r="D63" s="164" t="s">
+      <c r="D63" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="E63" s="164"/>
-      <c r="F63" s="164"/>
-      <c r="G63" s="164"/>
-      <c r="H63" s="164"/>
-      <c r="I63" s="164"/>
-      <c r="J63" s="164"/>
-      <c r="K63" s="164"/>
-      <c r="L63" s="164"/>
-      <c r="M63" s="164"/>
-      <c r="N63" s="164"/>
-      <c r="O63" s="164"/>
-      <c r="P63" s="164"/>
-      <c r="Q63" s="164"/>
-      <c r="R63" s="164"/>
+      <c r="E63" s="161"/>
+      <c r="F63" s="161"/>
+      <c r="G63" s="161"/>
+      <c r="H63" s="161"/>
+      <c r="I63" s="161"/>
+      <c r="J63" s="161"/>
+      <c r="K63" s="161"/>
+      <c r="L63" s="161"/>
+      <c r="M63" s="161"/>
+      <c r="N63" s="161"/>
+      <c r="O63" s="161"/>
+      <c r="P63" s="161"/>
+      <c r="Q63" s="161"/>
+      <c r="R63" s="161"/>
       <c r="S63" s="35"/>
-      <c r="U63" s="164" t="s">
+      <c r="U63" s="161" t="s">
         <v>274</v>
       </c>
-      <c r="V63" s="164"/>
-      <c r="W63" s="164"/>
-      <c r="X63" s="164"/>
-      <c r="Y63" s="164"/>
-      <c r="Z63" s="164"/>
-      <c r="AA63" s="164"/>
-      <c r="AB63" s="164"/>
-      <c r="AC63" s="164"/>
-      <c r="AD63" s="164"/>
-      <c r="AE63" s="164"/>
-      <c r="AF63" s="164"/>
-      <c r="AG63" s="164"/>
-      <c r="AH63" s="164"/>
-      <c r="AI63" s="164"/>
+      <c r="V63" s="161"/>
+      <c r="W63" s="161"/>
+      <c r="X63" s="161"/>
+      <c r="Y63" s="161"/>
+      <c r="Z63" s="161"/>
+      <c r="AA63" s="161"/>
+      <c r="AB63" s="161"/>
+      <c r="AC63" s="161"/>
+      <c r="AD63" s="161"/>
+      <c r="AE63" s="161"/>
+      <c r="AF63" s="161"/>
+      <c r="AG63" s="161"/>
+      <c r="AH63" s="161"/>
+      <c r="AI63" s="161"/>
       <c r="AJ63" s="35"/>
-      <c r="AL63" s="164" t="s">
+      <c r="AL63" s="161" t="s">
         <v>275</v>
       </c>
-      <c r="AM63" s="164"/>
-      <c r="AN63" s="164"/>
-      <c r="AO63" s="164"/>
-      <c r="AP63" s="164"/>
-      <c r="AQ63" s="164"/>
-      <c r="AR63" s="164"/>
-      <c r="AS63" s="164"/>
-      <c r="AT63" s="164"/>
-      <c r="AU63" s="164"/>
-      <c r="AV63" s="164"/>
-      <c r="AW63" s="164"/>
-      <c r="AX63" s="164"/>
-      <c r="AY63" s="164"/>
-      <c r="AZ63" s="164"/>
+      <c r="AM63" s="161"/>
+      <c r="AN63" s="161"/>
+      <c r="AO63" s="161"/>
+      <c r="AP63" s="161"/>
+      <c r="AQ63" s="161"/>
+      <c r="AR63" s="161"/>
+      <c r="AS63" s="161"/>
+      <c r="AT63" s="161"/>
+      <c r="AU63" s="161"/>
+      <c r="AV63" s="161"/>
+      <c r="AW63" s="161"/>
+      <c r="AX63" s="161"/>
+      <c r="AY63" s="161"/>
+      <c r="AZ63" s="161"/>
       <c r="BB63" s="36"/>
       <c r="BD63" s="48"/>
-      <c r="BE63" s="164" t="s">
+      <c r="BE63" s="161" t="s">
         <v>276</v>
       </c>
-      <c r="BF63" s="164"/>
-      <c r="BG63" s="164"/>
-      <c r="BH63" s="164"/>
-      <c r="BI63" s="164"/>
-      <c r="BJ63" s="164"/>
-      <c r="BK63" s="164"/>
-      <c r="BL63" s="164"/>
-      <c r="BM63" s="164"/>
-      <c r="BN63" s="164"/>
-      <c r="BO63" s="164"/>
-      <c r="BP63" s="164"/>
-      <c r="BQ63" s="164"/>
-      <c r="BR63" s="164"/>
-      <c r="BS63" s="164"/>
-      <c r="BT63" s="164"/>
-      <c r="BU63" s="164"/>
-      <c r="BV63" s="164"/>
-      <c r="BW63" s="164"/>
-      <c r="BX63" s="164"/>
-      <c r="BY63" s="164"/>
-      <c r="BZ63" s="164"/>
-      <c r="CA63" s="164"/>
-      <c r="CB63" s="164"/>
-      <c r="CC63" s="164"/>
-      <c r="CD63" s="164"/>
-      <c r="CE63" s="164"/>
-      <c r="CF63" s="164"/>
-      <c r="CG63" s="164"/>
-      <c r="CH63" s="164"/>
-      <c r="CI63" s="164"/>
-      <c r="CJ63" s="164"/>
-      <c r="CK63" s="164"/>
-      <c r="CL63" s="164"/>
-      <c r="CM63" s="164"/>
-      <c r="CN63" s="164"/>
-      <c r="CO63" s="164"/>
-      <c r="CP63" s="164"/>
-      <c r="CQ63" s="164"/>
-      <c r="CR63" s="164"/>
+      <c r="BF63" s="161"/>
+      <c r="BG63" s="161"/>
+      <c r="BH63" s="161"/>
+      <c r="BI63" s="161"/>
+      <c r="BJ63" s="161"/>
+      <c r="BK63" s="161"/>
+      <c r="BL63" s="161"/>
+      <c r="BM63" s="161"/>
+      <c r="BN63" s="161"/>
+      <c r="BO63" s="161"/>
+      <c r="BP63" s="161"/>
+      <c r="BQ63" s="161"/>
+      <c r="BR63" s="161"/>
+      <c r="BS63" s="161"/>
+      <c r="BT63" s="161"/>
+      <c r="BU63" s="161"/>
+      <c r="BV63" s="161"/>
+      <c r="BW63" s="161"/>
+      <c r="BX63" s="161"/>
+      <c r="BY63" s="161"/>
+      <c r="BZ63" s="161"/>
+      <c r="CA63" s="161"/>
+      <c r="CB63" s="161"/>
+      <c r="CC63" s="161"/>
+      <c r="CD63" s="161"/>
+      <c r="CE63" s="161"/>
+      <c r="CF63" s="161"/>
+      <c r="CG63" s="161"/>
+      <c r="CH63" s="161"/>
+      <c r="CI63" s="161"/>
+      <c r="CJ63" s="161"/>
+      <c r="CK63" s="161"/>
+      <c r="CL63" s="161"/>
+      <c r="CM63" s="161"/>
+      <c r="CN63" s="161"/>
+      <c r="CO63" s="161"/>
+      <c r="CP63" s="161"/>
+      <c r="CQ63" s="161"/>
+      <c r="CR63" s="161"/>
       <c r="CS63" s="36"/>
       <c r="DH63" s="10" t="s">
         <v>277</v>
@@ -37641,21 +37641,21 @@
     </row>
     <row r="64" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="48"/>
-      <c r="D64" s="165"/>
-      <c r="E64" s="165"/>
-      <c r="F64" s="165"/>
-      <c r="G64" s="165"/>
-      <c r="H64" s="165"/>
-      <c r="I64" s="165"/>
-      <c r="J64" s="165"/>
-      <c r="K64" s="165"/>
-      <c r="L64" s="165"/>
-      <c r="M64" s="165"/>
-      <c r="N64" s="165"/>
-      <c r="O64" s="165"/>
-      <c r="P64" s="165"/>
-      <c r="Q64" s="165"/>
-      <c r="R64" s="165"/>
+      <c r="D64" s="173"/>
+      <c r="E64" s="173"/>
+      <c r="F64" s="173"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="173"/>
+      <c r="I64" s="173"/>
+      <c r="J64" s="173"/>
+      <c r="K64" s="173"/>
+      <c r="L64" s="173"/>
+      <c r="M64" s="173"/>
+      <c r="N64" s="173"/>
+      <c r="O64" s="173"/>
+      <c r="P64" s="173"/>
+      <c r="Q64" s="173"/>
+      <c r="R64" s="173"/>
       <c r="S64" s="35"/>
       <c r="AJ64" s="35"/>
       <c r="BB64" s="36"/>
@@ -37670,21 +37670,21 @@
     </row>
     <row r="65" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="48"/>
-      <c r="D65" s="165"/>
-      <c r="E65" s="165"/>
-      <c r="F65" s="165"/>
-      <c r="G65" s="165"/>
-      <c r="H65" s="165"/>
-      <c r="I65" s="165"/>
-      <c r="J65" s="165"/>
-      <c r="K65" s="165"/>
-      <c r="L65" s="165"/>
-      <c r="M65" s="165"/>
-      <c r="N65" s="165"/>
-      <c r="O65" s="165"/>
-      <c r="P65" s="165"/>
-      <c r="Q65" s="165"/>
-      <c r="R65" s="165"/>
+      <c r="D65" s="173"/>
+      <c r="E65" s="173"/>
+      <c r="F65" s="173"/>
+      <c r="G65" s="173"/>
+      <c r="H65" s="173"/>
+      <c r="I65" s="173"/>
+      <c r="J65" s="173"/>
+      <c r="K65" s="173"/>
+      <c r="L65" s="173"/>
+      <c r="M65" s="173"/>
+      <c r="N65" s="173"/>
+      <c r="O65" s="173"/>
+      <c r="P65" s="173"/>
+      <c r="Q65" s="173"/>
+      <c r="R65" s="173"/>
       <c r="S65" s="35"/>
       <c r="AJ65" s="35"/>
       <c r="BB65" s="36"/>
@@ -37701,21 +37701,21 @@
     </row>
     <row r="66" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="48"/>
-      <c r="D66" s="165"/>
-      <c r="E66" s="165"/>
-      <c r="F66" s="165"/>
-      <c r="G66" s="165"/>
-      <c r="H66" s="165"/>
-      <c r="I66" s="165"/>
-      <c r="J66" s="165"/>
-      <c r="K66" s="165"/>
-      <c r="L66" s="165"/>
-      <c r="M66" s="165"/>
-      <c r="N66" s="165"/>
-      <c r="O66" s="165"/>
-      <c r="P66" s="165"/>
-      <c r="Q66" s="165"/>
-      <c r="R66" s="165"/>
+      <c r="D66" s="173"/>
+      <c r="E66" s="173"/>
+      <c r="F66" s="173"/>
+      <c r="G66" s="173"/>
+      <c r="H66" s="173"/>
+      <c r="I66" s="173"/>
+      <c r="J66" s="173"/>
+      <c r="K66" s="173"/>
+      <c r="L66" s="173"/>
+      <c r="M66" s="173"/>
+      <c r="N66" s="173"/>
+      <c r="O66" s="173"/>
+      <c r="P66" s="173"/>
+      <c r="Q66" s="173"/>
+      <c r="R66" s="173"/>
       <c r="S66" s="35"/>
       <c r="AJ66" s="35"/>
       <c r="BB66" s="36"/>
@@ -37732,21 +37732,21 @@
     </row>
     <row r="67" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="48"/>
-      <c r="D67" s="165"/>
-      <c r="E67" s="165"/>
-      <c r="F67" s="165"/>
-      <c r="G67" s="165"/>
-      <c r="H67" s="165"/>
-      <c r="I67" s="165"/>
-      <c r="J67" s="165"/>
-      <c r="K67" s="165"/>
-      <c r="L67" s="165"/>
-      <c r="M67" s="165"/>
-      <c r="N67" s="165"/>
-      <c r="O67" s="165"/>
-      <c r="P67" s="165"/>
-      <c r="Q67" s="165"/>
-      <c r="R67" s="165"/>
+      <c r="D67" s="173"/>
+      <c r="E67" s="173"/>
+      <c r="F67" s="173"/>
+      <c r="G67" s="173"/>
+      <c r="H67" s="173"/>
+      <c r="I67" s="173"/>
+      <c r="J67" s="173"/>
+      <c r="K67" s="173"/>
+      <c r="L67" s="173"/>
+      <c r="M67" s="173"/>
+      <c r="N67" s="173"/>
+      <c r="O67" s="173"/>
+      <c r="P67" s="173"/>
+      <c r="Q67" s="173"/>
+      <c r="R67" s="173"/>
       <c r="S67" s="35"/>
       <c r="AJ67" s="35"/>
       <c r="BB67" s="36"/>
@@ -37763,21 +37763,21 @@
     </row>
     <row r="68" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="48"/>
-      <c r="D68" s="165"/>
-      <c r="E68" s="165"/>
-      <c r="F68" s="165"/>
-      <c r="G68" s="165"/>
-      <c r="H68" s="165"/>
-      <c r="I68" s="165"/>
-      <c r="J68" s="165"/>
-      <c r="K68" s="165"/>
-      <c r="L68" s="165"/>
-      <c r="M68" s="165"/>
-      <c r="N68" s="165"/>
-      <c r="O68" s="165"/>
-      <c r="P68" s="165"/>
-      <c r="Q68" s="165"/>
-      <c r="R68" s="165"/>
+      <c r="D68" s="173"/>
+      <c r="E68" s="173"/>
+      <c r="F68" s="173"/>
+      <c r="G68" s="173"/>
+      <c r="H68" s="173"/>
+      <c r="I68" s="173"/>
+      <c r="J68" s="173"/>
+      <c r="K68" s="173"/>
+      <c r="L68" s="173"/>
+      <c r="M68" s="173"/>
+      <c r="N68" s="173"/>
+      <c r="O68" s="173"/>
+      <c r="P68" s="173"/>
+      <c r="Q68" s="173"/>
+      <c r="R68" s="173"/>
       <c r="S68" s="35"/>
       <c r="AJ68" s="35"/>
       <c r="BB68" s="36"/>
@@ -37786,21 +37786,21 @@
     </row>
     <row r="69" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="48"/>
-      <c r="D69" s="165"/>
-      <c r="E69" s="165"/>
-      <c r="F69" s="165"/>
-      <c r="G69" s="165"/>
-      <c r="H69" s="165"/>
-      <c r="I69" s="165"/>
-      <c r="J69" s="165"/>
-      <c r="K69" s="165"/>
-      <c r="L69" s="165"/>
-      <c r="M69" s="165"/>
-      <c r="N69" s="165"/>
-      <c r="O69" s="165"/>
-      <c r="P69" s="165"/>
-      <c r="Q69" s="165"/>
-      <c r="R69" s="165"/>
+      <c r="D69" s="173"/>
+      <c r="E69" s="173"/>
+      <c r="F69" s="173"/>
+      <c r="G69" s="173"/>
+      <c r="H69" s="173"/>
+      <c r="I69" s="173"/>
+      <c r="J69" s="173"/>
+      <c r="K69" s="173"/>
+      <c r="L69" s="173"/>
+      <c r="M69" s="173"/>
+      <c r="N69" s="173"/>
+      <c r="O69" s="173"/>
+      <c r="P69" s="173"/>
+      <c r="Q69" s="173"/>
+      <c r="R69" s="173"/>
       <c r="S69" s="35"/>
       <c r="AJ69" s="35"/>
       <c r="BB69" s="36"/>
@@ -37816,21 +37816,21 @@
     </row>
     <row r="70" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="48"/>
-      <c r="D70" s="165"/>
-      <c r="E70" s="165"/>
-      <c r="F70" s="165"/>
-      <c r="G70" s="165"/>
-      <c r="H70" s="165"/>
-      <c r="I70" s="165"/>
-      <c r="J70" s="165"/>
-      <c r="K70" s="165"/>
-      <c r="L70" s="165"/>
-      <c r="M70" s="165"/>
-      <c r="N70" s="165"/>
-      <c r="O70" s="165"/>
-      <c r="P70" s="165"/>
-      <c r="Q70" s="165"/>
-      <c r="R70" s="165"/>
+      <c r="D70" s="173"/>
+      <c r="E70" s="173"/>
+      <c r="F70" s="173"/>
+      <c r="G70" s="173"/>
+      <c r="H70" s="173"/>
+      <c r="I70" s="173"/>
+      <c r="J70" s="173"/>
+      <c r="K70" s="173"/>
+      <c r="L70" s="173"/>
+      <c r="M70" s="173"/>
+      <c r="N70" s="173"/>
+      <c r="O70" s="173"/>
+      <c r="P70" s="173"/>
+      <c r="Q70" s="173"/>
+      <c r="R70" s="173"/>
       <c r="S70" s="35"/>
       <c r="AJ70" s="35"/>
       <c r="BB70" s="36"/>
@@ -37846,21 +37846,21 @@
     </row>
     <row r="71" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="48"/>
-      <c r="D71" s="165"/>
-      <c r="E71" s="165"/>
-      <c r="F71" s="165"/>
-      <c r="G71" s="165"/>
-      <c r="H71" s="165"/>
-      <c r="I71" s="165"/>
-      <c r="J71" s="165"/>
-      <c r="K71" s="165"/>
-      <c r="L71" s="165"/>
-      <c r="M71" s="165"/>
-      <c r="N71" s="165"/>
-      <c r="O71" s="165"/>
-      <c r="P71" s="165"/>
-      <c r="Q71" s="165"/>
-      <c r="R71" s="165"/>
+      <c r="D71" s="173"/>
+      <c r="E71" s="173"/>
+      <c r="F71" s="173"/>
+      <c r="G71" s="173"/>
+      <c r="H71" s="173"/>
+      <c r="I71" s="173"/>
+      <c r="J71" s="173"/>
+      <c r="K71" s="173"/>
+      <c r="L71" s="173"/>
+      <c r="M71" s="173"/>
+      <c r="N71" s="173"/>
+      <c r="O71" s="173"/>
+      <c r="P71" s="173"/>
+      <c r="Q71" s="173"/>
+      <c r="R71" s="173"/>
       <c r="S71" s="35"/>
       <c r="AJ71" s="35"/>
       <c r="BB71" s="36"/>
@@ -37869,21 +37869,21 @@
     </row>
     <row r="72" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="48"/>
-      <c r="D72" s="165"/>
-      <c r="E72" s="165"/>
-      <c r="F72" s="165"/>
-      <c r="G72" s="165"/>
-      <c r="H72" s="165"/>
-      <c r="I72" s="165"/>
-      <c r="J72" s="165"/>
-      <c r="K72" s="165"/>
-      <c r="L72" s="165"/>
-      <c r="M72" s="165"/>
-      <c r="N72" s="165"/>
-      <c r="O72" s="165"/>
-      <c r="P72" s="165"/>
-      <c r="Q72" s="165"/>
-      <c r="R72" s="165"/>
+      <c r="D72" s="173"/>
+      <c r="E72" s="173"/>
+      <c r="F72" s="173"/>
+      <c r="G72" s="173"/>
+      <c r="H72" s="173"/>
+      <c r="I72" s="173"/>
+      <c r="J72" s="173"/>
+      <c r="K72" s="173"/>
+      <c r="L72" s="173"/>
+      <c r="M72" s="173"/>
+      <c r="N72" s="173"/>
+      <c r="O72" s="173"/>
+      <c r="P72" s="173"/>
+      <c r="Q72" s="173"/>
+      <c r="R72" s="173"/>
       <c r="S72" s="35"/>
       <c r="AJ72" s="35"/>
       <c r="BB72" s="36"/>
@@ -37936,113 +37936,113 @@
     </row>
     <row r="75" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="48"/>
-      <c r="D75" s="159" t="str">
+      <c r="D75" s="163" t="str">
         <f>"At the "&amp;$BH$4&amp;" rollout, ClaimPulse reduces cost to serve by "&amp;TEXT((1-((INDEX('5. Investor Metrics'!$D$9:$F$9,MATCH($BH$4,'5. Investor Metrics'!$D$6:$F$6,0)))/(INDEX('5. Investor Metrics'!$D$7:$F$7,MATCH($BH$4,'5. Investor Metrics'!$D$6:$F$6,0))))),"0.0%")&amp;" and eliminates "&amp;TEXT((((INDEX('3. Workings'!$D$11:$F$11,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))*(INDEX('1. Assumptions and Sources'!$D$23:$D$45,MATCH("Manual touches per claim today",'1. Assumptions and Sources'!$C$23:$C$45,0))))-((INDEX('3. Workings'!$D$11:$F$11,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))*((INDEX('3. Workings'!$D$12:$F$12,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))*(INDEX('3. Workings'!$D$19:$F$19,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)))+(1-(INDEX('3. Workings'!$D$12:$F$12,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0))))*(INDEX('1. Assumptions and Sources'!$D$23:$D$45,MATCH("Manual touches per claim today",'1. Assumptions and Sources'!$C$23:$C$45,0))))))/1000000,"0.00")&amp;"M manual touches annually, with "&amp;TEXT(INDEX('1. Assumptions and Sources'!$D$23:$D$45,MATCH("Green lane share",'1. Assumptions and Sources'!$C$23:$C$45,0)),"0%")&amp;" of claims flowing through the straight-through lane."</f>
         <v>At the Aggressive rollout, ClaimPulse reduces cost to serve by 85.9% and eliminates 1.58M manual touches annually, with 65% of claims flowing through the straight-through lane.</v>
       </c>
-      <c r="E75" s="159"/>
-      <c r="F75" s="159"/>
-      <c r="G75" s="159"/>
-      <c r="H75" s="159"/>
-      <c r="I75" s="159"/>
-      <c r="J75" s="159"/>
-      <c r="K75" s="159"/>
-      <c r="L75" s="159"/>
-      <c r="M75" s="159"/>
-      <c r="N75" s="159"/>
-      <c r="O75" s="159"/>
-      <c r="P75" s="159"/>
-      <c r="Q75" s="159"/>
-      <c r="R75" s="159"/>
-      <c r="S75" s="159"/>
-      <c r="T75" s="159"/>
-      <c r="U75" s="159"/>
-      <c r="V75" s="159"/>
-      <c r="W75" s="159"/>
-      <c r="X75" s="159"/>
-      <c r="Y75" s="159"/>
-      <c r="Z75" s="159"/>
-      <c r="AA75" s="159"/>
-      <c r="AB75" s="159"/>
-      <c r="AC75" s="159"/>
-      <c r="AD75" s="159"/>
-      <c r="AE75" s="159"/>
-      <c r="AF75" s="159"/>
-      <c r="AG75" s="159"/>
-      <c r="AH75" s="159"/>
-      <c r="AI75" s="159"/>
-      <c r="AJ75" s="159"/>
-      <c r="AK75" s="159"/>
-      <c r="AL75" s="159"/>
-      <c r="AM75" s="159"/>
-      <c r="AN75" s="159"/>
-      <c r="AO75" s="159"/>
-      <c r="AP75" s="159"/>
-      <c r="AQ75" s="159"/>
-      <c r="AR75" s="159"/>
-      <c r="AS75" s="159"/>
-      <c r="AT75" s="159"/>
-      <c r="AU75" s="159"/>
-      <c r="AV75" s="159"/>
-      <c r="AW75" s="159"/>
-      <c r="AX75" s="159"/>
-      <c r="AY75" s="159"/>
-      <c r="AZ75" s="159"/>
+      <c r="E75" s="163"/>
+      <c r="F75" s="163"/>
+      <c r="G75" s="163"/>
+      <c r="H75" s="163"/>
+      <c r="I75" s="163"/>
+      <c r="J75" s="163"/>
+      <c r="K75" s="163"/>
+      <c r="L75" s="163"/>
+      <c r="M75" s="163"/>
+      <c r="N75" s="163"/>
+      <c r="O75" s="163"/>
+      <c r="P75" s="163"/>
+      <c r="Q75" s="163"/>
+      <c r="R75" s="163"/>
+      <c r="S75" s="163"/>
+      <c r="T75" s="163"/>
+      <c r="U75" s="163"/>
+      <c r="V75" s="163"/>
+      <c r="W75" s="163"/>
+      <c r="X75" s="163"/>
+      <c r="Y75" s="163"/>
+      <c r="Z75" s="163"/>
+      <c r="AA75" s="163"/>
+      <c r="AB75" s="163"/>
+      <c r="AC75" s="163"/>
+      <c r="AD75" s="163"/>
+      <c r="AE75" s="163"/>
+      <c r="AF75" s="163"/>
+      <c r="AG75" s="163"/>
+      <c r="AH75" s="163"/>
+      <c r="AI75" s="163"/>
+      <c r="AJ75" s="163"/>
+      <c r="AK75" s="163"/>
+      <c r="AL75" s="163"/>
+      <c r="AM75" s="163"/>
+      <c r="AN75" s="163"/>
+      <c r="AO75" s="163"/>
+      <c r="AP75" s="163"/>
+      <c r="AQ75" s="163"/>
+      <c r="AR75" s="163"/>
+      <c r="AS75" s="163"/>
+      <c r="AT75" s="163"/>
+      <c r="AU75" s="163"/>
+      <c r="AV75" s="163"/>
+      <c r="AW75" s="163"/>
+      <c r="AX75" s="163"/>
+      <c r="AY75" s="163"/>
+      <c r="AZ75" s="163"/>
       <c r="BB75" s="36"/>
       <c r="BD75" s="48"/>
       <c r="CS75" s="36"/>
     </row>
     <row r="76" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="48"/>
-      <c r="D76" s="159"/>
-      <c r="E76" s="159"/>
-      <c r="F76" s="159"/>
-      <c r="G76" s="159"/>
-      <c r="H76" s="159"/>
-      <c r="I76" s="159"/>
-      <c r="J76" s="159"/>
-      <c r="K76" s="159"/>
-      <c r="L76" s="159"/>
-      <c r="M76" s="159"/>
-      <c r="N76" s="159"/>
-      <c r="O76" s="159"/>
-      <c r="P76" s="159"/>
-      <c r="Q76" s="159"/>
-      <c r="R76" s="159"/>
-      <c r="S76" s="159"/>
-      <c r="T76" s="159"/>
-      <c r="U76" s="159"/>
-      <c r="V76" s="159"/>
-      <c r="W76" s="159"/>
-      <c r="X76" s="159"/>
-      <c r="Y76" s="159"/>
-      <c r="Z76" s="159"/>
-      <c r="AA76" s="159"/>
-      <c r="AB76" s="159"/>
-      <c r="AC76" s="159"/>
-      <c r="AD76" s="159"/>
-      <c r="AE76" s="159"/>
-      <c r="AF76" s="159"/>
-      <c r="AG76" s="159"/>
-      <c r="AH76" s="159"/>
-      <c r="AI76" s="159"/>
-      <c r="AJ76" s="159"/>
-      <c r="AK76" s="159"/>
-      <c r="AL76" s="159"/>
-      <c r="AM76" s="159"/>
-      <c r="AN76" s="159"/>
-      <c r="AO76" s="159"/>
-      <c r="AP76" s="159"/>
-      <c r="AQ76" s="159"/>
-      <c r="AR76" s="159"/>
-      <c r="AS76" s="159"/>
-      <c r="AT76" s="159"/>
-      <c r="AU76" s="159"/>
-      <c r="AV76" s="159"/>
-      <c r="AW76" s="159"/>
-      <c r="AX76" s="159"/>
-      <c r="AY76" s="159"/>
-      <c r="AZ76" s="159"/>
+      <c r="D76" s="163"/>
+      <c r="E76" s="163"/>
+      <c r="F76" s="163"/>
+      <c r="G76" s="163"/>
+      <c r="H76" s="163"/>
+      <c r="I76" s="163"/>
+      <c r="J76" s="163"/>
+      <c r="K76" s="163"/>
+      <c r="L76" s="163"/>
+      <c r="M76" s="163"/>
+      <c r="N76" s="163"/>
+      <c r="O76" s="163"/>
+      <c r="P76" s="163"/>
+      <c r="Q76" s="163"/>
+      <c r="R76" s="163"/>
+      <c r="S76" s="163"/>
+      <c r="T76" s="163"/>
+      <c r="U76" s="163"/>
+      <c r="V76" s="163"/>
+      <c r="W76" s="163"/>
+      <c r="X76" s="163"/>
+      <c r="Y76" s="163"/>
+      <c r="Z76" s="163"/>
+      <c r="AA76" s="163"/>
+      <c r="AB76" s="163"/>
+      <c r="AC76" s="163"/>
+      <c r="AD76" s="163"/>
+      <c r="AE76" s="163"/>
+      <c r="AF76" s="163"/>
+      <c r="AG76" s="163"/>
+      <c r="AH76" s="163"/>
+      <c r="AI76" s="163"/>
+      <c r="AJ76" s="163"/>
+      <c r="AK76" s="163"/>
+      <c r="AL76" s="163"/>
+      <c r="AM76" s="163"/>
+      <c r="AN76" s="163"/>
+      <c r="AO76" s="163"/>
+      <c r="AP76" s="163"/>
+      <c r="AQ76" s="163"/>
+      <c r="AR76" s="163"/>
+      <c r="AS76" s="163"/>
+      <c r="AT76" s="163"/>
+      <c r="AU76" s="163"/>
+      <c r="AV76" s="163"/>
+      <c r="AW76" s="163"/>
+      <c r="AX76" s="163"/>
+      <c r="AY76" s="163"/>
+      <c r="AZ76" s="163"/>
       <c r="BB76" s="36"/>
       <c r="BD76" s="48"/>
       <c r="CS76" s="36"/>
@@ -38152,131 +38152,131 @@
       <c r="AR79" s="32"/>
       <c r="AS79" s="32"/>
       <c r="AT79" s="32"/>
-      <c r="AU79" s="163" t="str">
+      <c r="AU79" s="160" t="str">
         <f>"Selected scenario: "&amp;$BH$4</f>
         <v>Selected scenario: Aggressive</v>
       </c>
-      <c r="AV79" s="163"/>
-      <c r="AW79" s="163"/>
-      <c r="AX79" s="163"/>
-      <c r="AY79" s="163"/>
-      <c r="AZ79" s="163"/>
-      <c r="BA79" s="163"/>
-      <c r="BB79" s="163"/>
+      <c r="AV79" s="160"/>
+      <c r="AW79" s="160"/>
+      <c r="AX79" s="160"/>
+      <c r="AY79" s="160"/>
+      <c r="AZ79" s="160"/>
+      <c r="BA79" s="160"/>
+      <c r="BB79" s="160"/>
       <c r="BD79" s="48"/>
       <c r="CS79" s="36"/>
     </row>
     <row r="80" spans="3:113" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="48"/>
-      <c r="AU80" s="163"/>
-      <c r="AV80" s="163"/>
-      <c r="AW80" s="163"/>
-      <c r="AX80" s="163"/>
-      <c r="AY80" s="163"/>
-      <c r="AZ80" s="163"/>
-      <c r="BA80" s="163"/>
-      <c r="BB80" s="163"/>
+      <c r="AU80" s="160"/>
+      <c r="AV80" s="160"/>
+      <c r="AW80" s="160"/>
+      <c r="AX80" s="160"/>
+      <c r="AY80" s="160"/>
+      <c r="AZ80" s="160"/>
+      <c r="BA80" s="160"/>
+      <c r="BB80" s="160"/>
       <c r="BD80" s="48"/>
       <c r="CS80" s="36"/>
     </row>
     <row r="81" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="48"/>
-      <c r="D81" s="164" t="s">
+      <c r="D81" s="161" t="s">
         <v>281</v>
       </c>
-      <c r="E81" s="164"/>
-      <c r="F81" s="164"/>
-      <c r="G81" s="164"/>
-      <c r="H81" s="164"/>
-      <c r="I81" s="164"/>
-      <c r="J81" s="164"/>
-      <c r="K81" s="164"/>
-      <c r="L81" s="164"/>
-      <c r="M81" s="164"/>
-      <c r="N81" s="164"/>
+      <c r="E81" s="161"/>
+      <c r="F81" s="161"/>
+      <c r="G81" s="161"/>
+      <c r="H81" s="161"/>
+      <c r="I81" s="161"/>
+      <c r="J81" s="161"/>
+      <c r="K81" s="161"/>
+      <c r="L81" s="161"/>
+      <c r="M81" s="161"/>
+      <c r="N81" s="161"/>
       <c r="P81" s="42"/>
-      <c r="R81" s="164" t="s">
+      <c r="R81" s="161" t="s">
         <v>282</v>
       </c>
-      <c r="S81" s="164"/>
-      <c r="T81" s="164"/>
-      <c r="U81" s="164"/>
-      <c r="V81" s="164"/>
-      <c r="W81" s="164"/>
-      <c r="X81" s="164"/>
-      <c r="Y81" s="164"/>
-      <c r="Z81" s="164"/>
-      <c r="AA81" s="164"/>
-      <c r="AB81" s="164"/>
-      <c r="AC81" s="164"/>
-      <c r="AD81" s="164"/>
-      <c r="AE81" s="164"/>
-      <c r="AF81" s="164"/>
-      <c r="AG81" s="164"/>
-      <c r="AH81" s="164"/>
-      <c r="AI81" s="164"/>
-      <c r="AJ81" s="164"/>
-      <c r="AK81" s="164"/>
-      <c r="AL81" s="164"/>
-      <c r="AM81" s="164"/>
-      <c r="AN81" s="164"/>
-      <c r="AO81" s="164"/>
-      <c r="AP81" s="164"/>
-      <c r="AQ81" s="164"/>
-      <c r="AR81" s="164"/>
-      <c r="AS81" s="164"/>
-      <c r="AT81" s="164"/>
-      <c r="AU81" s="164"/>
-      <c r="AV81" s="164"/>
-      <c r="AW81" s="164"/>
-      <c r="AX81" s="164"/>
-      <c r="AY81" s="164"/>
-      <c r="AZ81" s="164"/>
-      <c r="BA81" s="164"/>
+      <c r="S81" s="161"/>
+      <c r="T81" s="161"/>
+      <c r="U81" s="161"/>
+      <c r="V81" s="161"/>
+      <c r="W81" s="161"/>
+      <c r="X81" s="161"/>
+      <c r="Y81" s="161"/>
+      <c r="Z81" s="161"/>
+      <c r="AA81" s="161"/>
+      <c r="AB81" s="161"/>
+      <c r="AC81" s="161"/>
+      <c r="AD81" s="161"/>
+      <c r="AE81" s="161"/>
+      <c r="AF81" s="161"/>
+      <c r="AG81" s="161"/>
+      <c r="AH81" s="161"/>
+      <c r="AI81" s="161"/>
+      <c r="AJ81" s="161"/>
+      <c r="AK81" s="161"/>
+      <c r="AL81" s="161"/>
+      <c r="AM81" s="161"/>
+      <c r="AN81" s="161"/>
+      <c r="AO81" s="161"/>
+      <c r="AP81" s="161"/>
+      <c r="AQ81" s="161"/>
+      <c r="AR81" s="161"/>
+      <c r="AS81" s="161"/>
+      <c r="AT81" s="161"/>
+      <c r="AU81" s="161"/>
+      <c r="AV81" s="161"/>
+      <c r="AW81" s="161"/>
+      <c r="AX81" s="161"/>
+      <c r="AY81" s="161"/>
+      <c r="AZ81" s="161"/>
+      <c r="BA81" s="161"/>
       <c r="BB81" s="36"/>
       <c r="BD81" s="48"/>
-      <c r="BE81" s="164" t="s">
+      <c r="BE81" s="161" t="s">
         <v>283</v>
       </c>
-      <c r="BF81" s="164"/>
-      <c r="BG81" s="164"/>
-      <c r="BH81" s="164"/>
-      <c r="BI81" s="164"/>
-      <c r="BJ81" s="164"/>
-      <c r="BK81" s="164"/>
-      <c r="BL81" s="164"/>
-      <c r="BM81" s="164"/>
-      <c r="BN81" s="164"/>
-      <c r="BO81" s="164"/>
-      <c r="BP81" s="164"/>
-      <c r="BQ81" s="164"/>
-      <c r="BR81" s="164"/>
-      <c r="BS81" s="164"/>
-      <c r="BT81" s="164"/>
-      <c r="BU81" s="164"/>
-      <c r="BV81" s="164"/>
-      <c r="BW81" s="164"/>
-      <c r="BX81" s="164"/>
-      <c r="BY81" s="164"/>
-      <c r="BZ81" s="164"/>
-      <c r="CA81" s="164"/>
-      <c r="CB81" s="164"/>
-      <c r="CC81" s="164"/>
-      <c r="CD81" s="164"/>
-      <c r="CE81" s="164"/>
-      <c r="CF81" s="164"/>
-      <c r="CG81" s="164"/>
-      <c r="CH81" s="164"/>
-      <c r="CI81" s="164"/>
-      <c r="CJ81" s="164"/>
-      <c r="CK81" s="164"/>
-      <c r="CL81" s="164"/>
-      <c r="CM81" s="164"/>
-      <c r="CN81" s="164"/>
-      <c r="CO81" s="164"/>
-      <c r="CP81" s="164"/>
-      <c r="CQ81" s="164"/>
-      <c r="CR81" s="164"/>
+      <c r="BF81" s="161"/>
+      <c r="BG81" s="161"/>
+      <c r="BH81" s="161"/>
+      <c r="BI81" s="161"/>
+      <c r="BJ81" s="161"/>
+      <c r="BK81" s="161"/>
+      <c r="BL81" s="161"/>
+      <c r="BM81" s="161"/>
+      <c r="BN81" s="161"/>
+      <c r="BO81" s="161"/>
+      <c r="BP81" s="161"/>
+      <c r="BQ81" s="161"/>
+      <c r="BR81" s="161"/>
+      <c r="BS81" s="161"/>
+      <c r="BT81" s="161"/>
+      <c r="BU81" s="161"/>
+      <c r="BV81" s="161"/>
+      <c r="BW81" s="161"/>
+      <c r="BX81" s="161"/>
+      <c r="BY81" s="161"/>
+      <c r="BZ81" s="161"/>
+      <c r="CA81" s="161"/>
+      <c r="CB81" s="161"/>
+      <c r="CC81" s="161"/>
+      <c r="CD81" s="161"/>
+      <c r="CE81" s="161"/>
+      <c r="CF81" s="161"/>
+      <c r="CG81" s="161"/>
+      <c r="CH81" s="161"/>
+      <c r="CI81" s="161"/>
+      <c r="CJ81" s="161"/>
+      <c r="CK81" s="161"/>
+      <c r="CL81" s="161"/>
+      <c r="CM81" s="161"/>
+      <c r="CN81" s="161"/>
+      <c r="CO81" s="161"/>
+      <c r="CP81" s="161"/>
+      <c r="CQ81" s="161"/>
+      <c r="CR81" s="161"/>
       <c r="CS81" s="36"/>
     </row>
     <row r="82" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -38288,22 +38288,22 @@
     </row>
     <row r="83" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="48"/>
-      <c r="D83" s="160" t="s">
+      <c r="D83" s="174" t="s">
         <v>284</v>
       </c>
-      <c r="E83" s="160"/>
-      <c r="F83" s="160"/>
-      <c r="G83" s="160"/>
-      <c r="H83" s="160"/>
-      <c r="I83" s="160"/>
-      <c r="J83" s="161" t="str">
+      <c r="E83" s="174"/>
+      <c r="F83" s="174"/>
+      <c r="G83" s="174"/>
+      <c r="H83" s="174"/>
+      <c r="I83" s="174"/>
+      <c r="J83" s="175" t="str">
         <f>TEXT(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH($BH$4,'5. Investor Metrics'!$D$32:$F$32,0)),"0.00")</f>
         <v>9.89</v>
       </c>
-      <c r="K83" s="161"/>
-      <c r="L83" s="161"/>
-      <c r="M83" s="161"/>
-      <c r="N83" s="161"/>
+      <c r="K83" s="175"/>
+      <c r="L83" s="175"/>
+      <c r="M83" s="175"/>
+      <c r="N83" s="175"/>
       <c r="P83" s="42"/>
       <c r="BB83" s="36"/>
       <c r="BD83" s="48"/>
@@ -38311,17 +38311,17 @@
     </row>
     <row r="84" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="48"/>
-      <c r="D84" s="160"/>
-      <c r="E84" s="160"/>
-      <c r="F84" s="160"/>
-      <c r="G84" s="160"/>
-      <c r="H84" s="160"/>
-      <c r="I84" s="160"/>
-      <c r="J84" s="161"/>
-      <c r="K84" s="161"/>
-      <c r="L84" s="161"/>
-      <c r="M84" s="161"/>
-      <c r="N84" s="161"/>
+      <c r="D84" s="174"/>
+      <c r="E84" s="174"/>
+      <c r="F84" s="174"/>
+      <c r="G84" s="174"/>
+      <c r="H84" s="174"/>
+      <c r="I84" s="174"/>
+      <c r="J84" s="175"/>
+      <c r="K84" s="175"/>
+      <c r="L84" s="175"/>
+      <c r="M84" s="175"/>
+      <c r="N84" s="175"/>
       <c r="P84" s="42"/>
       <c r="BB84" s="36"/>
       <c r="BD84" s="48"/>
@@ -38341,22 +38341,22 @@
     </row>
     <row r="86" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="48"/>
-      <c r="D86" s="160" t="s">
+      <c r="D86" s="174" t="s">
         <v>228</v>
       </c>
-      <c r="E86" s="160"/>
-      <c r="F86" s="160"/>
-      <c r="G86" s="160"/>
-      <c r="H86" s="160"/>
-      <c r="I86" s="160"/>
-      <c r="J86" s="161" t="str">
+      <c r="E86" s="174"/>
+      <c r="F86" s="174"/>
+      <c r="G86" s="174"/>
+      <c r="H86" s="174"/>
+      <c r="I86" s="174"/>
+      <c r="J86" s="175" t="str">
         <f>TEXT(INDEX('5. Investor Metrics'!$D$33:$F$33,MATCH($BH$4,'5. Investor Metrics'!$D$32:$F$32,0)),"0.00")</f>
         <v>75.28</v>
       </c>
-      <c r="K86" s="161"/>
-      <c r="L86" s="161"/>
-      <c r="M86" s="161"/>
-      <c r="N86" s="161"/>
+      <c r="K86" s="175"/>
+      <c r="L86" s="175"/>
+      <c r="M86" s="175"/>
+      <c r="N86" s="175"/>
       <c r="P86" s="42"/>
       <c r="BB86" s="36"/>
       <c r="BD86" s="48"/>
@@ -38364,17 +38364,17 @@
     </row>
     <row r="87" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="48"/>
-      <c r="D87" s="160"/>
-      <c r="E87" s="160"/>
-      <c r="F87" s="160"/>
-      <c r="G87" s="160"/>
-      <c r="H87" s="160"/>
-      <c r="I87" s="160"/>
-      <c r="J87" s="161"/>
-      <c r="K87" s="161"/>
-      <c r="L87" s="161"/>
-      <c r="M87" s="161"/>
-      <c r="N87" s="161"/>
+      <c r="D87" s="174"/>
+      <c r="E87" s="174"/>
+      <c r="F87" s="174"/>
+      <c r="G87" s="174"/>
+      <c r="H87" s="174"/>
+      <c r="I87" s="174"/>
+      <c r="J87" s="175"/>
+      <c r="K87" s="175"/>
+      <c r="L87" s="175"/>
+      <c r="M87" s="175"/>
+      <c r="N87" s="175"/>
       <c r="P87" s="42"/>
       <c r="BB87" s="36"/>
       <c r="BD87" s="48"/>
@@ -38394,22 +38394,22 @@
     </row>
     <row r="89" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="48"/>
-      <c r="D89" s="160" t="s">
+      <c r="D89" s="174" t="s">
         <v>285</v>
       </c>
-      <c r="E89" s="160"/>
-      <c r="F89" s="160"/>
-      <c r="G89" s="160"/>
-      <c r="H89" s="160"/>
-      <c r="I89" s="160"/>
-      <c r="J89" s="161" t="str">
+      <c r="E89" s="174"/>
+      <c r="F89" s="174"/>
+      <c r="G89" s="174"/>
+      <c r="H89" s="174"/>
+      <c r="I89" s="174"/>
+      <c r="J89" s="175" t="str">
         <f>TEXT(IF(((INDEX('5. Investor Metrics'!$D$22:$F$22,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))-(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0))))&gt;=0,10+(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))/(INDEX('5. Investor Metrics'!$D$22:$F$22,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))*12,IF((((INDEX('5. Investor Metrics'!$D$22:$F$22,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))-(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0))))+(INDEX('5. Investor Metrics'!$D$23:$F$23,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0))))&gt;=0,22+(-((INDEX('5. Investor Metrics'!$D$22:$F$22,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))-(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))))/(INDEX('5. Investor Metrics'!$D$23:$F$23,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))*12,34+(-(((INDEX('5. Investor Metrics'!$D$22:$F$22,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))-(INDEX('5. Investor Metrics'!$D$35:$F$35,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0))))+(INDEX('5. Investor Metrics'!$D$23:$F$23,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))))/(INDEX('5. Investor Metrics'!$D$24:$F$24,MATCH(($BH$4),'5. Investor Metrics'!$D$32:$F$32,0)))*12)),"0.00")</f>
         <v>13.83</v>
       </c>
-      <c r="K89" s="161"/>
-      <c r="L89" s="161"/>
-      <c r="M89" s="161"/>
-      <c r="N89" s="161"/>
+      <c r="K89" s="175"/>
+      <c r="L89" s="175"/>
+      <c r="M89" s="175"/>
+      <c r="N89" s="175"/>
       <c r="P89" s="42"/>
       <c r="BB89" s="36"/>
       <c r="BD89" s="48"/>
@@ -38417,17 +38417,17 @@
     </row>
     <row r="90" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="48"/>
-      <c r="D90" s="160"/>
-      <c r="E90" s="160"/>
-      <c r="F90" s="160"/>
-      <c r="G90" s="160"/>
-      <c r="H90" s="160"/>
-      <c r="I90" s="160"/>
-      <c r="J90" s="161"/>
-      <c r="K90" s="161"/>
-      <c r="L90" s="161"/>
-      <c r="M90" s="161"/>
-      <c r="N90" s="161"/>
+      <c r="D90" s="174"/>
+      <c r="E90" s="174"/>
+      <c r="F90" s="174"/>
+      <c r="G90" s="174"/>
+      <c r="H90" s="174"/>
+      <c r="I90" s="174"/>
+      <c r="J90" s="175"/>
+      <c r="K90" s="175"/>
+      <c r="L90" s="175"/>
+      <c r="M90" s="175"/>
+      <c r="N90" s="175"/>
       <c r="P90" s="42"/>
       <c r="BB90" s="36"/>
       <c r="BD90" s="48"/>
@@ -38447,22 +38447,22 @@
     </row>
     <row r="92" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="48"/>
-      <c r="D92" s="160" t="s">
+      <c r="D92" s="174" t="s">
         <v>286</v>
       </c>
-      <c r="E92" s="160"/>
-      <c r="F92" s="160"/>
-      <c r="G92" s="160"/>
-      <c r="H92" s="160"/>
-      <c r="I92" s="160"/>
-      <c r="J92" s="161" t="str">
+      <c r="E92" s="174"/>
+      <c r="F92" s="174"/>
+      <c r="G92" s="174"/>
+      <c r="H92" s="174"/>
+      <c r="I92" s="174"/>
+      <c r="J92" s="175" t="str">
         <f>TEXT(INDEX('4. Forecast'!$D$49:$F$49,MATCH($BH$4,'4. Forecast'!$D$45:$F$45,0)),"0.00")</f>
         <v>140.71</v>
       </c>
-      <c r="K92" s="161"/>
-      <c r="L92" s="161"/>
-      <c r="M92" s="161"/>
-      <c r="N92" s="161"/>
+      <c r="K92" s="175"/>
+      <c r="L92" s="175"/>
+      <c r="M92" s="175"/>
+      <c r="N92" s="175"/>
       <c r="P92" s="42"/>
       <c r="BB92" s="36"/>
       <c r="BD92" s="48"/>
@@ -38470,17 +38470,17 @@
     </row>
     <row r="93" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="48"/>
-      <c r="D93" s="160"/>
-      <c r="E93" s="160"/>
-      <c r="F93" s="160"/>
-      <c r="G93" s="160"/>
-      <c r="H93" s="160"/>
-      <c r="I93" s="160"/>
-      <c r="J93" s="161"/>
-      <c r="K93" s="161"/>
-      <c r="L93" s="161"/>
-      <c r="M93" s="161"/>
-      <c r="N93" s="161"/>
+      <c r="D93" s="174"/>
+      <c r="E93" s="174"/>
+      <c r="F93" s="174"/>
+      <c r="G93" s="174"/>
+      <c r="H93" s="174"/>
+      <c r="I93" s="174"/>
+      <c r="J93" s="175"/>
+      <c r="K93" s="175"/>
+      <c r="L93" s="175"/>
+      <c r="M93" s="175"/>
+      <c r="N93" s="175"/>
       <c r="P93" s="35"/>
       <c r="BB93" s="36"/>
       <c r="BD93" s="48"/>
@@ -38500,22 +38500,22 @@
     </row>
     <row r="95" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="48"/>
-      <c r="D95" s="160" t="s">
+      <c r="D95" s="174" t="s">
         <v>287</v>
       </c>
-      <c r="E95" s="160"/>
-      <c r="F95" s="160"/>
-      <c r="G95" s="160"/>
-      <c r="H95" s="160"/>
-      <c r="I95" s="160"/>
-      <c r="J95" s="161" t="str">
+      <c r="E95" s="174"/>
+      <c r="F95" s="174"/>
+      <c r="G95" s="174"/>
+      <c r="H95" s="174"/>
+      <c r="I95" s="174"/>
+      <c r="J95" s="175" t="str">
         <f>TEXT(INDEX('5. Investor Metrics'!$D$28:$F$28,MATCH($BH$4,'5. Investor Metrics'!$D$20:$F$20,0)),"0.00")</f>
         <v>261.79</v>
       </c>
-      <c r="K95" s="161"/>
-      <c r="L95" s="161"/>
-      <c r="M95" s="161"/>
-      <c r="N95" s="161"/>
+      <c r="K95" s="175"/>
+      <c r="L95" s="175"/>
+      <c r="M95" s="175"/>
+      <c r="N95" s="175"/>
       <c r="P95" s="35"/>
       <c r="BB95" s="36"/>
       <c r="BD95" s="48"/>
@@ -38523,17 +38523,17 @@
     </row>
     <row r="96" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="48"/>
-      <c r="D96" s="160"/>
-      <c r="E96" s="160"/>
-      <c r="F96" s="160"/>
-      <c r="G96" s="160"/>
-      <c r="H96" s="160"/>
-      <c r="I96" s="160"/>
-      <c r="J96" s="161"/>
-      <c r="K96" s="161"/>
-      <c r="L96" s="161"/>
-      <c r="M96" s="161"/>
-      <c r="N96" s="161"/>
+      <c r="D96" s="174"/>
+      <c r="E96" s="174"/>
+      <c r="F96" s="174"/>
+      <c r="G96" s="174"/>
+      <c r="H96" s="174"/>
+      <c r="I96" s="174"/>
+      <c r="J96" s="175"/>
+      <c r="K96" s="175"/>
+      <c r="L96" s="175"/>
+      <c r="M96" s="175"/>
+      <c r="N96" s="175"/>
       <c r="P96" s="35"/>
       <c r="BB96" s="36"/>
       <c r="BD96" s="48"/>
@@ -38544,202 +38544,202 @@
       <c r="P97" s="35"/>
       <c r="BB97" s="36"/>
       <c r="BD97" s="48"/>
-      <c r="BE97" s="159" t="str">
+      <c r="BE97" s="163" t="str">
         <f>"At the "&amp;$BH$4&amp;" rollout, every ₹1 of annual run cost generates ₹"&amp;TEXT(INDEX('3. Workings'!$D$69:$F$69,MATCH($BH$4,'3. Workings'!$D$68:$F$68,0))/INDEX('3. Workings'!$D$70:$F$70,MATCH($BH$4,'3. Workings'!$D$68:$F$68,0)),"0.0")&amp;" of gross benefit, delivering ₹"&amp;TEXT(INDEX('3. Workings'!$D$71:$F$71,MATCH($BH$4,'3. Workings'!$D$68:$F$68,0)),"0.0")&amp;" Cr in net annual value."</f>
         <v>At the Aggressive rollout, every ₹1 of annual run cost generates ₹15.2 of gross benefit, delivering ₹75.3 Cr in net annual value.</v>
       </c>
-      <c r="BF97" s="159"/>
-      <c r="BG97" s="159"/>
-      <c r="BH97" s="159"/>
-      <c r="BI97" s="159"/>
-      <c r="BJ97" s="159"/>
-      <c r="BK97" s="159"/>
-      <c r="BL97" s="159"/>
-      <c r="BM97" s="159"/>
-      <c r="BN97" s="159"/>
-      <c r="BO97" s="159"/>
-      <c r="BP97" s="159"/>
-      <c r="BQ97" s="159"/>
-      <c r="BR97" s="159"/>
-      <c r="BS97" s="159"/>
-      <c r="BT97" s="159"/>
-      <c r="BU97" s="159"/>
-      <c r="BV97" s="159"/>
-      <c r="BW97" s="159"/>
-      <c r="BX97" s="159"/>
-      <c r="BY97" s="159"/>
-      <c r="BZ97" s="159"/>
-      <c r="CA97" s="159"/>
-      <c r="CB97" s="159"/>
-      <c r="CC97" s="159"/>
-      <c r="CD97" s="159"/>
-      <c r="CE97" s="159"/>
-      <c r="CF97" s="159"/>
-      <c r="CG97" s="159"/>
-      <c r="CH97" s="159"/>
-      <c r="CI97" s="159"/>
-      <c r="CJ97" s="159"/>
-      <c r="CK97" s="159"/>
-      <c r="CL97" s="159"/>
-      <c r="CM97" s="159"/>
-      <c r="CN97" s="159"/>
-      <c r="CO97" s="159"/>
-      <c r="CP97" s="159"/>
-      <c r="CQ97" s="159"/>
-      <c r="CR97" s="159"/>
+      <c r="BF97" s="163"/>
+      <c r="BG97" s="163"/>
+      <c r="BH97" s="163"/>
+      <c r="BI97" s="163"/>
+      <c r="BJ97" s="163"/>
+      <c r="BK97" s="163"/>
+      <c r="BL97" s="163"/>
+      <c r="BM97" s="163"/>
+      <c r="BN97" s="163"/>
+      <c r="BO97" s="163"/>
+      <c r="BP97" s="163"/>
+      <c r="BQ97" s="163"/>
+      <c r="BR97" s="163"/>
+      <c r="BS97" s="163"/>
+      <c r="BT97" s="163"/>
+      <c r="BU97" s="163"/>
+      <c r="BV97" s="163"/>
+      <c r="BW97" s="163"/>
+      <c r="BX97" s="163"/>
+      <c r="BY97" s="163"/>
+      <c r="BZ97" s="163"/>
+      <c r="CA97" s="163"/>
+      <c r="CB97" s="163"/>
+      <c r="CC97" s="163"/>
+      <c r="CD97" s="163"/>
+      <c r="CE97" s="163"/>
+      <c r="CF97" s="163"/>
+      <c r="CG97" s="163"/>
+      <c r="CH97" s="163"/>
+      <c r="CI97" s="163"/>
+      <c r="CJ97" s="163"/>
+      <c r="CK97" s="163"/>
+      <c r="CL97" s="163"/>
+      <c r="CM97" s="163"/>
+      <c r="CN97" s="163"/>
+      <c r="CO97" s="163"/>
+      <c r="CP97" s="163"/>
+      <c r="CQ97" s="163"/>
+      <c r="CR97" s="163"/>
       <c r="CS97" s="36"/>
     </row>
     <row r="98" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="48"/>
-      <c r="D98" s="162" t="str">
+      <c r="D98" s="176" t="str">
         <f>"At the "&amp;$BH$4&amp;" rollout, the ₹"&amp;TEXT(J83,"0.0")&amp;" Cr build investment reaches payback in "&amp;TEXT(J89,"0.0")&amp;" months and generates ₹"&amp;TEXT(J95,"0.0")&amp;" Cr of 5-year NPV."</f>
         <v>At the Aggressive rollout, the ₹9.9 Cr build investment reaches payback in 13.8 months and generates ₹261.8 Cr of 5-year NPV.</v>
       </c>
-      <c r="E98" s="162"/>
-      <c r="F98" s="162"/>
-      <c r="G98" s="162"/>
-      <c r="H98" s="162"/>
-      <c r="I98" s="162"/>
-      <c r="J98" s="162"/>
-      <c r="K98" s="162"/>
-      <c r="L98" s="162"/>
-      <c r="M98" s="162"/>
-      <c r="N98" s="162"/>
-      <c r="O98" s="162"/>
-      <c r="P98" s="162"/>
-      <c r="Q98" s="162"/>
-      <c r="R98" s="162"/>
-      <c r="S98" s="162"/>
-      <c r="T98" s="162"/>
-      <c r="U98" s="162"/>
-      <c r="V98" s="162"/>
-      <c r="W98" s="162"/>
-      <c r="X98" s="162"/>
-      <c r="Y98" s="162"/>
-      <c r="Z98" s="162"/>
-      <c r="AA98" s="162"/>
-      <c r="AB98" s="162"/>
-      <c r="AC98" s="162"/>
-      <c r="AD98" s="162"/>
-      <c r="AE98" s="162"/>
-      <c r="AF98" s="162"/>
-      <c r="AG98" s="162"/>
-      <c r="AH98" s="162"/>
-      <c r="AI98" s="162"/>
-      <c r="AJ98" s="162"/>
-      <c r="AK98" s="162"/>
-      <c r="AL98" s="162"/>
-      <c r="AM98" s="162"/>
-      <c r="AN98" s="162"/>
-      <c r="AO98" s="162"/>
-      <c r="AP98" s="162"/>
-      <c r="AQ98" s="162"/>
-      <c r="AR98" s="162"/>
-      <c r="AS98" s="162"/>
-      <c r="AT98" s="162"/>
-      <c r="AU98" s="162"/>
-      <c r="AV98" s="162"/>
-      <c r="AW98" s="162"/>
-      <c r="AX98" s="162"/>
-      <c r="AY98" s="162"/>
-      <c r="AZ98" s="162"/>
-      <c r="BA98" s="162"/>
+      <c r="E98" s="176"/>
+      <c r="F98" s="176"/>
+      <c r="G98" s="176"/>
+      <c r="H98" s="176"/>
+      <c r="I98" s="176"/>
+      <c r="J98" s="176"/>
+      <c r="K98" s="176"/>
+      <c r="L98" s="176"/>
+      <c r="M98" s="176"/>
+      <c r="N98" s="176"/>
+      <c r="O98" s="176"/>
+      <c r="P98" s="176"/>
+      <c r="Q98" s="176"/>
+      <c r="R98" s="176"/>
+      <c r="S98" s="176"/>
+      <c r="T98" s="176"/>
+      <c r="U98" s="176"/>
+      <c r="V98" s="176"/>
+      <c r="W98" s="176"/>
+      <c r="X98" s="176"/>
+      <c r="Y98" s="176"/>
+      <c r="Z98" s="176"/>
+      <c r="AA98" s="176"/>
+      <c r="AB98" s="176"/>
+      <c r="AC98" s="176"/>
+      <c r="AD98" s="176"/>
+      <c r="AE98" s="176"/>
+      <c r="AF98" s="176"/>
+      <c r="AG98" s="176"/>
+      <c r="AH98" s="176"/>
+      <c r="AI98" s="176"/>
+      <c r="AJ98" s="176"/>
+      <c r="AK98" s="176"/>
+      <c r="AL98" s="176"/>
+      <c r="AM98" s="176"/>
+      <c r="AN98" s="176"/>
+      <c r="AO98" s="176"/>
+      <c r="AP98" s="176"/>
+      <c r="AQ98" s="176"/>
+      <c r="AR98" s="176"/>
+      <c r="AS98" s="176"/>
+      <c r="AT98" s="176"/>
+      <c r="AU98" s="176"/>
+      <c r="AV98" s="176"/>
+      <c r="AW98" s="176"/>
+      <c r="AX98" s="176"/>
+      <c r="AY98" s="176"/>
+      <c r="AZ98" s="176"/>
+      <c r="BA98" s="176"/>
       <c r="BB98" s="36"/>
       <c r="BD98" s="48"/>
-      <c r="BE98" s="159"/>
-      <c r="BF98" s="159"/>
-      <c r="BG98" s="159"/>
-      <c r="BH98" s="159"/>
-      <c r="BI98" s="159"/>
-      <c r="BJ98" s="159"/>
-      <c r="BK98" s="159"/>
-      <c r="BL98" s="159"/>
-      <c r="BM98" s="159"/>
-      <c r="BN98" s="159"/>
-      <c r="BO98" s="159"/>
-      <c r="BP98" s="159"/>
-      <c r="BQ98" s="159"/>
-      <c r="BR98" s="159"/>
-      <c r="BS98" s="159"/>
-      <c r="BT98" s="159"/>
-      <c r="BU98" s="159"/>
-      <c r="BV98" s="159"/>
-      <c r="BW98" s="159"/>
-      <c r="BX98" s="159"/>
-      <c r="BY98" s="159"/>
-      <c r="BZ98" s="159"/>
-      <c r="CA98" s="159"/>
-      <c r="CB98" s="159"/>
-      <c r="CC98" s="159"/>
-      <c r="CD98" s="159"/>
-      <c r="CE98" s="159"/>
-      <c r="CF98" s="159"/>
-      <c r="CG98" s="159"/>
-      <c r="CH98" s="159"/>
-      <c r="CI98" s="159"/>
-      <c r="CJ98" s="159"/>
-      <c r="CK98" s="159"/>
-      <c r="CL98" s="159"/>
-      <c r="CM98" s="159"/>
-      <c r="CN98" s="159"/>
-      <c r="CO98" s="159"/>
-      <c r="CP98" s="159"/>
-      <c r="CQ98" s="159"/>
-      <c r="CR98" s="159"/>
+      <c r="BE98" s="163"/>
+      <c r="BF98" s="163"/>
+      <c r="BG98" s="163"/>
+      <c r="BH98" s="163"/>
+      <c r="BI98" s="163"/>
+      <c r="BJ98" s="163"/>
+      <c r="BK98" s="163"/>
+      <c r="BL98" s="163"/>
+      <c r="BM98" s="163"/>
+      <c r="BN98" s="163"/>
+      <c r="BO98" s="163"/>
+      <c r="BP98" s="163"/>
+      <c r="BQ98" s="163"/>
+      <c r="BR98" s="163"/>
+      <c r="BS98" s="163"/>
+      <c r="BT98" s="163"/>
+      <c r="BU98" s="163"/>
+      <c r="BV98" s="163"/>
+      <c r="BW98" s="163"/>
+      <c r="BX98" s="163"/>
+      <c r="BY98" s="163"/>
+      <c r="BZ98" s="163"/>
+      <c r="CA98" s="163"/>
+      <c r="CB98" s="163"/>
+      <c r="CC98" s="163"/>
+      <c r="CD98" s="163"/>
+      <c r="CE98" s="163"/>
+      <c r="CF98" s="163"/>
+      <c r="CG98" s="163"/>
+      <c r="CH98" s="163"/>
+      <c r="CI98" s="163"/>
+      <c r="CJ98" s="163"/>
+      <c r="CK98" s="163"/>
+      <c r="CL98" s="163"/>
+      <c r="CM98" s="163"/>
+      <c r="CN98" s="163"/>
+      <c r="CO98" s="163"/>
+      <c r="CP98" s="163"/>
+      <c r="CQ98" s="163"/>
+      <c r="CR98" s="163"/>
       <c r="CS98" s="36"/>
     </row>
     <row r="99" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="50"/>
-      <c r="D99" s="162"/>
-      <c r="E99" s="162"/>
-      <c r="F99" s="162"/>
-      <c r="G99" s="162"/>
-      <c r="H99" s="162"/>
-      <c r="I99" s="162"/>
-      <c r="J99" s="162"/>
-      <c r="K99" s="162"/>
-      <c r="L99" s="162"/>
-      <c r="M99" s="162"/>
-      <c r="N99" s="162"/>
-      <c r="O99" s="162"/>
-      <c r="P99" s="162"/>
-      <c r="Q99" s="162"/>
-      <c r="R99" s="162"/>
-      <c r="S99" s="162"/>
-      <c r="T99" s="162"/>
-      <c r="U99" s="162"/>
-      <c r="V99" s="162"/>
-      <c r="W99" s="162"/>
-      <c r="X99" s="162"/>
-      <c r="Y99" s="162"/>
-      <c r="Z99" s="162"/>
-      <c r="AA99" s="162"/>
-      <c r="AB99" s="162"/>
-      <c r="AC99" s="162"/>
-      <c r="AD99" s="162"/>
-      <c r="AE99" s="162"/>
-      <c r="AF99" s="162"/>
-      <c r="AG99" s="162"/>
-      <c r="AH99" s="162"/>
-      <c r="AI99" s="162"/>
-      <c r="AJ99" s="162"/>
-      <c r="AK99" s="162"/>
-      <c r="AL99" s="162"/>
-      <c r="AM99" s="162"/>
-      <c r="AN99" s="162"/>
-      <c r="AO99" s="162"/>
-      <c r="AP99" s="162"/>
-      <c r="AQ99" s="162"/>
-      <c r="AR99" s="162"/>
-      <c r="AS99" s="162"/>
-      <c r="AT99" s="162"/>
-      <c r="AU99" s="162"/>
-      <c r="AV99" s="162"/>
-      <c r="AW99" s="162"/>
-      <c r="AX99" s="162"/>
-      <c r="AY99" s="162"/>
-      <c r="AZ99" s="162"/>
-      <c r="BA99" s="162"/>
+      <c r="D99" s="176"/>
+      <c r="E99" s="176"/>
+      <c r="F99" s="176"/>
+      <c r="G99" s="176"/>
+      <c r="H99" s="176"/>
+      <c r="I99" s="176"/>
+      <c r="J99" s="176"/>
+      <c r="K99" s="176"/>
+      <c r="L99" s="176"/>
+      <c r="M99" s="176"/>
+      <c r="N99" s="176"/>
+      <c r="O99" s="176"/>
+      <c r="P99" s="176"/>
+      <c r="Q99" s="176"/>
+      <c r="R99" s="176"/>
+      <c r="S99" s="176"/>
+      <c r="T99" s="176"/>
+      <c r="U99" s="176"/>
+      <c r="V99" s="176"/>
+      <c r="W99" s="176"/>
+      <c r="X99" s="176"/>
+      <c r="Y99" s="176"/>
+      <c r="Z99" s="176"/>
+      <c r="AA99" s="176"/>
+      <c r="AB99" s="176"/>
+      <c r="AC99" s="176"/>
+      <c r="AD99" s="176"/>
+      <c r="AE99" s="176"/>
+      <c r="AF99" s="176"/>
+      <c r="AG99" s="176"/>
+      <c r="AH99" s="176"/>
+      <c r="AI99" s="176"/>
+      <c r="AJ99" s="176"/>
+      <c r="AK99" s="176"/>
+      <c r="AL99" s="176"/>
+      <c r="AM99" s="176"/>
+      <c r="AN99" s="176"/>
+      <c r="AO99" s="176"/>
+      <c r="AP99" s="176"/>
+      <c r="AQ99" s="176"/>
+      <c r="AR99" s="176"/>
+      <c r="AS99" s="176"/>
+      <c r="AT99" s="176"/>
+      <c r="AU99" s="176"/>
+      <c r="AV99" s="176"/>
+      <c r="AW99" s="176"/>
+      <c r="AX99" s="176"/>
+      <c r="AY99" s="176"/>
+      <c r="AZ99" s="176"/>
+      <c r="BA99" s="176"/>
       <c r="BB99" s="46"/>
       <c r="BD99" s="50"/>
       <c r="BE99" s="45"/>
@@ -38873,128 +38873,128 @@
       <c r="CI101" s="32"/>
       <c r="CJ101" s="32"/>
       <c r="CK101" s="32"/>
-      <c r="CL101" s="163" t="str">
+      <c r="CL101" s="160" t="str">
         <f>"Selected scenario: "&amp;$BH$4</f>
         <v>Selected scenario: Aggressive</v>
       </c>
-      <c r="CM101" s="163"/>
-      <c r="CN101" s="163"/>
-      <c r="CO101" s="163"/>
-      <c r="CP101" s="163"/>
-      <c r="CQ101" s="163"/>
-      <c r="CR101" s="163"/>
-      <c r="CS101" s="163"/>
+      <c r="CM101" s="160"/>
+      <c r="CN101" s="160"/>
+      <c r="CO101" s="160"/>
+      <c r="CP101" s="160"/>
+      <c r="CQ101" s="160"/>
+      <c r="CR101" s="160"/>
+      <c r="CS101" s="160"/>
     </row>
     <row r="102" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="48"/>
-      <c r="CL102" s="163"/>
-      <c r="CM102" s="163"/>
-      <c r="CN102" s="163"/>
-      <c r="CO102" s="163"/>
-      <c r="CP102" s="163"/>
-      <c r="CQ102" s="163"/>
-      <c r="CR102" s="163"/>
-      <c r="CS102" s="163"/>
+      <c r="CL102" s="160"/>
+      <c r="CM102" s="160"/>
+      <c r="CN102" s="160"/>
+      <c r="CO102" s="160"/>
+      <c r="CP102" s="160"/>
+      <c r="CQ102" s="160"/>
+      <c r="CR102" s="160"/>
+      <c r="CS102" s="160"/>
     </row>
     <row r="103" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="48"/>
-      <c r="D103" s="164" t="s">
+      <c r="D103" s="161" t="s">
         <v>288</v>
       </c>
-      <c r="E103" s="164"/>
-      <c r="F103" s="164"/>
-      <c r="G103" s="164"/>
-      <c r="H103" s="164"/>
-      <c r="I103" s="164"/>
-      <c r="J103" s="164"/>
-      <c r="K103" s="164"/>
-      <c r="L103" s="164"/>
-      <c r="M103" s="164"/>
-      <c r="N103" s="164"/>
-      <c r="O103" s="164"/>
-      <c r="P103" s="164"/>
-      <c r="Q103" s="164"/>
-      <c r="R103" s="164"/>
-      <c r="S103" s="164"/>
-      <c r="T103" s="164"/>
-      <c r="U103" s="164"/>
-      <c r="V103" s="164"/>
-      <c r="W103" s="164"/>
-      <c r="X103" s="164"/>
-      <c r="Y103" s="164"/>
-      <c r="Z103" s="164"/>
-      <c r="AA103" s="164"/>
-      <c r="AB103" s="164"/>
-      <c r="AC103" s="164"/>
-      <c r="AD103" s="164"/>
-      <c r="AE103" s="164"/>
-      <c r="AF103" s="164"/>
-      <c r="AG103" s="164"/>
-      <c r="AH103" s="164"/>
-      <c r="AI103" s="164"/>
+      <c r="E103" s="161"/>
+      <c r="F103" s="161"/>
+      <c r="G103" s="161"/>
+      <c r="H103" s="161"/>
+      <c r="I103" s="161"/>
+      <c r="J103" s="161"/>
+      <c r="K103" s="161"/>
+      <c r="L103" s="161"/>
+      <c r="M103" s="161"/>
+      <c r="N103" s="161"/>
+      <c r="O103" s="161"/>
+      <c r="P103" s="161"/>
+      <c r="Q103" s="161"/>
+      <c r="R103" s="161"/>
+      <c r="S103" s="161"/>
+      <c r="T103" s="161"/>
+      <c r="U103" s="161"/>
+      <c r="V103" s="161"/>
+      <c r="W103" s="161"/>
+      <c r="X103" s="161"/>
+      <c r="Y103" s="161"/>
+      <c r="Z103" s="161"/>
+      <c r="AA103" s="161"/>
+      <c r="AB103" s="161"/>
+      <c r="AC103" s="161"/>
+      <c r="AD103" s="161"/>
+      <c r="AE103" s="161"/>
+      <c r="AF103" s="161"/>
+      <c r="AG103" s="161"/>
+      <c r="AH103" s="161"/>
+      <c r="AI103" s="161"/>
       <c r="AJ103" s="54"/>
       <c r="AK103" s="55"/>
-      <c r="AL103" s="164" t="s">
+      <c r="AL103" s="161" t="s">
         <v>289</v>
       </c>
-      <c r="AM103" s="164"/>
-      <c r="AN103" s="164"/>
-      <c r="AO103" s="164"/>
-      <c r="AP103" s="164"/>
-      <c r="AQ103" s="164"/>
-      <c r="AR103" s="164"/>
-      <c r="AS103" s="164"/>
-      <c r="AT103" s="164"/>
-      <c r="AU103" s="164"/>
-      <c r="AV103" s="164"/>
-      <c r="AW103" s="164"/>
-      <c r="AX103" s="164"/>
-      <c r="AY103" s="164"/>
-      <c r="AZ103" s="164"/>
-      <c r="BA103" s="164"/>
-      <c r="BB103" s="164"/>
-      <c r="BC103" s="164"/>
-      <c r="BD103" s="164"/>
-      <c r="BE103" s="164"/>
-      <c r="BF103" s="164"/>
-      <c r="BG103" s="164"/>
-      <c r="BH103" s="164"/>
+      <c r="AM103" s="161"/>
+      <c r="AN103" s="161"/>
+      <c r="AO103" s="161"/>
+      <c r="AP103" s="161"/>
+      <c r="AQ103" s="161"/>
+      <c r="AR103" s="161"/>
+      <c r="AS103" s="161"/>
+      <c r="AT103" s="161"/>
+      <c r="AU103" s="161"/>
+      <c r="AV103" s="161"/>
+      <c r="AW103" s="161"/>
+      <c r="AX103" s="161"/>
+      <c r="AY103" s="161"/>
+      <c r="AZ103" s="161"/>
+      <c r="BA103" s="161"/>
+      <c r="BB103" s="161"/>
+      <c r="BC103" s="161"/>
+      <c r="BD103" s="161"/>
+      <c r="BE103" s="161"/>
+      <c r="BF103" s="161"/>
+      <c r="BG103" s="161"/>
+      <c r="BH103" s="161"/>
       <c r="BI103" s="55"/>
       <c r="BJ103" s="55"/>
-      <c r="BK103" s="164" t="s">
+      <c r="BK103" s="161" t="s">
         <v>290</v>
       </c>
-      <c r="BL103" s="164"/>
-      <c r="BM103" s="164"/>
-      <c r="BN103" s="164"/>
-      <c r="BO103" s="164"/>
-      <c r="BP103" s="164"/>
-      <c r="BQ103" s="164"/>
-      <c r="BR103" s="164"/>
-      <c r="BS103" s="164"/>
-      <c r="BT103" s="164"/>
-      <c r="BU103" s="164"/>
-      <c r="BV103" s="164"/>
-      <c r="BW103" s="164"/>
-      <c r="BX103" s="164"/>
-      <c r="BY103" s="164"/>
-      <c r="BZ103" s="164"/>
-      <c r="CA103" s="164"/>
-      <c r="CB103" s="164"/>
-      <c r="CC103" s="164"/>
-      <c r="CD103" s="164"/>
-      <c r="CE103" s="164"/>
-      <c r="CF103" s="164"/>
-      <c r="CG103" s="164"/>
-      <c r="CH103" s="164"/>
-      <c r="CI103" s="164"/>
-      <c r="CJ103" s="164"/>
-      <c r="CK103" s="164"/>
-      <c r="CL103" s="164"/>
-      <c r="CM103" s="164"/>
-      <c r="CN103" s="164"/>
-      <c r="CO103" s="164"/>
-      <c r="CP103" s="164"/>
+      <c r="BL103" s="161"/>
+      <c r="BM103" s="161"/>
+      <c r="BN103" s="161"/>
+      <c r="BO103" s="161"/>
+      <c r="BP103" s="161"/>
+      <c r="BQ103" s="161"/>
+      <c r="BR103" s="161"/>
+      <c r="BS103" s="161"/>
+      <c r="BT103" s="161"/>
+      <c r="BU103" s="161"/>
+      <c r="BV103" s="161"/>
+      <c r="BW103" s="161"/>
+      <c r="BX103" s="161"/>
+      <c r="BY103" s="161"/>
+      <c r="BZ103" s="161"/>
+      <c r="CA103" s="161"/>
+      <c r="CB103" s="161"/>
+      <c r="CC103" s="161"/>
+      <c r="CD103" s="161"/>
+      <c r="CE103" s="161"/>
+      <c r="CF103" s="161"/>
+      <c r="CG103" s="161"/>
+      <c r="CH103" s="161"/>
+      <c r="CI103" s="161"/>
+      <c r="CJ103" s="161"/>
+      <c r="CK103" s="161"/>
+      <c r="CL103" s="161"/>
+      <c r="CM103" s="161"/>
+      <c r="CN103" s="161"/>
+      <c r="CO103" s="161"/>
+      <c r="CP103" s="161"/>
       <c r="CS103" s="36"/>
     </row>
     <row r="104" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -39005,203 +39005,203 @@
     </row>
     <row r="105" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="48"/>
-      <c r="D105" s="153" t="s">
+      <c r="D105" s="177" t="s">
         <v>291</v>
       </c>
-      <c r="E105" s="153"/>
-      <c r="F105" s="153"/>
-      <c r="G105" s="153"/>
-      <c r="H105" s="153"/>
-      <c r="I105" s="153"/>
-      <c r="J105" s="153"/>
-      <c r="K105" s="153"/>
-      <c r="L105" s="153"/>
-      <c r="M105" s="153"/>
-      <c r="N105" s="153"/>
-      <c r="O105" s="153"/>
-      <c r="P105" s="153"/>
-      <c r="Q105" s="155"/>
-      <c r="R105" s="155"/>
-      <c r="S105" s="155"/>
-      <c r="T105" s="155"/>
-      <c r="U105" s="155"/>
-      <c r="V105" s="155"/>
-      <c r="X105" s="156" t="s">
+      <c r="E105" s="177"/>
+      <c r="F105" s="177"/>
+      <c r="G105" s="177"/>
+      <c r="H105" s="177"/>
+      <c r="I105" s="177"/>
+      <c r="J105" s="177"/>
+      <c r="K105" s="177"/>
+      <c r="L105" s="177"/>
+      <c r="M105" s="177"/>
+      <c r="N105" s="177"/>
+      <c r="O105" s="177"/>
+      <c r="P105" s="177"/>
+      <c r="Q105" s="178"/>
+      <c r="R105" s="178"/>
+      <c r="S105" s="178"/>
+      <c r="T105" s="178"/>
+      <c r="U105" s="178"/>
+      <c r="V105" s="178"/>
+      <c r="X105" s="179" t="s">
         <v>292</v>
       </c>
-      <c r="Y105" s="156"/>
-      <c r="Z105" s="156"/>
-      <c r="AA105" s="156"/>
-      <c r="AB105" s="156"/>
-      <c r="AC105" s="156"/>
-      <c r="AD105" s="156"/>
-      <c r="AE105" s="156"/>
-      <c r="AF105" s="156"/>
-      <c r="AG105" s="156"/>
-      <c r="AH105" s="156"/>
-      <c r="AI105" s="156"/>
+      <c r="Y105" s="179"/>
+      <c r="Z105" s="179"/>
+      <c r="AA105" s="179"/>
+      <c r="AB105" s="179"/>
+      <c r="AC105" s="179"/>
+      <c r="AD105" s="179"/>
+      <c r="AE105" s="179"/>
+      <c r="AF105" s="179"/>
+      <c r="AG105" s="179"/>
+      <c r="AH105" s="179"/>
+      <c r="AI105" s="179"/>
       <c r="AJ105" s="57"/>
-      <c r="AL105" s="153" t="s">
+      <c r="AL105" s="177" t="s">
         <v>293</v>
       </c>
-      <c r="AM105" s="153"/>
-      <c r="AN105" s="153"/>
-      <c r="AO105" s="153"/>
-      <c r="AP105" s="153"/>
-      <c r="AQ105" s="153"/>
-      <c r="AR105" s="153"/>
-      <c r="AS105" s="153"/>
-      <c r="AT105" s="153"/>
-      <c r="AU105" s="153"/>
-      <c r="AV105" s="153"/>
-      <c r="AW105" s="153"/>
-      <c r="AX105" s="153"/>
-      <c r="AY105" s="157" t="str">
+      <c r="AM105" s="177"/>
+      <c r="AN105" s="177"/>
+      <c r="AO105" s="177"/>
+      <c r="AP105" s="177"/>
+      <c r="AQ105" s="177"/>
+      <c r="AR105" s="177"/>
+      <c r="AS105" s="177"/>
+      <c r="AT105" s="177"/>
+      <c r="AU105" s="177"/>
+      <c r="AV105" s="177"/>
+      <c r="AW105" s="177"/>
+      <c r="AX105" s="177"/>
+      <c r="AY105" s="180" t="str">
         <f>"₹"&amp;TEXT(INDEX('3. Workings'!$D$71:$F$71,MATCH($BH$4,'3. Workings'!$D$68:$F$68,0)),"0.0")&amp;" Cr"</f>
         <v>₹75.3 Cr</v>
       </c>
-      <c r="AZ105" s="157"/>
-      <c r="BA105" s="157"/>
-      <c r="BB105" s="157"/>
-      <c r="BC105" s="157"/>
-      <c r="BD105" s="157"/>
-      <c r="BE105" s="157"/>
-      <c r="BF105" s="157"/>
-      <c r="BG105" s="157"/>
-      <c r="BH105" s="157"/>
+      <c r="AZ105" s="180"/>
+      <c r="BA105" s="180"/>
+      <c r="BB105" s="180"/>
+      <c r="BC105" s="180"/>
+      <c r="BD105" s="180"/>
+      <c r="BE105" s="180"/>
+      <c r="BF105" s="180"/>
+      <c r="BG105" s="180"/>
+      <c r="BH105" s="180"/>
       <c r="BI105" s="35"/>
-      <c r="BK105" s="153" t="str">
+      <c r="BK105" s="177" t="str">
         <f>"Manual touches per claim  ·  we assume "&amp;TEXT('1. Assumptions and Sources'!$F$147,"0.0")</f>
         <v>Manual touches per claim  ·  we assume 7.0</v>
       </c>
-      <c r="BL105" s="153"/>
-      <c r="BM105" s="153"/>
-      <c r="BN105" s="153"/>
-      <c r="BO105" s="153"/>
-      <c r="BP105" s="153"/>
-      <c r="BQ105" s="153"/>
-      <c r="BR105" s="153"/>
-      <c r="BS105" s="153"/>
-      <c r="BT105" s="153"/>
-      <c r="BU105" s="153"/>
-      <c r="BW105" s="154" t="str">
+      <c r="BL105" s="177"/>
+      <c r="BM105" s="177"/>
+      <c r="BN105" s="177"/>
+      <c r="BO105" s="177"/>
+      <c r="BP105" s="177"/>
+      <c r="BQ105" s="177"/>
+      <c r="BR105" s="177"/>
+      <c r="BS105" s="177"/>
+      <c r="BT105" s="177"/>
+      <c r="BU105" s="177"/>
+      <c r="BW105" s="181" t="str">
         <f>"Breaks at "&amp;TEXT(INDEX('3. Workings'!$D$138:$F$138,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0.0")&amp;"   ·   "&amp;IF(INDEX('3. Workings'!$D$139:$F$139,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0))&gt;0,TEXT(INDEX('3. Workings'!$D$139:$F$139,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;" cushion","NO cushion at this plan")</f>
         <v>Breaks at 1.8   ·   75% cushion</v>
       </c>
-      <c r="BX105" s="154"/>
-      <c r="BY105" s="154"/>
-      <c r="BZ105" s="154"/>
-      <c r="CA105" s="154"/>
-      <c r="CB105" s="154"/>
-      <c r="CC105" s="154"/>
-      <c r="CD105" s="154"/>
-      <c r="CE105" s="154"/>
-      <c r="CF105" s="154"/>
-      <c r="CG105" s="154"/>
-      <c r="CH105" s="154"/>
-      <c r="CI105" s="154"/>
-      <c r="CJ105" s="154"/>
-      <c r="CK105" s="154"/>
-      <c r="CL105" s="154"/>
-      <c r="CM105" s="154"/>
-      <c r="CN105" s="154"/>
-      <c r="CO105" s="154"/>
-      <c r="CP105" s="154"/>
-      <c r="CQ105" s="154"/>
-      <c r="CR105" s="154"/>
+      <c r="BX105" s="181"/>
+      <c r="BY105" s="181"/>
+      <c r="BZ105" s="181"/>
+      <c r="CA105" s="181"/>
+      <c r="CB105" s="181"/>
+      <c r="CC105" s="181"/>
+      <c r="CD105" s="181"/>
+      <c r="CE105" s="181"/>
+      <c r="CF105" s="181"/>
+      <c r="CG105" s="181"/>
+      <c r="CH105" s="181"/>
+      <c r="CI105" s="181"/>
+      <c r="CJ105" s="181"/>
+      <c r="CK105" s="181"/>
+      <c r="CL105" s="181"/>
+      <c r="CM105" s="181"/>
+      <c r="CN105" s="181"/>
+      <c r="CO105" s="181"/>
+      <c r="CP105" s="181"/>
+      <c r="CQ105" s="181"/>
+      <c r="CR105" s="181"/>
       <c r="CS105" s="36"/>
     </row>
     <row r="106" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="48"/>
-      <c r="D106" s="153"/>
-      <c r="E106" s="153"/>
-      <c r="F106" s="153"/>
-      <c r="G106" s="153"/>
-      <c r="H106" s="153"/>
-      <c r="I106" s="153"/>
-      <c r="J106" s="153"/>
-      <c r="K106" s="153"/>
-      <c r="L106" s="153"/>
-      <c r="M106" s="153"/>
-      <c r="N106" s="153"/>
-      <c r="O106" s="153"/>
-      <c r="P106" s="153"/>
-      <c r="Q106" s="155"/>
-      <c r="R106" s="155"/>
-      <c r="S106" s="155"/>
-      <c r="T106" s="155"/>
-      <c r="U106" s="155"/>
-      <c r="V106" s="155"/>
-      <c r="X106" s="156"/>
-      <c r="Y106" s="156"/>
-      <c r="Z106" s="156"/>
-      <c r="AA106" s="156"/>
-      <c r="AB106" s="156"/>
-      <c r="AC106" s="156"/>
-      <c r="AD106" s="156"/>
-      <c r="AE106" s="156"/>
-      <c r="AF106" s="156"/>
-      <c r="AG106" s="156"/>
-      <c r="AH106" s="156"/>
-      <c r="AI106" s="156"/>
+      <c r="D106" s="177"/>
+      <c r="E106" s="177"/>
+      <c r="F106" s="177"/>
+      <c r="G106" s="177"/>
+      <c r="H106" s="177"/>
+      <c r="I106" s="177"/>
+      <c r="J106" s="177"/>
+      <c r="K106" s="177"/>
+      <c r="L106" s="177"/>
+      <c r="M106" s="177"/>
+      <c r="N106" s="177"/>
+      <c r="O106" s="177"/>
+      <c r="P106" s="177"/>
+      <c r="Q106" s="178"/>
+      <c r="R106" s="178"/>
+      <c r="S106" s="178"/>
+      <c r="T106" s="178"/>
+      <c r="U106" s="178"/>
+      <c r="V106" s="178"/>
+      <c r="X106" s="179"/>
+      <c r="Y106" s="179"/>
+      <c r="Z106" s="179"/>
+      <c r="AA106" s="179"/>
+      <c r="AB106" s="179"/>
+      <c r="AC106" s="179"/>
+      <c r="AD106" s="179"/>
+      <c r="AE106" s="179"/>
+      <c r="AF106" s="179"/>
+      <c r="AG106" s="179"/>
+      <c r="AH106" s="179"/>
+      <c r="AI106" s="179"/>
       <c r="AJ106" s="57"/>
-      <c r="AL106" s="153"/>
-      <c r="AM106" s="153"/>
-      <c r="AN106" s="153"/>
-      <c r="AO106" s="153"/>
-      <c r="AP106" s="153"/>
-      <c r="AQ106" s="153"/>
-      <c r="AR106" s="153"/>
-      <c r="AS106" s="153"/>
-      <c r="AT106" s="153"/>
-      <c r="AU106" s="153"/>
-      <c r="AV106" s="153"/>
-      <c r="AW106" s="153"/>
-      <c r="AX106" s="153"/>
-      <c r="AY106" s="157"/>
-      <c r="AZ106" s="157"/>
-      <c r="BA106" s="157"/>
-      <c r="BB106" s="157"/>
-      <c r="BC106" s="157"/>
-      <c r="BD106" s="157"/>
-      <c r="BE106" s="157"/>
-      <c r="BF106" s="157"/>
-      <c r="BG106" s="157"/>
-      <c r="BH106" s="157"/>
+      <c r="AL106" s="177"/>
+      <c r="AM106" s="177"/>
+      <c r="AN106" s="177"/>
+      <c r="AO106" s="177"/>
+      <c r="AP106" s="177"/>
+      <c r="AQ106" s="177"/>
+      <c r="AR106" s="177"/>
+      <c r="AS106" s="177"/>
+      <c r="AT106" s="177"/>
+      <c r="AU106" s="177"/>
+      <c r="AV106" s="177"/>
+      <c r="AW106" s="177"/>
+      <c r="AX106" s="177"/>
+      <c r="AY106" s="180"/>
+      <c r="AZ106" s="180"/>
+      <c r="BA106" s="180"/>
+      <c r="BB106" s="180"/>
+      <c r="BC106" s="180"/>
+      <c r="BD106" s="180"/>
+      <c r="BE106" s="180"/>
+      <c r="BF106" s="180"/>
+      <c r="BG106" s="180"/>
+      <c r="BH106" s="180"/>
       <c r="BI106" s="35"/>
-      <c r="BK106" s="153"/>
-      <c r="BL106" s="153"/>
-      <c r="BM106" s="153"/>
-      <c r="BN106" s="153"/>
-      <c r="BO106" s="153"/>
-      <c r="BP106" s="153"/>
-      <c r="BQ106" s="153"/>
-      <c r="BR106" s="153"/>
-      <c r="BS106" s="153"/>
-      <c r="BT106" s="153"/>
-      <c r="BU106" s="153"/>
-      <c r="BW106" s="154"/>
-      <c r="BX106" s="154"/>
-      <c r="BY106" s="154"/>
-      <c r="BZ106" s="154"/>
-      <c r="CA106" s="154"/>
-      <c r="CB106" s="154"/>
-      <c r="CC106" s="154"/>
-      <c r="CD106" s="154"/>
-      <c r="CE106" s="154"/>
-      <c r="CF106" s="154"/>
-      <c r="CG106" s="154"/>
-      <c r="CH106" s="154"/>
-      <c r="CI106" s="154"/>
-      <c r="CJ106" s="154"/>
-      <c r="CK106" s="154"/>
-      <c r="CL106" s="154"/>
-      <c r="CM106" s="154"/>
-      <c r="CN106" s="154"/>
-      <c r="CO106" s="154"/>
-      <c r="CP106" s="154"/>
-      <c r="CQ106" s="154"/>
-      <c r="CR106" s="154"/>
+      <c r="BK106" s="177"/>
+      <c r="BL106" s="177"/>
+      <c r="BM106" s="177"/>
+      <c r="BN106" s="177"/>
+      <c r="BO106" s="177"/>
+      <c r="BP106" s="177"/>
+      <c r="BQ106" s="177"/>
+      <c r="BR106" s="177"/>
+      <c r="BS106" s="177"/>
+      <c r="BT106" s="177"/>
+      <c r="BU106" s="177"/>
+      <c r="BW106" s="181"/>
+      <c r="BX106" s="181"/>
+      <c r="BY106" s="181"/>
+      <c r="BZ106" s="181"/>
+      <c r="CA106" s="181"/>
+      <c r="CB106" s="181"/>
+      <c r="CC106" s="181"/>
+      <c r="CD106" s="181"/>
+      <c r="CE106" s="181"/>
+      <c r="CF106" s="181"/>
+      <c r="CG106" s="181"/>
+      <c r="CH106" s="181"/>
+      <c r="CI106" s="181"/>
+      <c r="CJ106" s="181"/>
+      <c r="CK106" s="181"/>
+      <c r="CL106" s="181"/>
+      <c r="CM106" s="181"/>
+      <c r="CN106" s="181"/>
+      <c r="CO106" s="181"/>
+      <c r="CP106" s="181"/>
+      <c r="CQ106" s="181"/>
+      <c r="CR106" s="181"/>
       <c r="CS106" s="36"/>
     </row>
     <row r="107" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -39215,107 +39215,107 @@
       <c r="AJ107" s="57"/>
       <c r="AL107" s="55"/>
       <c r="BI107" s="35"/>
-      <c r="BK107" s="153"/>
-      <c r="BL107" s="153"/>
-      <c r="BM107" s="153"/>
-      <c r="BN107" s="153"/>
-      <c r="BO107" s="153"/>
-      <c r="BP107" s="153"/>
-      <c r="BQ107" s="153"/>
-      <c r="BR107" s="153"/>
-      <c r="BS107" s="153"/>
-      <c r="BT107" s="153"/>
-      <c r="BU107" s="153"/>
-      <c r="BW107" s="154"/>
-      <c r="BX107" s="154"/>
-      <c r="BY107" s="154"/>
-      <c r="BZ107" s="154"/>
-      <c r="CA107" s="154"/>
-      <c r="CB107" s="154"/>
-      <c r="CC107" s="154"/>
-      <c r="CD107" s="154"/>
-      <c r="CE107" s="154"/>
-      <c r="CF107" s="154"/>
-      <c r="CG107" s="154"/>
-      <c r="CH107" s="154"/>
-      <c r="CI107" s="154"/>
-      <c r="CJ107" s="154"/>
-      <c r="CK107" s="154"/>
-      <c r="CL107" s="154"/>
-      <c r="CM107" s="154"/>
-      <c r="CN107" s="154"/>
-      <c r="CO107" s="154"/>
-      <c r="CP107" s="154"/>
-      <c r="CQ107" s="154"/>
-      <c r="CR107" s="154"/>
+      <c r="BK107" s="177"/>
+      <c r="BL107" s="177"/>
+      <c r="BM107" s="177"/>
+      <c r="BN107" s="177"/>
+      <c r="BO107" s="177"/>
+      <c r="BP107" s="177"/>
+      <c r="BQ107" s="177"/>
+      <c r="BR107" s="177"/>
+      <c r="BS107" s="177"/>
+      <c r="BT107" s="177"/>
+      <c r="BU107" s="177"/>
+      <c r="BW107" s="181"/>
+      <c r="BX107" s="181"/>
+      <c r="BY107" s="181"/>
+      <c r="BZ107" s="181"/>
+      <c r="CA107" s="181"/>
+      <c r="CB107" s="181"/>
+      <c r="CC107" s="181"/>
+      <c r="CD107" s="181"/>
+      <c r="CE107" s="181"/>
+      <c r="CF107" s="181"/>
+      <c r="CG107" s="181"/>
+      <c r="CH107" s="181"/>
+      <c r="CI107" s="181"/>
+      <c r="CJ107" s="181"/>
+      <c r="CK107" s="181"/>
+      <c r="CL107" s="181"/>
+      <c r="CM107" s="181"/>
+      <c r="CN107" s="181"/>
+      <c r="CO107" s="181"/>
+      <c r="CP107" s="181"/>
+      <c r="CQ107" s="181"/>
+      <c r="CR107" s="181"/>
       <c r="CS107" s="36"/>
     </row>
     <row r="108" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="48"/>
-      <c r="D108" s="153" t="s">
+      <c r="D108" s="177" t="s">
         <v>294</v>
       </c>
-      <c r="E108" s="153"/>
-      <c r="F108" s="153"/>
-      <c r="G108" s="153"/>
-      <c r="H108" s="153"/>
-      <c r="I108" s="153"/>
-      <c r="J108" s="153"/>
-      <c r="K108" s="153"/>
-      <c r="L108" s="153"/>
-      <c r="M108" s="153"/>
-      <c r="N108" s="153"/>
-      <c r="O108" s="153"/>
-      <c r="P108" s="153"/>
-      <c r="Q108" s="155"/>
-      <c r="R108" s="155"/>
-      <c r="S108" s="155"/>
-      <c r="T108" s="155"/>
-      <c r="U108" s="155"/>
-      <c r="V108" s="155"/>
-      <c r="X108" s="156" t="s">
+      <c r="E108" s="177"/>
+      <c r="F108" s="177"/>
+      <c r="G108" s="177"/>
+      <c r="H108" s="177"/>
+      <c r="I108" s="177"/>
+      <c r="J108" s="177"/>
+      <c r="K108" s="177"/>
+      <c r="L108" s="177"/>
+      <c r="M108" s="177"/>
+      <c r="N108" s="177"/>
+      <c r="O108" s="177"/>
+      <c r="P108" s="177"/>
+      <c r="Q108" s="178"/>
+      <c r="R108" s="178"/>
+      <c r="S108" s="178"/>
+      <c r="T108" s="178"/>
+      <c r="U108" s="178"/>
+      <c r="V108" s="178"/>
+      <c r="X108" s="179" t="s">
         <v>295</v>
       </c>
-      <c r="Y108" s="156"/>
-      <c r="Z108" s="156"/>
-      <c r="AA108" s="156"/>
-      <c r="AB108" s="156"/>
-      <c r="AC108" s="156"/>
-      <c r="AD108" s="156"/>
-      <c r="AE108" s="156"/>
-      <c r="AF108" s="156"/>
-      <c r="AG108" s="156"/>
-      <c r="AH108" s="156"/>
-      <c r="AI108" s="156"/>
+      <c r="Y108" s="179"/>
+      <c r="Z108" s="179"/>
+      <c r="AA108" s="179"/>
+      <c r="AB108" s="179"/>
+      <c r="AC108" s="179"/>
+      <c r="AD108" s="179"/>
+      <c r="AE108" s="179"/>
+      <c r="AF108" s="179"/>
+      <c r="AG108" s="179"/>
+      <c r="AH108" s="179"/>
+      <c r="AI108" s="179"/>
       <c r="AJ108" s="57"/>
-      <c r="AL108" s="153" t="s">
+      <c r="AL108" s="177" t="s">
         <v>34</v>
       </c>
-      <c r="AM108" s="153"/>
-      <c r="AN108" s="153"/>
-      <c r="AO108" s="153"/>
-      <c r="AP108" s="153"/>
-      <c r="AQ108" s="153"/>
-      <c r="AR108" s="153"/>
-      <c r="AS108" s="153"/>
-      <c r="AT108" s="153"/>
-      <c r="AU108" s="153"/>
-      <c r="AV108" s="153"/>
-      <c r="AW108" s="153"/>
-      <c r="AX108" s="153"/>
-      <c r="AY108" s="157" t="str">
+      <c r="AM108" s="177"/>
+      <c r="AN108" s="177"/>
+      <c r="AO108" s="177"/>
+      <c r="AP108" s="177"/>
+      <c r="AQ108" s="177"/>
+      <c r="AR108" s="177"/>
+      <c r="AS108" s="177"/>
+      <c r="AT108" s="177"/>
+      <c r="AU108" s="177"/>
+      <c r="AV108" s="177"/>
+      <c r="AW108" s="177"/>
+      <c r="AX108" s="177"/>
+      <c r="AY108" s="180" t="str">
         <f>TEXT(INDEX('4. Forecast'!$D$50:$F$50,MATCH($BH$4,'4. Forecast'!$D$45:$F$45,0)),"0.0")&amp;" months"</f>
         <v>13.8 months</v>
       </c>
-      <c r="AZ108" s="157"/>
-      <c r="BA108" s="157"/>
-      <c r="BB108" s="157"/>
-      <c r="BC108" s="157"/>
-      <c r="BD108" s="157"/>
-      <c r="BE108" s="157"/>
-      <c r="BF108" s="157"/>
-      <c r="BG108" s="157"/>
-      <c r="BH108" s="157"/>
+      <c r="AZ108" s="180"/>
+      <c r="BA108" s="180"/>
+      <c r="BB108" s="180"/>
+      <c r="BC108" s="180"/>
+      <c r="BD108" s="180"/>
+      <c r="BE108" s="180"/>
+      <c r="BF108" s="180"/>
+      <c r="BG108" s="180"/>
+      <c r="BH108" s="180"/>
       <c r="BI108" s="35"/>
       <c r="BW108" s="11"/>
       <c r="BX108" s="11"/>
@@ -39343,101 +39343,101 @@
     </row>
     <row r="109" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="48"/>
-      <c r="D109" s="153"/>
-      <c r="E109" s="153"/>
-      <c r="F109" s="153"/>
-      <c r="G109" s="153"/>
-      <c r="H109" s="153"/>
-      <c r="I109" s="153"/>
-      <c r="J109" s="153"/>
-      <c r="K109" s="153"/>
-      <c r="L109" s="153"/>
-      <c r="M109" s="153"/>
-      <c r="N109" s="153"/>
-      <c r="O109" s="153"/>
-      <c r="P109" s="153"/>
-      <c r="Q109" s="155"/>
-      <c r="R109" s="155"/>
-      <c r="S109" s="155"/>
-      <c r="T109" s="155"/>
-      <c r="U109" s="155"/>
-      <c r="V109" s="155"/>
-      <c r="X109" s="156"/>
-      <c r="Y109" s="156"/>
-      <c r="Z109" s="156"/>
-      <c r="AA109" s="156"/>
-      <c r="AB109" s="156"/>
-      <c r="AC109" s="156"/>
-      <c r="AD109" s="156"/>
-      <c r="AE109" s="156"/>
-      <c r="AF109" s="156"/>
-      <c r="AG109" s="156"/>
-      <c r="AH109" s="156"/>
-      <c r="AI109" s="156"/>
+      <c r="D109" s="177"/>
+      <c r="E109" s="177"/>
+      <c r="F109" s="177"/>
+      <c r="G109" s="177"/>
+      <c r="H109" s="177"/>
+      <c r="I109" s="177"/>
+      <c r="J109" s="177"/>
+      <c r="K109" s="177"/>
+      <c r="L109" s="177"/>
+      <c r="M109" s="177"/>
+      <c r="N109" s="177"/>
+      <c r="O109" s="177"/>
+      <c r="P109" s="177"/>
+      <c r="Q109" s="178"/>
+      <c r="R109" s="178"/>
+      <c r="S109" s="178"/>
+      <c r="T109" s="178"/>
+      <c r="U109" s="178"/>
+      <c r="V109" s="178"/>
+      <c r="X109" s="179"/>
+      <c r="Y109" s="179"/>
+      <c r="Z109" s="179"/>
+      <c r="AA109" s="179"/>
+      <c r="AB109" s="179"/>
+      <c r="AC109" s="179"/>
+      <c r="AD109" s="179"/>
+      <c r="AE109" s="179"/>
+      <c r="AF109" s="179"/>
+      <c r="AG109" s="179"/>
+      <c r="AH109" s="179"/>
+      <c r="AI109" s="179"/>
       <c r="AJ109" s="57"/>
-      <c r="AL109" s="153"/>
-      <c r="AM109" s="153"/>
-      <c r="AN109" s="153"/>
-      <c r="AO109" s="153"/>
-      <c r="AP109" s="153"/>
-      <c r="AQ109" s="153"/>
-      <c r="AR109" s="153"/>
-      <c r="AS109" s="153"/>
-      <c r="AT109" s="153"/>
-      <c r="AU109" s="153"/>
-      <c r="AV109" s="153"/>
-      <c r="AW109" s="153"/>
-      <c r="AX109" s="153"/>
-      <c r="AY109" s="157"/>
-      <c r="AZ109" s="157"/>
-      <c r="BA109" s="157"/>
-      <c r="BB109" s="157"/>
-      <c r="BC109" s="157"/>
-      <c r="BD109" s="157"/>
-      <c r="BE109" s="157"/>
-      <c r="BF109" s="157"/>
-      <c r="BG109" s="157"/>
-      <c r="BH109" s="157"/>
+      <c r="AL109" s="177"/>
+      <c r="AM109" s="177"/>
+      <c r="AN109" s="177"/>
+      <c r="AO109" s="177"/>
+      <c r="AP109" s="177"/>
+      <c r="AQ109" s="177"/>
+      <c r="AR109" s="177"/>
+      <c r="AS109" s="177"/>
+      <c r="AT109" s="177"/>
+      <c r="AU109" s="177"/>
+      <c r="AV109" s="177"/>
+      <c r="AW109" s="177"/>
+      <c r="AX109" s="177"/>
+      <c r="AY109" s="180"/>
+      <c r="AZ109" s="180"/>
+      <c r="BA109" s="180"/>
+      <c r="BB109" s="180"/>
+      <c r="BC109" s="180"/>
+      <c r="BD109" s="180"/>
+      <c r="BE109" s="180"/>
+      <c r="BF109" s="180"/>
+      <c r="BG109" s="180"/>
+      <c r="BH109" s="180"/>
       <c r="BI109" s="35"/>
-      <c r="BK109" s="153" t="str">
+      <c r="BK109" s="177" t="str">
         <f>"Cost per manual touch  ·  we assume ₹"&amp;TEXT(INDEX('1. Assumptions and Sources'!$D$55:$F$55,MATCH($BH$4,'1. Assumptions and Sources'!$D$53:$F$53,0)),"0")</f>
         <v>Cost per manual touch  ·  we assume ₹200</v>
       </c>
-      <c r="BL109" s="153"/>
-      <c r="BM109" s="153"/>
-      <c r="BN109" s="153"/>
-      <c r="BO109" s="153"/>
-      <c r="BP109" s="153"/>
-      <c r="BQ109" s="153"/>
-      <c r="BR109" s="153"/>
-      <c r="BS109" s="153"/>
-      <c r="BT109" s="153"/>
-      <c r="BU109" s="153"/>
-      <c r="BW109" s="154" t="str">
+      <c r="BL109" s="177"/>
+      <c r="BM109" s="177"/>
+      <c r="BN109" s="177"/>
+      <c r="BO109" s="177"/>
+      <c r="BP109" s="177"/>
+      <c r="BQ109" s="177"/>
+      <c r="BR109" s="177"/>
+      <c r="BS109" s="177"/>
+      <c r="BT109" s="177"/>
+      <c r="BU109" s="177"/>
+      <c r="BW109" s="181" t="str">
         <f>"Breaks at "&amp;TEXT(INDEX('3. Workings'!$D$140:$F$140,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0")&amp;"   ·   "&amp;IF(INDEX('3. Workings'!$D$141:$F$141,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0))&gt;0,TEXT(INDEX('3. Workings'!$D$141:$F$141,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;" cushion","NO cushion at this plan")</f>
         <v>Breaks at 63   ·   75% cushion</v>
       </c>
-      <c r="BX109" s="154"/>
-      <c r="BY109" s="154"/>
-      <c r="BZ109" s="154"/>
-      <c r="CA109" s="154"/>
-      <c r="CB109" s="154"/>
-      <c r="CC109" s="154"/>
-      <c r="CD109" s="154"/>
-      <c r="CE109" s="154"/>
-      <c r="CF109" s="154"/>
-      <c r="CG109" s="154"/>
-      <c r="CH109" s="154"/>
-      <c r="CI109" s="154"/>
-      <c r="CJ109" s="154"/>
-      <c r="CK109" s="154"/>
-      <c r="CL109" s="154"/>
-      <c r="CM109" s="154"/>
-      <c r="CN109" s="154"/>
-      <c r="CO109" s="154"/>
-      <c r="CP109" s="154"/>
-      <c r="CQ109" s="154"/>
-      <c r="CR109" s="154"/>
+      <c r="BX109" s="181"/>
+      <c r="BY109" s="181"/>
+      <c r="BZ109" s="181"/>
+      <c r="CA109" s="181"/>
+      <c r="CB109" s="181"/>
+      <c r="CC109" s="181"/>
+      <c r="CD109" s="181"/>
+      <c r="CE109" s="181"/>
+      <c r="CF109" s="181"/>
+      <c r="CG109" s="181"/>
+      <c r="CH109" s="181"/>
+      <c r="CI109" s="181"/>
+      <c r="CJ109" s="181"/>
+      <c r="CK109" s="181"/>
+      <c r="CL109" s="181"/>
+      <c r="CM109" s="181"/>
+      <c r="CN109" s="181"/>
+      <c r="CO109" s="181"/>
+      <c r="CP109" s="181"/>
+      <c r="CQ109" s="181"/>
+      <c r="CR109" s="181"/>
       <c r="CS109" s="36"/>
     </row>
     <row r="110" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -39450,200 +39450,200 @@
       <c r="AI110" s="39"/>
       <c r="AJ110" s="57"/>
       <c r="BI110" s="35"/>
-      <c r="BK110" s="153"/>
-      <c r="BL110" s="153"/>
-      <c r="BM110" s="153"/>
-      <c r="BN110" s="153"/>
-      <c r="BO110" s="153"/>
-      <c r="BP110" s="153"/>
-      <c r="BQ110" s="153"/>
-      <c r="BR110" s="153"/>
-      <c r="BS110" s="153"/>
-      <c r="BT110" s="153"/>
-      <c r="BU110" s="153"/>
-      <c r="BW110" s="154"/>
-      <c r="BX110" s="154"/>
-      <c r="BY110" s="154"/>
-      <c r="BZ110" s="154"/>
-      <c r="CA110" s="154"/>
-      <c r="CB110" s="154"/>
-      <c r="CC110" s="154"/>
-      <c r="CD110" s="154"/>
-      <c r="CE110" s="154"/>
-      <c r="CF110" s="154"/>
-      <c r="CG110" s="154"/>
-      <c r="CH110" s="154"/>
-      <c r="CI110" s="154"/>
-      <c r="CJ110" s="154"/>
-      <c r="CK110" s="154"/>
-      <c r="CL110" s="154"/>
-      <c r="CM110" s="154"/>
-      <c r="CN110" s="154"/>
-      <c r="CO110" s="154"/>
-      <c r="CP110" s="154"/>
-      <c r="CQ110" s="154"/>
-      <c r="CR110" s="154"/>
+      <c r="BK110" s="177"/>
+      <c r="BL110" s="177"/>
+      <c r="BM110" s="177"/>
+      <c r="BN110" s="177"/>
+      <c r="BO110" s="177"/>
+      <c r="BP110" s="177"/>
+      <c r="BQ110" s="177"/>
+      <c r="BR110" s="177"/>
+      <c r="BS110" s="177"/>
+      <c r="BT110" s="177"/>
+      <c r="BU110" s="177"/>
+      <c r="BW110" s="181"/>
+      <c r="BX110" s="181"/>
+      <c r="BY110" s="181"/>
+      <c r="BZ110" s="181"/>
+      <c r="CA110" s="181"/>
+      <c r="CB110" s="181"/>
+      <c r="CC110" s="181"/>
+      <c r="CD110" s="181"/>
+      <c r="CE110" s="181"/>
+      <c r="CF110" s="181"/>
+      <c r="CG110" s="181"/>
+      <c r="CH110" s="181"/>
+      <c r="CI110" s="181"/>
+      <c r="CJ110" s="181"/>
+      <c r="CK110" s="181"/>
+      <c r="CL110" s="181"/>
+      <c r="CM110" s="181"/>
+      <c r="CN110" s="181"/>
+      <c r="CO110" s="181"/>
+      <c r="CP110" s="181"/>
+      <c r="CQ110" s="181"/>
+      <c r="CR110" s="181"/>
       <c r="CS110" s="36"/>
     </row>
     <row r="111" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="48"/>
-      <c r="D111" s="153" t="s">
+      <c r="D111" s="177" t="s">
         <v>296</v>
       </c>
-      <c r="E111" s="153"/>
-      <c r="F111" s="153"/>
-      <c r="G111" s="153"/>
-      <c r="H111" s="153"/>
-      <c r="I111" s="153"/>
-      <c r="J111" s="153"/>
-      <c r="K111" s="153"/>
-      <c r="L111" s="153"/>
-      <c r="M111" s="153"/>
-      <c r="N111" s="153"/>
-      <c r="O111" s="153"/>
-      <c r="P111" s="153"/>
-      <c r="Q111" s="155"/>
-      <c r="R111" s="155"/>
-      <c r="S111" s="155"/>
-      <c r="T111" s="155"/>
-      <c r="U111" s="155"/>
-      <c r="V111" s="155"/>
-      <c r="X111" s="156" t="s">
+      <c r="E111" s="177"/>
+      <c r="F111" s="177"/>
+      <c r="G111" s="177"/>
+      <c r="H111" s="177"/>
+      <c r="I111" s="177"/>
+      <c r="J111" s="177"/>
+      <c r="K111" s="177"/>
+      <c r="L111" s="177"/>
+      <c r="M111" s="177"/>
+      <c r="N111" s="177"/>
+      <c r="O111" s="177"/>
+      <c r="P111" s="177"/>
+      <c r="Q111" s="178"/>
+      <c r="R111" s="178"/>
+      <c r="S111" s="178"/>
+      <c r="T111" s="178"/>
+      <c r="U111" s="178"/>
+      <c r="V111" s="178"/>
+      <c r="X111" s="179" t="s">
         <v>297</v>
       </c>
-      <c r="Y111" s="156"/>
-      <c r="Z111" s="156"/>
-      <c r="AA111" s="156"/>
-      <c r="AB111" s="156"/>
-      <c r="AC111" s="156"/>
-      <c r="AD111" s="156"/>
-      <c r="AE111" s="156"/>
-      <c r="AF111" s="156"/>
-      <c r="AG111" s="156"/>
-      <c r="AH111" s="156"/>
-      <c r="AI111" s="156"/>
+      <c r="Y111" s="179"/>
+      <c r="Z111" s="179"/>
+      <c r="AA111" s="179"/>
+      <c r="AB111" s="179"/>
+      <c r="AC111" s="179"/>
+      <c r="AD111" s="179"/>
+      <c r="AE111" s="179"/>
+      <c r="AF111" s="179"/>
+      <c r="AG111" s="179"/>
+      <c r="AH111" s="179"/>
+      <c r="AI111" s="179"/>
       <c r="AJ111" s="35"/>
-      <c r="AL111" s="153" t="s">
+      <c r="AL111" s="177" t="s">
         <v>298</v>
       </c>
-      <c r="AM111" s="153"/>
-      <c r="AN111" s="153"/>
-      <c r="AO111" s="153"/>
-      <c r="AP111" s="153"/>
-      <c r="AQ111" s="153"/>
-      <c r="AR111" s="153"/>
-      <c r="AS111" s="153"/>
-      <c r="AT111" s="153"/>
-      <c r="AU111" s="153"/>
-      <c r="AV111" s="153"/>
-      <c r="AW111" s="153"/>
-      <c r="AX111" s="153"/>
-      <c r="AY111" s="157" t="str">
+      <c r="AM111" s="177"/>
+      <c r="AN111" s="177"/>
+      <c r="AO111" s="177"/>
+      <c r="AP111" s="177"/>
+      <c r="AQ111" s="177"/>
+      <c r="AR111" s="177"/>
+      <c r="AS111" s="177"/>
+      <c r="AT111" s="177"/>
+      <c r="AU111" s="177"/>
+      <c r="AV111" s="177"/>
+      <c r="AW111" s="177"/>
+      <c r="AX111" s="177"/>
+      <c r="AY111" s="180" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$96:$F$96,MATCH($BH$4,'3. Workings'!$D$89:$F$89,0)),"0.0")&amp;" months"</f>
         <v>4.2 months</v>
       </c>
-      <c r="AZ111" s="157"/>
-      <c r="BA111" s="157"/>
-      <c r="BB111" s="157"/>
-      <c r="BC111" s="157"/>
-      <c r="BD111" s="157"/>
-      <c r="BE111" s="157"/>
-      <c r="BF111" s="157"/>
-      <c r="BG111" s="157"/>
-      <c r="BH111" s="157"/>
+      <c r="AZ111" s="180"/>
+      <c r="BA111" s="180"/>
+      <c r="BB111" s="180"/>
+      <c r="BC111" s="180"/>
+      <c r="BD111" s="180"/>
+      <c r="BE111" s="180"/>
+      <c r="BF111" s="180"/>
+      <c r="BG111" s="180"/>
+      <c r="BH111" s="180"/>
       <c r="BI111" s="35"/>
-      <c r="BK111" s="153"/>
-      <c r="BL111" s="153"/>
-      <c r="BM111" s="153"/>
-      <c r="BN111" s="153"/>
-      <c r="BO111" s="153"/>
-      <c r="BP111" s="153"/>
-      <c r="BQ111" s="153"/>
-      <c r="BR111" s="153"/>
-      <c r="BS111" s="153"/>
-      <c r="BT111" s="153"/>
-      <c r="BU111" s="153"/>
-      <c r="BW111" s="154"/>
-      <c r="BX111" s="154"/>
-      <c r="BY111" s="154"/>
-      <c r="BZ111" s="154"/>
-      <c r="CA111" s="154"/>
-      <c r="CB111" s="154"/>
-      <c r="CC111" s="154"/>
-      <c r="CD111" s="154"/>
-      <c r="CE111" s="154"/>
-      <c r="CF111" s="154"/>
-      <c r="CG111" s="154"/>
-      <c r="CH111" s="154"/>
-      <c r="CI111" s="154"/>
-      <c r="CJ111" s="154"/>
-      <c r="CK111" s="154"/>
-      <c r="CL111" s="154"/>
-      <c r="CM111" s="154"/>
-      <c r="CN111" s="154"/>
-      <c r="CO111" s="154"/>
-      <c r="CP111" s="154"/>
-      <c r="CQ111" s="154"/>
-      <c r="CR111" s="154"/>
+      <c r="BK111" s="177"/>
+      <c r="BL111" s="177"/>
+      <c r="BM111" s="177"/>
+      <c r="BN111" s="177"/>
+      <c r="BO111" s="177"/>
+      <c r="BP111" s="177"/>
+      <c r="BQ111" s="177"/>
+      <c r="BR111" s="177"/>
+      <c r="BS111" s="177"/>
+      <c r="BT111" s="177"/>
+      <c r="BU111" s="177"/>
+      <c r="BW111" s="181"/>
+      <c r="BX111" s="181"/>
+      <c r="BY111" s="181"/>
+      <c r="BZ111" s="181"/>
+      <c r="CA111" s="181"/>
+      <c r="CB111" s="181"/>
+      <c r="CC111" s="181"/>
+      <c r="CD111" s="181"/>
+      <c r="CE111" s="181"/>
+      <c r="CF111" s="181"/>
+      <c r="CG111" s="181"/>
+      <c r="CH111" s="181"/>
+      <c r="CI111" s="181"/>
+      <c r="CJ111" s="181"/>
+      <c r="CK111" s="181"/>
+      <c r="CL111" s="181"/>
+      <c r="CM111" s="181"/>
+      <c r="CN111" s="181"/>
+      <c r="CO111" s="181"/>
+      <c r="CP111" s="181"/>
+      <c r="CQ111" s="181"/>
+      <c r="CR111" s="181"/>
       <c r="CS111" s="36"/>
     </row>
     <row r="112" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="48"/>
-      <c r="D112" s="153"/>
-      <c r="E112" s="153"/>
-      <c r="F112" s="153"/>
-      <c r="G112" s="153"/>
-      <c r="H112" s="153"/>
-      <c r="I112" s="153"/>
-      <c r="J112" s="153"/>
-      <c r="K112" s="153"/>
-      <c r="L112" s="153"/>
-      <c r="M112" s="153"/>
-      <c r="N112" s="153"/>
-      <c r="O112" s="153"/>
-      <c r="P112" s="153"/>
-      <c r="Q112" s="155"/>
-      <c r="R112" s="155"/>
-      <c r="S112" s="155"/>
-      <c r="T112" s="155"/>
-      <c r="U112" s="155"/>
-      <c r="V112" s="155"/>
-      <c r="X112" s="156"/>
-      <c r="Y112" s="156"/>
-      <c r="Z112" s="156"/>
-      <c r="AA112" s="156"/>
-      <c r="AB112" s="156"/>
-      <c r="AC112" s="156"/>
-      <c r="AD112" s="156"/>
-      <c r="AE112" s="156"/>
-      <c r="AF112" s="156"/>
-      <c r="AG112" s="156"/>
-      <c r="AH112" s="156"/>
-      <c r="AI112" s="156"/>
+      <c r="D112" s="177"/>
+      <c r="E112" s="177"/>
+      <c r="F112" s="177"/>
+      <c r="G112" s="177"/>
+      <c r="H112" s="177"/>
+      <c r="I112" s="177"/>
+      <c r="J112" s="177"/>
+      <c r="K112" s="177"/>
+      <c r="L112" s="177"/>
+      <c r="M112" s="177"/>
+      <c r="N112" s="177"/>
+      <c r="O112" s="177"/>
+      <c r="P112" s="177"/>
+      <c r="Q112" s="178"/>
+      <c r="R112" s="178"/>
+      <c r="S112" s="178"/>
+      <c r="T112" s="178"/>
+      <c r="U112" s="178"/>
+      <c r="V112" s="178"/>
+      <c r="X112" s="179"/>
+      <c r="Y112" s="179"/>
+      <c r="Z112" s="179"/>
+      <c r="AA112" s="179"/>
+      <c r="AB112" s="179"/>
+      <c r="AC112" s="179"/>
+      <c r="AD112" s="179"/>
+      <c r="AE112" s="179"/>
+      <c r="AF112" s="179"/>
+      <c r="AG112" s="179"/>
+      <c r="AH112" s="179"/>
+      <c r="AI112" s="179"/>
       <c r="AJ112" s="35"/>
-      <c r="AL112" s="153"/>
-      <c r="AM112" s="153"/>
-      <c r="AN112" s="153"/>
-      <c r="AO112" s="153"/>
-      <c r="AP112" s="153"/>
-      <c r="AQ112" s="153"/>
-      <c r="AR112" s="153"/>
-      <c r="AS112" s="153"/>
-      <c r="AT112" s="153"/>
-      <c r="AU112" s="153"/>
-      <c r="AV112" s="153"/>
-      <c r="AW112" s="153"/>
-      <c r="AX112" s="153"/>
-      <c r="AY112" s="157"/>
-      <c r="AZ112" s="157"/>
-      <c r="BA112" s="157"/>
-      <c r="BB112" s="157"/>
-      <c r="BC112" s="157"/>
-      <c r="BD112" s="157"/>
-      <c r="BE112" s="157"/>
-      <c r="BF112" s="157"/>
-      <c r="BG112" s="157"/>
-      <c r="BH112" s="157"/>
+      <c r="AL112" s="177"/>
+      <c r="AM112" s="177"/>
+      <c r="AN112" s="177"/>
+      <c r="AO112" s="177"/>
+      <c r="AP112" s="177"/>
+      <c r="AQ112" s="177"/>
+      <c r="AR112" s="177"/>
+      <c r="AS112" s="177"/>
+      <c r="AT112" s="177"/>
+      <c r="AU112" s="177"/>
+      <c r="AV112" s="177"/>
+      <c r="AW112" s="177"/>
+      <c r="AX112" s="177"/>
+      <c r="AY112" s="180"/>
+      <c r="AZ112" s="180"/>
+      <c r="BA112" s="180"/>
+      <c r="BB112" s="180"/>
+      <c r="BC112" s="180"/>
+      <c r="BD112" s="180"/>
+      <c r="BE112" s="180"/>
+      <c r="BF112" s="180"/>
+      <c r="BG112" s="180"/>
+      <c r="BH112" s="180"/>
       <c r="BI112" s="35"/>
       <c r="BW112" s="11"/>
       <c r="BX112" s="11"/>
@@ -39673,240 +39673,240 @@
       <c r="C113" s="48"/>
       <c r="AJ113" s="35"/>
       <c r="BI113" s="35"/>
-      <c r="BK113" s="153" t="str">
+      <c r="BK113" s="177" t="str">
         <f>"Rollout of the book  ·  we plan "&amp;TEXT(INDEX('3. Workings'!$D$12:$F$12,MATCH($BH$4,'3. Workings'!$D$6:$F$6,0)),"0%")</f>
         <v>Rollout of the book  ·  we plan 100%</v>
       </c>
-      <c r="BL113" s="153"/>
-      <c r="BM113" s="153"/>
-      <c r="BN113" s="153"/>
-      <c r="BO113" s="153"/>
-      <c r="BP113" s="153"/>
-      <c r="BQ113" s="153"/>
-      <c r="BR113" s="153"/>
-      <c r="BS113" s="153"/>
-      <c r="BT113" s="153"/>
-      <c r="BU113" s="153"/>
-      <c r="BW113" s="154" t="str">
+      <c r="BL113" s="177"/>
+      <c r="BM113" s="177"/>
+      <c r="BN113" s="177"/>
+      <c r="BO113" s="177"/>
+      <c r="BP113" s="177"/>
+      <c r="BQ113" s="177"/>
+      <c r="BR113" s="177"/>
+      <c r="BS113" s="177"/>
+      <c r="BT113" s="177"/>
+      <c r="BU113" s="177"/>
+      <c r="BW113" s="181" t="str">
         <f>"Breaks at "&amp;TEXT(INDEX('3. Workings'!$D$142:$F$142,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;"   ·   "&amp;IF(INDEX('3. Workings'!$D$143:$F$143,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0))&gt;0,TEXT(INDEX('3. Workings'!$D$143:$F$143,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;" cushion","NO cushion at this plan")</f>
         <v>Breaks at 31%   ·   69% cushion</v>
       </c>
-      <c r="BX113" s="154"/>
-      <c r="BY113" s="154"/>
-      <c r="BZ113" s="154"/>
-      <c r="CA113" s="154"/>
-      <c r="CB113" s="154"/>
-      <c r="CC113" s="154"/>
-      <c r="CD113" s="154"/>
-      <c r="CE113" s="154"/>
-      <c r="CF113" s="154"/>
-      <c r="CG113" s="154"/>
-      <c r="CH113" s="154"/>
-      <c r="CI113" s="154"/>
-      <c r="CJ113" s="154"/>
-      <c r="CK113" s="154"/>
-      <c r="CL113" s="154"/>
-      <c r="CM113" s="154"/>
-      <c r="CN113" s="154"/>
-      <c r="CO113" s="154"/>
-      <c r="CP113" s="154"/>
-      <c r="CQ113" s="154"/>
-      <c r="CR113" s="154"/>
+      <c r="BX113" s="181"/>
+      <c r="BY113" s="181"/>
+      <c r="BZ113" s="181"/>
+      <c r="CA113" s="181"/>
+      <c r="CB113" s="181"/>
+      <c r="CC113" s="181"/>
+      <c r="CD113" s="181"/>
+      <c r="CE113" s="181"/>
+      <c r="CF113" s="181"/>
+      <c r="CG113" s="181"/>
+      <c r="CH113" s="181"/>
+      <c r="CI113" s="181"/>
+      <c r="CJ113" s="181"/>
+      <c r="CK113" s="181"/>
+      <c r="CL113" s="181"/>
+      <c r="CM113" s="181"/>
+      <c r="CN113" s="181"/>
+      <c r="CO113" s="181"/>
+      <c r="CP113" s="181"/>
+      <c r="CQ113" s="181"/>
+      <c r="CR113" s="181"/>
       <c r="CS113" s="36"/>
     </row>
     <row r="114" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="48"/>
-      <c r="D114" s="153" t="s">
+      <c r="D114" s="177" t="s">
         <v>299</v>
       </c>
-      <c r="E114" s="153"/>
-      <c r="F114" s="153"/>
-      <c r="G114" s="153"/>
-      <c r="H114" s="153"/>
-      <c r="I114" s="153"/>
-      <c r="J114" s="153"/>
-      <c r="K114" s="153"/>
-      <c r="L114" s="153"/>
-      <c r="M114" s="153"/>
-      <c r="N114" s="153"/>
-      <c r="O114" s="153"/>
-      <c r="P114" s="153"/>
-      <c r="Q114" s="155"/>
-      <c r="R114" s="155"/>
-      <c r="S114" s="155"/>
-      <c r="T114" s="155"/>
-      <c r="U114" s="155"/>
-      <c r="V114" s="155"/>
-      <c r="X114" s="156" t="s">
+      <c r="E114" s="177"/>
+      <c r="F114" s="177"/>
+      <c r="G114" s="177"/>
+      <c r="H114" s="177"/>
+      <c r="I114" s="177"/>
+      <c r="J114" s="177"/>
+      <c r="K114" s="177"/>
+      <c r="L114" s="177"/>
+      <c r="M114" s="177"/>
+      <c r="N114" s="177"/>
+      <c r="O114" s="177"/>
+      <c r="P114" s="177"/>
+      <c r="Q114" s="178"/>
+      <c r="R114" s="178"/>
+      <c r="S114" s="178"/>
+      <c r="T114" s="178"/>
+      <c r="U114" s="178"/>
+      <c r="V114" s="178"/>
+      <c r="X114" s="179" t="s">
         <v>300</v>
       </c>
-      <c r="Y114" s="156"/>
-      <c r="Z114" s="156"/>
-      <c r="AA114" s="156"/>
-      <c r="AB114" s="156"/>
-      <c r="AC114" s="156"/>
-      <c r="AD114" s="156"/>
-      <c r="AE114" s="156"/>
-      <c r="AF114" s="156"/>
-      <c r="AG114" s="156"/>
-      <c r="AH114" s="156"/>
-      <c r="AI114" s="156"/>
+      <c r="Y114" s="179"/>
+      <c r="Z114" s="179"/>
+      <c r="AA114" s="179"/>
+      <c r="AB114" s="179"/>
+      <c r="AC114" s="179"/>
+      <c r="AD114" s="179"/>
+      <c r="AE114" s="179"/>
+      <c r="AF114" s="179"/>
+      <c r="AG114" s="179"/>
+      <c r="AH114" s="179"/>
+      <c r="AI114" s="179"/>
       <c r="AJ114" s="35"/>
-      <c r="AL114" s="153" t="s">
+      <c r="AL114" s="177" t="s">
         <v>301</v>
       </c>
-      <c r="AM114" s="153"/>
-      <c r="AN114" s="153"/>
-      <c r="AO114" s="153"/>
-      <c r="AP114" s="153"/>
-      <c r="AQ114" s="153"/>
-      <c r="AR114" s="153"/>
-      <c r="AS114" s="153"/>
-      <c r="AT114" s="153"/>
-      <c r="AU114" s="153"/>
-      <c r="AV114" s="153"/>
-      <c r="AW114" s="153"/>
-      <c r="AX114" s="153"/>
-      <c r="AY114" s="157" t="str">
+      <c r="AM114" s="177"/>
+      <c r="AN114" s="177"/>
+      <c r="AO114" s="177"/>
+      <c r="AP114" s="177"/>
+      <c r="AQ114" s="177"/>
+      <c r="AR114" s="177"/>
+      <c r="AS114" s="177"/>
+      <c r="AT114" s="177"/>
+      <c r="AU114" s="177"/>
+      <c r="AV114" s="177"/>
+      <c r="AW114" s="177"/>
+      <c r="AX114" s="177"/>
+      <c r="AY114" s="180" t="str">
         <f>TEXT(INDEX('3. Workings'!$D$82:$F$82,MATCH($BH$4,'3. Workings'!$D$77:$F$77,0)),"0.00")&amp;" pp"</f>
         <v>4.49 pp</v>
       </c>
-      <c r="AZ114" s="157"/>
-      <c r="BA114" s="157"/>
-      <c r="BB114" s="157"/>
-      <c r="BC114" s="157"/>
-      <c r="BD114" s="157"/>
-      <c r="BE114" s="157"/>
-      <c r="BF114" s="157"/>
-      <c r="BG114" s="157"/>
-      <c r="BH114" s="157"/>
+      <c r="AZ114" s="180"/>
+      <c r="BA114" s="180"/>
+      <c r="BB114" s="180"/>
+      <c r="BC114" s="180"/>
+      <c r="BD114" s="180"/>
+      <c r="BE114" s="180"/>
+      <c r="BF114" s="180"/>
+      <c r="BG114" s="180"/>
+      <c r="BH114" s="180"/>
       <c r="BI114" s="35"/>
-      <c r="BK114" s="153"/>
-      <c r="BL114" s="153"/>
-      <c r="BM114" s="153"/>
-      <c r="BN114" s="153"/>
-      <c r="BO114" s="153"/>
-      <c r="BP114" s="153"/>
-      <c r="BQ114" s="153"/>
-      <c r="BR114" s="153"/>
-      <c r="BS114" s="153"/>
-      <c r="BT114" s="153"/>
-      <c r="BU114" s="153"/>
-      <c r="BW114" s="154"/>
-      <c r="BX114" s="154"/>
-      <c r="BY114" s="154"/>
-      <c r="BZ114" s="154"/>
-      <c r="CA114" s="154"/>
-      <c r="CB114" s="154"/>
-      <c r="CC114" s="154"/>
-      <c r="CD114" s="154"/>
-      <c r="CE114" s="154"/>
-      <c r="CF114" s="154"/>
-      <c r="CG114" s="154"/>
-      <c r="CH114" s="154"/>
-      <c r="CI114" s="154"/>
-      <c r="CJ114" s="154"/>
-      <c r="CK114" s="154"/>
-      <c r="CL114" s="154"/>
-      <c r="CM114" s="154"/>
-      <c r="CN114" s="154"/>
-      <c r="CO114" s="154"/>
-      <c r="CP114" s="154"/>
-      <c r="CQ114" s="154"/>
-      <c r="CR114" s="154"/>
+      <c r="BK114" s="177"/>
+      <c r="BL114" s="177"/>
+      <c r="BM114" s="177"/>
+      <c r="BN114" s="177"/>
+      <c r="BO114" s="177"/>
+      <c r="BP114" s="177"/>
+      <c r="BQ114" s="177"/>
+      <c r="BR114" s="177"/>
+      <c r="BS114" s="177"/>
+      <c r="BT114" s="177"/>
+      <c r="BU114" s="177"/>
+      <c r="BW114" s="181"/>
+      <c r="BX114" s="181"/>
+      <c r="BY114" s="181"/>
+      <c r="BZ114" s="181"/>
+      <c r="CA114" s="181"/>
+      <c r="CB114" s="181"/>
+      <c r="CC114" s="181"/>
+      <c r="CD114" s="181"/>
+      <c r="CE114" s="181"/>
+      <c r="CF114" s="181"/>
+      <c r="CG114" s="181"/>
+      <c r="CH114" s="181"/>
+      <c r="CI114" s="181"/>
+      <c r="CJ114" s="181"/>
+      <c r="CK114" s="181"/>
+      <c r="CL114" s="181"/>
+      <c r="CM114" s="181"/>
+      <c r="CN114" s="181"/>
+      <c r="CO114" s="181"/>
+      <c r="CP114" s="181"/>
+      <c r="CQ114" s="181"/>
+      <c r="CR114" s="181"/>
       <c r="CS114" s="36"/>
     </row>
     <row r="115" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="48"/>
-      <c r="D115" s="153"/>
-      <c r="E115" s="153"/>
-      <c r="F115" s="153"/>
-      <c r="G115" s="153"/>
-      <c r="H115" s="153"/>
-      <c r="I115" s="153"/>
-      <c r="J115" s="153"/>
-      <c r="K115" s="153"/>
-      <c r="L115" s="153"/>
-      <c r="M115" s="153"/>
-      <c r="N115" s="153"/>
-      <c r="O115" s="153"/>
-      <c r="P115" s="153"/>
-      <c r="Q115" s="155"/>
-      <c r="R115" s="155"/>
-      <c r="S115" s="155"/>
-      <c r="T115" s="155"/>
-      <c r="U115" s="155"/>
-      <c r="V115" s="155"/>
-      <c r="X115" s="156"/>
-      <c r="Y115" s="156"/>
-      <c r="Z115" s="156"/>
-      <c r="AA115" s="156"/>
-      <c r="AB115" s="156"/>
-      <c r="AC115" s="156"/>
-      <c r="AD115" s="156"/>
-      <c r="AE115" s="156"/>
-      <c r="AF115" s="156"/>
-      <c r="AG115" s="156"/>
-      <c r="AH115" s="156"/>
-      <c r="AI115" s="156"/>
+      <c r="D115" s="177"/>
+      <c r="E115" s="177"/>
+      <c r="F115" s="177"/>
+      <c r="G115" s="177"/>
+      <c r="H115" s="177"/>
+      <c r="I115" s="177"/>
+      <c r="J115" s="177"/>
+      <c r="K115" s="177"/>
+      <c r="L115" s="177"/>
+      <c r="M115" s="177"/>
+      <c r="N115" s="177"/>
+      <c r="O115" s="177"/>
+      <c r="P115" s="177"/>
+      <c r="Q115" s="178"/>
+      <c r="R115" s="178"/>
+      <c r="S115" s="178"/>
+      <c r="T115" s="178"/>
+      <c r="U115" s="178"/>
+      <c r="V115" s="178"/>
+      <c r="X115" s="179"/>
+      <c r="Y115" s="179"/>
+      <c r="Z115" s="179"/>
+      <c r="AA115" s="179"/>
+      <c r="AB115" s="179"/>
+      <c r="AC115" s="179"/>
+      <c r="AD115" s="179"/>
+      <c r="AE115" s="179"/>
+      <c r="AF115" s="179"/>
+      <c r="AG115" s="179"/>
+      <c r="AH115" s="179"/>
+      <c r="AI115" s="179"/>
       <c r="AJ115" s="35"/>
-      <c r="AL115" s="153"/>
-      <c r="AM115" s="153"/>
-      <c r="AN115" s="153"/>
-      <c r="AO115" s="153"/>
-      <c r="AP115" s="153"/>
-      <c r="AQ115" s="153"/>
-      <c r="AR115" s="153"/>
-      <c r="AS115" s="153"/>
-      <c r="AT115" s="153"/>
-      <c r="AU115" s="153"/>
-      <c r="AV115" s="153"/>
-      <c r="AW115" s="153"/>
-      <c r="AX115" s="153"/>
-      <c r="AY115" s="157"/>
-      <c r="AZ115" s="157"/>
-      <c r="BA115" s="157"/>
-      <c r="BB115" s="157"/>
-      <c r="BC115" s="157"/>
-      <c r="BD115" s="157"/>
-      <c r="BE115" s="157"/>
-      <c r="BF115" s="157"/>
-      <c r="BG115" s="157"/>
-      <c r="BH115" s="157"/>
+      <c r="AL115" s="177"/>
+      <c r="AM115" s="177"/>
+      <c r="AN115" s="177"/>
+      <c r="AO115" s="177"/>
+      <c r="AP115" s="177"/>
+      <c r="AQ115" s="177"/>
+      <c r="AR115" s="177"/>
+      <c r="AS115" s="177"/>
+      <c r="AT115" s="177"/>
+      <c r="AU115" s="177"/>
+      <c r="AV115" s="177"/>
+      <c r="AW115" s="177"/>
+      <c r="AX115" s="177"/>
+      <c r="AY115" s="180"/>
+      <c r="AZ115" s="180"/>
+      <c r="BA115" s="180"/>
+      <c r="BB115" s="180"/>
+      <c r="BC115" s="180"/>
+      <c r="BD115" s="180"/>
+      <c r="BE115" s="180"/>
+      <c r="BF115" s="180"/>
+      <c r="BG115" s="180"/>
+      <c r="BH115" s="180"/>
       <c r="BI115" s="35"/>
-      <c r="BK115" s="153"/>
-      <c r="BL115" s="153"/>
-      <c r="BM115" s="153"/>
-      <c r="BN115" s="153"/>
-      <c r="BO115" s="153"/>
-      <c r="BP115" s="153"/>
-      <c r="BQ115" s="153"/>
-      <c r="BR115" s="153"/>
-      <c r="BS115" s="153"/>
-      <c r="BT115" s="153"/>
-      <c r="BU115" s="153"/>
-      <c r="BW115" s="154"/>
-      <c r="BX115" s="154"/>
-      <c r="BY115" s="154"/>
-      <c r="BZ115" s="154"/>
-      <c r="CA115" s="154"/>
-      <c r="CB115" s="154"/>
-      <c r="CC115" s="154"/>
-      <c r="CD115" s="154"/>
-      <c r="CE115" s="154"/>
-      <c r="CF115" s="154"/>
-      <c r="CG115" s="154"/>
-      <c r="CH115" s="154"/>
-      <c r="CI115" s="154"/>
-      <c r="CJ115" s="154"/>
-      <c r="CK115" s="154"/>
-      <c r="CL115" s="154"/>
-      <c r="CM115" s="154"/>
-      <c r="CN115" s="154"/>
-      <c r="CO115" s="154"/>
-      <c r="CP115" s="154"/>
-      <c r="CQ115" s="154"/>
-      <c r="CR115" s="154"/>
+      <c r="BK115" s="177"/>
+      <c r="BL115" s="177"/>
+      <c r="BM115" s="177"/>
+      <c r="BN115" s="177"/>
+      <c r="BO115" s="177"/>
+      <c r="BP115" s="177"/>
+      <c r="BQ115" s="177"/>
+      <c r="BR115" s="177"/>
+      <c r="BS115" s="177"/>
+      <c r="BT115" s="177"/>
+      <c r="BU115" s="177"/>
+      <c r="BW115" s="181"/>
+      <c r="BX115" s="181"/>
+      <c r="BY115" s="181"/>
+      <c r="BZ115" s="181"/>
+      <c r="CA115" s="181"/>
+      <c r="CB115" s="181"/>
+      <c r="CC115" s="181"/>
+      <c r="CD115" s="181"/>
+      <c r="CE115" s="181"/>
+      <c r="CF115" s="181"/>
+      <c r="CG115" s="181"/>
+      <c r="CH115" s="181"/>
+      <c r="CI115" s="181"/>
+      <c r="CJ115" s="181"/>
+      <c r="CK115" s="181"/>
+      <c r="CL115" s="181"/>
+      <c r="CM115" s="181"/>
+      <c r="CN115" s="181"/>
+      <c r="CO115" s="181"/>
+      <c r="CP115" s="181"/>
+      <c r="CQ115" s="181"/>
+      <c r="CR115" s="181"/>
       <c r="CS115" s="36"/>
     </row>
     <row r="116" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -39943,199 +39943,199 @@
     </row>
     <row r="117" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="48"/>
-      <c r="D117" s="158" t="str">
+      <c r="D117" s="182" t="str">
         <f>"At the "&amp;$BH$4&amp;" rollout, the case does not rest on the fraud benefit. Labour alone covers the annual run cost down to "&amp;TEXT(INDEX('3. Workings'!$D$138:$F$138,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0.0")&amp;" touches per claim and ₹"&amp;TEXT(INDEX('3. Workings'!$D$140:$F$140,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0")&amp;" per touch, which is "&amp;TEXT(INDEX('3. Workings'!$D$139:$F$139,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;" and "&amp;TEXT(INDEX('3. Workings'!$D$141:$F$141,MATCH($BH$4,'3. Workings'!$D$137:$F$137,0)),"0%")&amp;" below what we assume. Payback moves from "&amp;TEXT(INDEX('3. Workings'!$D$95:$F$95,MATCH($BH$4,'3. Workings'!$D$89:$F$89,0)),"0.0")&amp;" months as modelled to "&amp;TEXT(INDEX('3. Workings'!$D$96:$F$96,MATCH($BH$4,'3. Workings'!$D$89:$F$89,0)),"0.0")&amp;" months if both our weakest assumptions break, and "&amp;'2. Summary'!$D$74&amp;"."</f>
         <v>At the Aggressive rollout, the case does not rest on the fraud benefit. Labour alone covers the annual run cost down to 1.8 touches per claim and ₹63 per touch, which is 75% and 75% below what we assume. Payback moves from 1.6 months as modelled to 4.2 months if both our weakest assumptions break, and ALL 24 CHECKS PASS.</v>
       </c>
-      <c r="E117" s="158"/>
-      <c r="F117" s="158"/>
-      <c r="G117" s="158"/>
-      <c r="H117" s="158"/>
-      <c r="I117" s="158"/>
-      <c r="J117" s="158"/>
-      <c r="K117" s="158"/>
-      <c r="L117" s="158"/>
-      <c r="M117" s="158"/>
-      <c r="N117" s="158"/>
-      <c r="O117" s="158"/>
-      <c r="P117" s="158"/>
-      <c r="Q117" s="158"/>
-      <c r="R117" s="158"/>
-      <c r="S117" s="158"/>
-      <c r="T117" s="158"/>
-      <c r="U117" s="158"/>
-      <c r="V117" s="158"/>
-      <c r="W117" s="158"/>
-      <c r="X117" s="158"/>
-      <c r="Y117" s="158"/>
-      <c r="Z117" s="158"/>
-      <c r="AA117" s="158"/>
-      <c r="AB117" s="158"/>
-      <c r="AC117" s="158"/>
-      <c r="AD117" s="158"/>
-      <c r="AE117" s="158"/>
-      <c r="AF117" s="158"/>
-      <c r="AG117" s="158"/>
-      <c r="AH117" s="158"/>
-      <c r="AI117" s="158"/>
-      <c r="AJ117" s="158"/>
-      <c r="AK117" s="158"/>
-      <c r="AL117" s="158"/>
-      <c r="AM117" s="158"/>
-      <c r="AN117" s="158"/>
-      <c r="AO117" s="158"/>
-      <c r="AP117" s="158"/>
-      <c r="AQ117" s="158"/>
-      <c r="AR117" s="158"/>
-      <c r="AS117" s="158"/>
-      <c r="AT117" s="158"/>
-      <c r="AU117" s="158"/>
-      <c r="AV117" s="158"/>
-      <c r="AW117" s="158"/>
-      <c r="AX117" s="158"/>
-      <c r="AY117" s="158"/>
-      <c r="AZ117" s="158"/>
-      <c r="BA117" s="158"/>
-      <c r="BB117" s="158"/>
-      <c r="BC117" s="158"/>
-      <c r="BD117" s="158"/>
-      <c r="BE117" s="158"/>
-      <c r="BF117" s="158"/>
-      <c r="BG117" s="158"/>
-      <c r="BH117" s="158"/>
-      <c r="BI117" s="158"/>
-      <c r="BJ117" s="158"/>
-      <c r="BK117" s="158"/>
-      <c r="BL117" s="158"/>
-      <c r="BM117" s="158"/>
-      <c r="BN117" s="158"/>
-      <c r="BO117" s="158"/>
-      <c r="BP117" s="158"/>
-      <c r="BQ117" s="158"/>
-      <c r="BR117" s="158"/>
-      <c r="BS117" s="158"/>
-      <c r="BT117" s="158"/>
-      <c r="BU117" s="158"/>
-      <c r="BV117" s="158"/>
-      <c r="BW117" s="158"/>
-      <c r="BX117" s="158"/>
-      <c r="BY117" s="158"/>
-      <c r="BZ117" s="158"/>
-      <c r="CA117" s="158"/>
-      <c r="CB117" s="158"/>
-      <c r="CC117" s="158"/>
-      <c r="CD117" s="158"/>
-      <c r="CE117" s="158"/>
-      <c r="CF117" s="158"/>
-      <c r="CG117" s="158"/>
-      <c r="CH117" s="158"/>
-      <c r="CI117" s="158"/>
-      <c r="CJ117" s="158"/>
-      <c r="CK117" s="158"/>
-      <c r="CL117" s="158"/>
-      <c r="CM117" s="158"/>
-      <c r="CN117" s="158"/>
-      <c r="CO117" s="158"/>
-      <c r="CP117" s="158"/>
-      <c r="CQ117" s="158"/>
-      <c r="CR117" s="158"/>
+      <c r="E117" s="182"/>
+      <c r="F117" s="182"/>
+      <c r="G117" s="182"/>
+      <c r="H117" s="182"/>
+      <c r="I117" s="182"/>
+      <c r="J117" s="182"/>
+      <c r="K117" s="182"/>
+      <c r="L117" s="182"/>
+      <c r="M117" s="182"/>
+      <c r="N117" s="182"/>
+      <c r="O117" s="182"/>
+      <c r="P117" s="182"/>
+      <c r="Q117" s="182"/>
+      <c r="R117" s="182"/>
+      <c r="S117" s="182"/>
+      <c r="T117" s="182"/>
+      <c r="U117" s="182"/>
+      <c r="V117" s="182"/>
+      <c r="W117" s="182"/>
+      <c r="X117" s="182"/>
+      <c r="Y117" s="182"/>
+      <c r="Z117" s="182"/>
+      <c r="AA117" s="182"/>
+      <c r="AB117" s="182"/>
+      <c r="AC117" s="182"/>
+      <c r="AD117" s="182"/>
+      <c r="AE117" s="182"/>
+      <c r="AF117" s="182"/>
+      <c r="AG117" s="182"/>
+      <c r="AH117" s="182"/>
+      <c r="AI117" s="182"/>
+      <c r="AJ117" s="182"/>
+      <c r="AK117" s="182"/>
+      <c r="AL117" s="182"/>
+      <c r="AM117" s="182"/>
+      <c r="AN117" s="182"/>
+      <c r="AO117" s="182"/>
+      <c r="AP117" s="182"/>
+      <c r="AQ117" s="182"/>
+      <c r="AR117" s="182"/>
+      <c r="AS117" s="182"/>
+      <c r="AT117" s="182"/>
+      <c r="AU117" s="182"/>
+      <c r="AV117" s="182"/>
+      <c r="AW117" s="182"/>
+      <c r="AX117" s="182"/>
+      <c r="AY117" s="182"/>
+      <c r="AZ117" s="182"/>
+      <c r="BA117" s="182"/>
+      <c r="BB117" s="182"/>
+      <c r="BC117" s="182"/>
+      <c r="BD117" s="182"/>
+      <c r="BE117" s="182"/>
+      <c r="BF117" s="182"/>
+      <c r="BG117" s="182"/>
+      <c r="BH117" s="182"/>
+      <c r="BI117" s="182"/>
+      <c r="BJ117" s="182"/>
+      <c r="BK117" s="182"/>
+      <c r="BL117" s="182"/>
+      <c r="BM117" s="182"/>
+      <c r="BN117" s="182"/>
+      <c r="BO117" s="182"/>
+      <c r="BP117" s="182"/>
+      <c r="BQ117" s="182"/>
+      <c r="BR117" s="182"/>
+      <c r="BS117" s="182"/>
+      <c r="BT117" s="182"/>
+      <c r="BU117" s="182"/>
+      <c r="BV117" s="182"/>
+      <c r="BW117" s="182"/>
+      <c r="BX117" s="182"/>
+      <c r="BY117" s="182"/>
+      <c r="BZ117" s="182"/>
+      <c r="CA117" s="182"/>
+      <c r="CB117" s="182"/>
+      <c r="CC117" s="182"/>
+      <c r="CD117" s="182"/>
+      <c r="CE117" s="182"/>
+      <c r="CF117" s="182"/>
+      <c r="CG117" s="182"/>
+      <c r="CH117" s="182"/>
+      <c r="CI117" s="182"/>
+      <c r="CJ117" s="182"/>
+      <c r="CK117" s="182"/>
+      <c r="CL117" s="182"/>
+      <c r="CM117" s="182"/>
+      <c r="CN117" s="182"/>
+      <c r="CO117" s="182"/>
+      <c r="CP117" s="182"/>
+      <c r="CQ117" s="182"/>
+      <c r="CR117" s="182"/>
       <c r="CS117" s="36"/>
     </row>
     <row r="118" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="50"/>
-      <c r="D118" s="158"/>
-      <c r="E118" s="158"/>
-      <c r="F118" s="158"/>
-      <c r="G118" s="158"/>
-      <c r="H118" s="158"/>
-      <c r="I118" s="158"/>
-      <c r="J118" s="158"/>
-      <c r="K118" s="158"/>
-      <c r="L118" s="158"/>
-      <c r="M118" s="158"/>
-      <c r="N118" s="158"/>
-      <c r="O118" s="158"/>
-      <c r="P118" s="158"/>
-      <c r="Q118" s="158"/>
-      <c r="R118" s="158"/>
-      <c r="S118" s="158"/>
-      <c r="T118" s="158"/>
-      <c r="U118" s="158"/>
-      <c r="V118" s="158"/>
-      <c r="W118" s="158"/>
-      <c r="X118" s="158"/>
-      <c r="Y118" s="158"/>
-      <c r="Z118" s="158"/>
-      <c r="AA118" s="158"/>
-      <c r="AB118" s="158"/>
-      <c r="AC118" s="158"/>
-      <c r="AD118" s="158"/>
-      <c r="AE118" s="158"/>
-      <c r="AF118" s="158"/>
-      <c r="AG118" s="158"/>
-      <c r="AH118" s="158"/>
-      <c r="AI118" s="158"/>
-      <c r="AJ118" s="158"/>
-      <c r="AK118" s="158"/>
-      <c r="AL118" s="158"/>
-      <c r="AM118" s="158"/>
-      <c r="AN118" s="158"/>
-      <c r="AO118" s="158"/>
-      <c r="AP118" s="158"/>
-      <c r="AQ118" s="158"/>
-      <c r="AR118" s="158"/>
-      <c r="AS118" s="158"/>
-      <c r="AT118" s="158"/>
-      <c r="AU118" s="158"/>
-      <c r="AV118" s="158"/>
-      <c r="AW118" s="158"/>
-      <c r="AX118" s="158"/>
-      <c r="AY118" s="158"/>
-      <c r="AZ118" s="158"/>
-      <c r="BA118" s="158"/>
-      <c r="BB118" s="158"/>
-      <c r="BC118" s="158"/>
-      <c r="BD118" s="158"/>
-      <c r="BE118" s="158"/>
-      <c r="BF118" s="158"/>
-      <c r="BG118" s="158"/>
-      <c r="BH118" s="158"/>
-      <c r="BI118" s="158"/>
-      <c r="BJ118" s="158"/>
-      <c r="BK118" s="158"/>
-      <c r="BL118" s="158"/>
-      <c r="BM118" s="158"/>
-      <c r="BN118" s="158"/>
-      <c r="BO118" s="158"/>
-      <c r="BP118" s="158"/>
-      <c r="BQ118" s="158"/>
-      <c r="BR118" s="158"/>
-      <c r="BS118" s="158"/>
-      <c r="BT118" s="158"/>
-      <c r="BU118" s="158"/>
-      <c r="BV118" s="158"/>
-      <c r="BW118" s="158"/>
-      <c r="BX118" s="158"/>
-      <c r="BY118" s="158"/>
-      <c r="BZ118" s="158"/>
-      <c r="CA118" s="158"/>
-      <c r="CB118" s="158"/>
-      <c r="CC118" s="158"/>
-      <c r="CD118" s="158"/>
-      <c r="CE118" s="158"/>
-      <c r="CF118" s="158"/>
-      <c r="CG118" s="158"/>
-      <c r="CH118" s="158"/>
-      <c r="CI118" s="158"/>
-      <c r="CJ118" s="158"/>
-      <c r="CK118" s="158"/>
-      <c r="CL118" s="158"/>
-      <c r="CM118" s="158"/>
-      <c r="CN118" s="158"/>
-      <c r="CO118" s="158"/>
-      <c r="CP118" s="158"/>
-      <c r="CQ118" s="158"/>
-      <c r="CR118" s="158"/>
+      <c r="D118" s="182"/>
+      <c r="E118" s="182"/>
+      <c r="F118" s="182"/>
+      <c r="G118" s="182"/>
+      <c r="H118" s="182"/>
+      <c r="I118" s="182"/>
+      <c r="J118" s="182"/>
+      <c r="K118" s="182"/>
+      <c r="L118" s="182"/>
+      <c r="M118" s="182"/>
+      <c r="N118" s="182"/>
+      <c r="O118" s="182"/>
+      <c r="P118" s="182"/>
+      <c r="Q118" s="182"/>
+      <c r="R118" s="182"/>
+      <c r="S118" s="182"/>
+      <c r="T118" s="182"/>
+      <c r="U118" s="182"/>
+      <c r="V118" s="182"/>
+      <c r="W118" s="182"/>
+      <c r="X118" s="182"/>
+      <c r="Y118" s="182"/>
+      <c r="Z118" s="182"/>
+      <c r="AA118" s="182"/>
+      <c r="AB118" s="182"/>
+      <c r="AC118" s="182"/>
+      <c r="AD118" s="182"/>
+      <c r="AE118" s="182"/>
+      <c r="AF118" s="182"/>
+      <c r="AG118" s="182"/>
+      <c r="AH118" s="182"/>
+      <c r="AI118" s="182"/>
+      <c r="AJ118" s="182"/>
+      <c r="AK118" s="182"/>
+      <c r="AL118" s="182"/>
+      <c r="AM118" s="182"/>
+      <c r="AN118" s="182"/>
+      <c r="AO118" s="182"/>
+      <c r="AP118" s="182"/>
+      <c r="AQ118" s="182"/>
+      <c r="AR118" s="182"/>
+      <c r="AS118" s="182"/>
+      <c r="AT118" s="182"/>
+      <c r="AU118" s="182"/>
+      <c r="AV118" s="182"/>
+      <c r="AW118" s="182"/>
+      <c r="AX118" s="182"/>
+      <c r="AY118" s="182"/>
+      <c r="AZ118" s="182"/>
+      <c r="BA118" s="182"/>
+      <c r="BB118" s="182"/>
+      <c r="BC118" s="182"/>
+      <c r="BD118" s="182"/>
+      <c r="BE118" s="182"/>
+      <c r="BF118" s="182"/>
+      <c r="BG118" s="182"/>
+      <c r="BH118" s="182"/>
+      <c r="BI118" s="182"/>
+      <c r="BJ118" s="182"/>
+      <c r="BK118" s="182"/>
+      <c r="BL118" s="182"/>
+      <c r="BM118" s="182"/>
+      <c r="BN118" s="182"/>
+      <c r="BO118" s="182"/>
+      <c r="BP118" s="182"/>
+      <c r="BQ118" s="182"/>
+      <c r="BR118" s="182"/>
+      <c r="BS118" s="182"/>
+      <c r="BT118" s="182"/>
+      <c r="BU118" s="182"/>
+      <c r="BV118" s="182"/>
+      <c r="BW118" s="182"/>
+      <c r="BX118" s="182"/>
+      <c r="BY118" s="182"/>
+      <c r="BZ118" s="182"/>
+      <c r="CA118" s="182"/>
+      <c r="CB118" s="182"/>
+      <c r="CC118" s="182"/>
+      <c r="CD118" s="182"/>
+      <c r="CE118" s="182"/>
+      <c r="CF118" s="182"/>
+      <c r="CG118" s="182"/>
+      <c r="CH118" s="182"/>
+      <c r="CI118" s="182"/>
+      <c r="CJ118" s="182"/>
+      <c r="CK118" s="182"/>
+      <c r="CL118" s="182"/>
+      <c r="CM118" s="182"/>
+      <c r="CN118" s="182"/>
+      <c r="CO118" s="182"/>
+      <c r="CP118" s="182"/>
+      <c r="CQ118" s="182"/>
+      <c r="CR118" s="182"/>
       <c r="CS118" s="46"/>
     </row>
     <row r="119" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -40197,179 +40197,102 @@
       <c r="CR119" s="39"/>
     </row>
     <row r="120" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I120" s="159" t="str">
+      <c r="I120" s="163" t="str">
         <f>IF(SUMPRODUCT(--('1. Assumptions and Sources'!$E$147:$E$150&lt;&gt;""))=0,"No overrides. The model is running on its published assumptions.","LIVE OVERRIDE ACTIVE  ·  "&amp;SUMPRODUCT(--('1. Assumptions and Sources'!$E$147:$E$150&lt;&gt;""))&amp;" of 4 levers overridden. Clear the yellow cells to return to published assumptions.")</f>
         <v>No overrides. The model is running on its published assumptions.</v>
       </c>
-      <c r="J120" s="159"/>
-      <c r="K120" s="159"/>
-      <c r="L120" s="159"/>
-      <c r="M120" s="159"/>
-      <c r="N120" s="159"/>
-      <c r="O120" s="159"/>
-      <c r="P120" s="159"/>
-      <c r="Q120" s="159"/>
-      <c r="R120" s="159"/>
-      <c r="S120" s="159"/>
-      <c r="T120" s="159"/>
-      <c r="U120" s="159"/>
-      <c r="V120" s="159"/>
-      <c r="W120" s="159"/>
-      <c r="X120" s="159"/>
-      <c r="Y120" s="159"/>
-      <c r="Z120" s="159"/>
-      <c r="AA120" s="159"/>
-      <c r="AB120" s="159"/>
-      <c r="AC120" s="159"/>
-      <c r="AD120" s="159"/>
-      <c r="AE120" s="159"/>
-      <c r="AF120" s="159"/>
-      <c r="AG120" s="159"/>
-      <c r="AH120" s="159"/>
-      <c r="AI120" s="159"/>
-      <c r="AJ120" s="159"/>
-      <c r="AK120" s="159"/>
-      <c r="AL120" s="159"/>
-      <c r="AM120" s="159"/>
-      <c r="AN120" s="159"/>
-      <c r="AO120" s="159"/>
-      <c r="AP120" s="159"/>
-      <c r="AQ120" s="159"/>
-      <c r="AR120" s="159"/>
-      <c r="AS120" s="159"/>
-      <c r="AT120" s="159"/>
-      <c r="AU120" s="159"/>
-      <c r="AV120" s="159"/>
-      <c r="AW120" s="159"/>
-      <c r="AX120" s="159"/>
-      <c r="AY120" s="159"/>
-      <c r="AZ120" s="159"/>
-      <c r="BA120" s="159"/>
-      <c r="BB120" s="159"/>
-      <c r="BC120" s="159"/>
-      <c r="BD120" s="159"/>
-      <c r="BE120" s="159"/>
-      <c r="BF120" s="159"/>
-      <c r="BG120" s="159"/>
-      <c r="BH120" s="159"/>
-      <c r="BI120" s="159"/>
-      <c r="BJ120" s="159"/>
-      <c r="BK120" s="159"/>
-      <c r="BL120" s="159"/>
-      <c r="BM120" s="159"/>
-      <c r="BN120" s="159"/>
-      <c r="BO120" s="159"/>
-      <c r="BP120" s="159"/>
-      <c r="BQ120" s="159"/>
-      <c r="BR120" s="159"/>
-      <c r="BS120" s="159"/>
-      <c r="BT120" s="159"/>
-      <c r="BU120" s="159"/>
-      <c r="BV120" s="159"/>
-      <c r="BW120" s="159"/>
-      <c r="BX120" s="159"/>
-      <c r="BY120" s="159"/>
-      <c r="BZ120" s="159"/>
-      <c r="CA120" s="159"/>
-      <c r="CB120" s="159"/>
-      <c r="CC120" s="159"/>
-      <c r="CD120" s="159"/>
-      <c r="CE120" s="159"/>
-      <c r="CF120" s="159"/>
-      <c r="CG120" s="159"/>
-      <c r="CH120" s="159"/>
-      <c r="CI120" s="159"/>
+      <c r="J120" s="163"/>
+      <c r="K120" s="163"/>
+      <c r="L120" s="163"/>
+      <c r="M120" s="163"/>
+      <c r="N120" s="163"/>
+      <c r="O120" s="163"/>
+      <c r="P120" s="163"/>
+      <c r="Q120" s="163"/>
+      <c r="R120" s="163"/>
+      <c r="S120" s="163"/>
+      <c r="T120" s="163"/>
+      <c r="U120" s="163"/>
+      <c r="V120" s="163"/>
+      <c r="W120" s="163"/>
+      <c r="X120" s="163"/>
+      <c r="Y120" s="163"/>
+      <c r="Z120" s="163"/>
+      <c r="AA120" s="163"/>
+      <c r="AB120" s="163"/>
+      <c r="AC120" s="163"/>
+      <c r="AD120" s="163"/>
+      <c r="AE120" s="163"/>
+      <c r="AF120" s="163"/>
+      <c r="AG120" s="163"/>
+      <c r="AH120" s="163"/>
+      <c r="AI120" s="163"/>
+      <c r="AJ120" s="163"/>
+      <c r="AK120" s="163"/>
+      <c r="AL120" s="163"/>
+      <c r="AM120" s="163"/>
+      <c r="AN120" s="163"/>
+      <c r="AO120" s="163"/>
+      <c r="AP120" s="163"/>
+      <c r="AQ120" s="163"/>
+      <c r="AR120" s="163"/>
+      <c r="AS120" s="163"/>
+      <c r="AT120" s="163"/>
+      <c r="AU120" s="163"/>
+      <c r="AV120" s="163"/>
+      <c r="AW120" s="163"/>
+      <c r="AX120" s="163"/>
+      <c r="AY120" s="163"/>
+      <c r="AZ120" s="163"/>
+      <c r="BA120" s="163"/>
+      <c r="BB120" s="163"/>
+      <c r="BC120" s="163"/>
+      <c r="BD120" s="163"/>
+      <c r="BE120" s="163"/>
+      <c r="BF120" s="163"/>
+      <c r="BG120" s="163"/>
+      <c r="BH120" s="163"/>
+      <c r="BI120" s="163"/>
+      <c r="BJ120" s="163"/>
+      <c r="BK120" s="163"/>
+      <c r="BL120" s="163"/>
+      <c r="BM120" s="163"/>
+      <c r="BN120" s="163"/>
+      <c r="BO120" s="163"/>
+      <c r="BP120" s="163"/>
+      <c r="BQ120" s="163"/>
+      <c r="BR120" s="163"/>
+      <c r="BS120" s="163"/>
+      <c r="BT120" s="163"/>
+      <c r="BU120" s="163"/>
+      <c r="BV120" s="163"/>
+      <c r="BW120" s="163"/>
+      <c r="BX120" s="163"/>
+      <c r="BY120" s="163"/>
+      <c r="BZ120" s="163"/>
+      <c r="CA120" s="163"/>
+      <c r="CB120" s="163"/>
+      <c r="CC120" s="163"/>
+      <c r="CD120" s="163"/>
+      <c r="CE120" s="163"/>
+      <c r="CF120" s="163"/>
+      <c r="CG120" s="163"/>
+      <c r="CH120" s="163"/>
+      <c r="CI120" s="163"/>
     </row>
     <row r="121" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="122" spans="3:97" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="D2:Q4"/>
-    <mergeCell ref="S2:BF4"/>
-    <mergeCell ref="BH3:BU3"/>
-    <mergeCell ref="BH4:BU5"/>
-    <mergeCell ref="D5:P5"/>
-    <mergeCell ref="S5:BD5"/>
-    <mergeCell ref="D10:N11"/>
-    <mergeCell ref="S10:Z11"/>
-    <mergeCell ref="AB10:AI11"/>
-    <mergeCell ref="AN10:AX11"/>
-    <mergeCell ref="BC10:BM11"/>
-    <mergeCell ref="BR10:CB11"/>
-    <mergeCell ref="CG10:CQ11"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="S12:Z12"/>
-    <mergeCell ref="AB12:AI12"/>
-    <mergeCell ref="AN12:AX12"/>
-    <mergeCell ref="BC12:BM12"/>
-    <mergeCell ref="BR12:CB12"/>
-    <mergeCell ref="CG12:CQ12"/>
-    <mergeCell ref="CL16:CS17"/>
-    <mergeCell ref="D18:AB18"/>
-    <mergeCell ref="AG18:BD18"/>
-    <mergeCell ref="BI18:CQ18"/>
-    <mergeCell ref="AH20:BD21"/>
-    <mergeCell ref="E34:AB35"/>
-    <mergeCell ref="BJ34:CQ35"/>
-    <mergeCell ref="F37:AL37"/>
-    <mergeCell ref="AQ37:BG37"/>
-    <mergeCell ref="BL37:CQ37"/>
-    <mergeCell ref="F39:P40"/>
-    <mergeCell ref="Q39:AA40"/>
-    <mergeCell ref="AB39:AL40"/>
-    <mergeCell ref="F41:P42"/>
-    <mergeCell ref="Q41:AA42"/>
-    <mergeCell ref="AB41:AL42"/>
-    <mergeCell ref="F43:P44"/>
-    <mergeCell ref="Q43:AA44"/>
-    <mergeCell ref="AB43:AL44"/>
-    <mergeCell ref="F45:P46"/>
-    <mergeCell ref="Q45:AA46"/>
-    <mergeCell ref="AB45:AL46"/>
-    <mergeCell ref="F47:P48"/>
-    <mergeCell ref="Q47:AA48"/>
-    <mergeCell ref="AB47:AL48"/>
-    <mergeCell ref="F49:P50"/>
-    <mergeCell ref="Q49:AA50"/>
-    <mergeCell ref="AB49:AL50"/>
-    <mergeCell ref="F51:P52"/>
-    <mergeCell ref="Q51:AA52"/>
-    <mergeCell ref="AB51:AL52"/>
-    <mergeCell ref="F53:P54"/>
-    <mergeCell ref="Q53:AA54"/>
-    <mergeCell ref="AB53:AL54"/>
-    <mergeCell ref="F55:P56"/>
-    <mergeCell ref="Q55:AA56"/>
-    <mergeCell ref="AB55:AL56"/>
-    <mergeCell ref="AU61:BB62"/>
-    <mergeCell ref="CL61:CS62"/>
-    <mergeCell ref="D63:R63"/>
-    <mergeCell ref="U63:AI63"/>
-    <mergeCell ref="AL63:AZ63"/>
-    <mergeCell ref="BE63:CR63"/>
-    <mergeCell ref="D64:R72"/>
-    <mergeCell ref="D75:AZ76"/>
-    <mergeCell ref="AU79:BB80"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="R81:BA81"/>
-    <mergeCell ref="BE81:CR81"/>
-    <mergeCell ref="D83:I84"/>
-    <mergeCell ref="J83:N84"/>
-    <mergeCell ref="D86:I87"/>
-    <mergeCell ref="J86:N87"/>
-    <mergeCell ref="D89:I90"/>
-    <mergeCell ref="J89:N90"/>
-    <mergeCell ref="D92:I93"/>
-    <mergeCell ref="J92:N93"/>
-    <mergeCell ref="D95:I96"/>
-    <mergeCell ref="J95:N96"/>
-    <mergeCell ref="BE97:CR98"/>
-    <mergeCell ref="D98:AZ99"/>
-    <mergeCell ref="BA98:BA99"/>
-    <mergeCell ref="CL101:CS102"/>
-    <mergeCell ref="D103:AI103"/>
-    <mergeCell ref="AL103:BH103"/>
-    <mergeCell ref="BK103:CP103"/>
+    <mergeCell ref="BK113:BU115"/>
+    <mergeCell ref="BW113:CR115"/>
+    <mergeCell ref="D114:P115"/>
+    <mergeCell ref="Q114:V115"/>
+    <mergeCell ref="X114:AI115"/>
+    <mergeCell ref="AL114:AX115"/>
+    <mergeCell ref="AY114:BH115"/>
+    <mergeCell ref="D117:CR118"/>
+    <mergeCell ref="I120:CI120"/>
     <mergeCell ref="D105:P106"/>
     <mergeCell ref="Q105:V106"/>
     <mergeCell ref="X105:AI106"/>
@@ -40389,15 +40312,92 @@
     <mergeCell ref="X111:AI112"/>
     <mergeCell ref="AL111:AX112"/>
     <mergeCell ref="AY111:BH112"/>
-    <mergeCell ref="BK113:BU115"/>
-    <mergeCell ref="BW113:CR115"/>
-    <mergeCell ref="D114:P115"/>
-    <mergeCell ref="Q114:V115"/>
-    <mergeCell ref="X114:AI115"/>
-    <mergeCell ref="AL114:AX115"/>
-    <mergeCell ref="AY114:BH115"/>
-    <mergeCell ref="D117:CR118"/>
-    <mergeCell ref="I120:CI120"/>
+    <mergeCell ref="D92:I93"/>
+    <mergeCell ref="J92:N93"/>
+    <mergeCell ref="D95:I96"/>
+    <mergeCell ref="J95:N96"/>
+    <mergeCell ref="BE97:CR98"/>
+    <mergeCell ref="D98:AZ99"/>
+    <mergeCell ref="BA98:BA99"/>
+    <mergeCell ref="CL101:CS102"/>
+    <mergeCell ref="D103:AI103"/>
+    <mergeCell ref="AL103:BH103"/>
+    <mergeCell ref="BK103:CP103"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="R81:BA81"/>
+    <mergeCell ref="BE81:CR81"/>
+    <mergeCell ref="D83:I84"/>
+    <mergeCell ref="J83:N84"/>
+    <mergeCell ref="D86:I87"/>
+    <mergeCell ref="J86:N87"/>
+    <mergeCell ref="D89:I90"/>
+    <mergeCell ref="J89:N90"/>
+    <mergeCell ref="AU61:BB62"/>
+    <mergeCell ref="CL61:CS62"/>
+    <mergeCell ref="D63:R63"/>
+    <mergeCell ref="U63:AI63"/>
+    <mergeCell ref="AL63:AZ63"/>
+    <mergeCell ref="BE63:CR63"/>
+    <mergeCell ref="D64:R72"/>
+    <mergeCell ref="D75:AZ76"/>
+    <mergeCell ref="AU79:BB80"/>
+    <mergeCell ref="F51:P52"/>
+    <mergeCell ref="Q51:AA52"/>
+    <mergeCell ref="AB51:AL52"/>
+    <mergeCell ref="F53:P54"/>
+    <mergeCell ref="Q53:AA54"/>
+    <mergeCell ref="AB53:AL54"/>
+    <mergeCell ref="F55:P56"/>
+    <mergeCell ref="Q55:AA56"/>
+    <mergeCell ref="AB55:AL56"/>
+    <mergeCell ref="F45:P46"/>
+    <mergeCell ref="Q45:AA46"/>
+    <mergeCell ref="AB45:AL46"/>
+    <mergeCell ref="F47:P48"/>
+    <mergeCell ref="Q47:AA48"/>
+    <mergeCell ref="AB47:AL48"/>
+    <mergeCell ref="F49:P50"/>
+    <mergeCell ref="Q49:AA50"/>
+    <mergeCell ref="AB49:AL50"/>
+    <mergeCell ref="F39:P40"/>
+    <mergeCell ref="Q39:AA40"/>
+    <mergeCell ref="AB39:AL40"/>
+    <mergeCell ref="F41:P42"/>
+    <mergeCell ref="Q41:AA42"/>
+    <mergeCell ref="AB41:AL42"/>
+    <mergeCell ref="F43:P44"/>
+    <mergeCell ref="Q43:AA44"/>
+    <mergeCell ref="AB43:AL44"/>
+    <mergeCell ref="D18:AB18"/>
+    <mergeCell ref="AG18:BD18"/>
+    <mergeCell ref="BI18:CQ18"/>
+    <mergeCell ref="AH20:BD21"/>
+    <mergeCell ref="E34:AB35"/>
+    <mergeCell ref="BJ34:CQ35"/>
+    <mergeCell ref="F37:AL37"/>
+    <mergeCell ref="AQ37:BG37"/>
+    <mergeCell ref="BL37:CQ37"/>
+    <mergeCell ref="CG10:CQ11"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="S12:Z12"/>
+    <mergeCell ref="AB12:AI12"/>
+    <mergeCell ref="AN12:AX12"/>
+    <mergeCell ref="BC12:BM12"/>
+    <mergeCell ref="BR12:CB12"/>
+    <mergeCell ref="CG12:CQ12"/>
+    <mergeCell ref="CL16:CS17"/>
+    <mergeCell ref="D2:Q4"/>
+    <mergeCell ref="S2:BF4"/>
+    <mergeCell ref="BH3:BU3"/>
+    <mergeCell ref="BH4:BU5"/>
+    <mergeCell ref="D5:P5"/>
+    <mergeCell ref="S5:BD5"/>
+    <mergeCell ref="D10:N11"/>
+    <mergeCell ref="S10:Z11"/>
+    <mergeCell ref="AB10:AI11"/>
+    <mergeCell ref="AN10:AX11"/>
+    <mergeCell ref="BC10:BM11"/>
+    <mergeCell ref="BR10:CB11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -40464,16 +40464,16 @@
     </row>
     <row r="4" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>392</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
     </row>
     <row r="6" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -40757,16 +40757,16 @@
     </row>
     <row r="20" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="182" t="s">
+      <c r="B21" s="185" t="s">
         <v>445</v>
       </c>
-      <c r="C21" s="182"/>
-      <c r="D21" s="182"/>
-      <c r="E21" s="182"/>
-      <c r="F21" s="182"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="182"/>
-      <c r="I21" s="182"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="185"/>
+      <c r="F21" s="185"/>
+      <c r="G21" s="185"/>
+      <c r="H21" s="185"/>
+      <c r="I21" s="185"/>
     </row>
     <row r="22" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="60" t="s">
@@ -41372,16 +41372,16 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="182" t="s">
+      <c r="B52" s="185" t="s">
         <v>540</v>
       </c>
-      <c r="C52" s="182"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="182"/>
-      <c r="F52" s="182"/>
-      <c r="G52" s="182"/>
-      <c r="H52" s="182"/>
-      <c r="I52" s="182"/>
+      <c r="C52" s="185"/>
+      <c r="D52" s="185"/>
+      <c r="E52" s="185"/>
+      <c r="F52" s="185"/>
+      <c r="G52" s="185"/>
+      <c r="H52" s="185"/>
+      <c r="I52" s="185"/>
     </row>
     <row r="53" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="60" t="s">
@@ -41453,16 +41453,16 @@
     </row>
     <row r="57" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="182" t="s">
+      <c r="B58" s="185" t="s">
         <v>547</v>
       </c>
-      <c r="C58" s="182"/>
-      <c r="D58" s="182"/>
-      <c r="E58" s="182"/>
-      <c r="F58" s="182"/>
-      <c r="G58" s="182"/>
-      <c r="H58" s="182"/>
-      <c r="I58" s="182"/>
+      <c r="C58" s="185"/>
+      <c r="D58" s="185"/>
+      <c r="E58" s="185"/>
+      <c r="F58" s="185"/>
+      <c r="G58" s="185"/>
+      <c r="H58" s="185"/>
+      <c r="I58" s="185"/>
     </row>
     <row r="59" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="60" t="s">
@@ -41741,16 +41741,16 @@
     </row>
     <row r="75" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="182" t="s">
+      <c r="B76" s="185" t="s">
         <v>601</v>
       </c>
-      <c r="C76" s="182"/>
-      <c r="D76" s="182"/>
-      <c r="E76" s="182"/>
-      <c r="F76" s="182"/>
-      <c r="G76" s="182"/>
-      <c r="H76" s="182"/>
-      <c r="I76" s="182"/>
+      <c r="C76" s="185"/>
+      <c r="D76" s="185"/>
+      <c r="E76" s="185"/>
+      <c r="F76" s="185"/>
+      <c r="G76" s="185"/>
+      <c r="H76" s="185"/>
+      <c r="I76" s="185"/>
     </row>
     <row r="77" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="60" t="s">
@@ -41975,16 +41975,16 @@
     <row r="88" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="182" t="s">
+      <c r="B90" s="185" t="s">
         <v>637</v>
       </c>
-      <c r="C90" s="182"/>
-      <c r="D90" s="182"/>
-      <c r="E90" s="182"/>
-      <c r="F90" s="182"/>
-      <c r="G90" s="182"/>
-      <c r="H90" s="182"/>
-      <c r="I90" s="182"/>
+      <c r="C90" s="185"/>
+      <c r="D90" s="185"/>
+      <c r="E90" s="185"/>
+      <c r="F90" s="185"/>
+      <c r="G90" s="185"/>
+      <c r="H90" s="185"/>
+      <c r="I90" s="185"/>
     </row>
     <row r="91" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="60" t="s">
@@ -42048,16 +42048,16 @@
     </row>
     <row r="94" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="182" t="s">
+      <c r="B95" s="185" t="s">
         <v>645</v>
       </c>
-      <c r="C95" s="182"/>
-      <c r="D95" s="182"/>
-      <c r="E95" s="182"/>
-      <c r="F95" s="182"/>
-      <c r="G95" s="182"/>
-      <c r="H95" s="182"/>
-      <c r="I95" s="182"/>
+      <c r="C95" s="185"/>
+      <c r="D95" s="185"/>
+      <c r="E95" s="185"/>
+      <c r="F95" s="185"/>
+      <c r="G95" s="185"/>
+      <c r="H95" s="185"/>
+      <c r="I95" s="185"/>
     </row>
     <row r="96" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="60" t="s">
@@ -42173,16 +42173,16 @@
     </row>
     <row r="104" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="182" t="s">
+      <c r="B105" s="185" t="s">
         <v>675</v>
       </c>
-      <c r="C105" s="182"/>
-      <c r="D105" s="182"/>
-      <c r="E105" s="182"/>
-      <c r="F105" s="182"/>
-      <c r="G105" s="182"/>
-      <c r="H105" s="182"/>
-      <c r="I105" s="182"/>
+      <c r="C105" s="185"/>
+      <c r="D105" s="185"/>
+      <c r="E105" s="185"/>
+      <c r="F105" s="185"/>
+      <c r="G105" s="185"/>
+      <c r="H105" s="185"/>
+      <c r="I105" s="185"/>
     </row>
     <row r="106" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="60" t="s">
@@ -42312,13 +42312,13 @@
     </row>
     <row r="115" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="116" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="182" t="s">
+      <c r="B116" s="185" t="s">
         <v>710</v>
       </c>
-      <c r="C116" s="182"/>
-      <c r="D116" s="182"/>
-      <c r="E116" s="182"/>
-      <c r="F116" s="182"/>
+      <c r="C116" s="185"/>
+      <c r="D116" s="185"/>
+      <c r="E116" s="185"/>
+      <c r="F116" s="185"/>
     </row>
     <row r="117" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="60" t="s">
@@ -42402,13 +42402,13 @@
     </row>
     <row r="121" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="122" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="182" t="s">
+      <c r="B122" s="185" t="s">
         <v>721</v>
       </c>
-      <c r="C122" s="182"/>
-      <c r="D122" s="182"/>
-      <c r="E122" s="182"/>
-      <c r="F122" s="182"/>
+      <c r="C122" s="185"/>
+      <c r="D122" s="185"/>
+      <c r="E122" s="185"/>
+      <c r="F122" s="185"/>
     </row>
     <row r="123" spans="2:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="60" t="s">
@@ -42572,16 +42572,16 @@
     </row>
     <row r="131" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="182" t="s">
+      <c r="B132" s="185" t="s">
         <v>745</v>
       </c>
-      <c r="C132" s="182"/>
-      <c r="D132" s="182"/>
-      <c r="E132" s="182"/>
-      <c r="F132" s="182"/>
-      <c r="G132" s="182"/>
-      <c r="H132" s="182"/>
-      <c r="I132" s="182"/>
+      <c r="C132" s="185"/>
+      <c r="D132" s="185"/>
+      <c r="E132" s="185"/>
+      <c r="F132" s="185"/>
+      <c r="G132" s="185"/>
+      <c r="H132" s="185"/>
+      <c r="I132" s="185"/>
     </row>
     <row r="133" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="60" t="s">
@@ -43847,11 +43847,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B52:I52"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B132:I132"/>
@@ -43860,6 +43855,11 @@
     <mergeCell ref="B90:I90"/>
     <mergeCell ref="B95:I95"/>
     <mergeCell ref="B105:I105"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B52:I52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -43909,16 +43909,16 @@
     </row>
     <row r="4" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>927</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
     </row>
     <row r="6" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -44379,16 +44379,16 @@
     </row>
     <row r="26" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="182" t="s">
+      <c r="B27" s="185" t="s">
         <v>967</v>
       </c>
-      <c r="C27" s="182"/>
-      <c r="D27" s="182"/>
-      <c r="E27" s="182"/>
-      <c r="F27" s="182"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="182"/>
-      <c r="I27" s="182"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
     </row>
     <row r="28" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="60" t="s">
@@ -44576,16 +44576,16 @@
     </row>
     <row r="37" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="182" t="s">
+      <c r="B38" s="185" t="s">
         <v>988</v>
       </c>
-      <c r="C38" s="182"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="182"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="182"/>
-      <c r="I38" s="182"/>
+      <c r="C38" s="185"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
+      <c r="F38" s="185"/>
+      <c r="G38" s="185"/>
+      <c r="H38" s="185"/>
+      <c r="I38" s="185"/>
     </row>
     <row r="39" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
@@ -44920,76 +44920,76 @@
     <row r="53" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="182" t="s">
+      <c r="B55" s="185" t="s">
         <v>1004</v>
       </c>
-      <c r="C55" s="182"/>
-      <c r="D55" s="182"/>
-      <c r="E55" s="182"/>
-      <c r="F55" s="182"/>
-      <c r="G55" s="182"/>
-      <c r="H55" s="182"/>
-      <c r="I55" s="182"/>
+      <c r="C55" s="185"/>
+      <c r="D55" s="185"/>
+      <c r="E55" s="185"/>
+      <c r="F55" s="185"/>
+      <c r="G55" s="185"/>
+      <c r="H55" s="185"/>
+      <c r="I55" s="185"/>
     </row>
     <row r="56" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="185" t="s">
+      <c r="B56" s="186" t="s">
         <v>1005</v>
       </c>
-      <c r="C56" s="185"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="185"/>
-      <c r="F56" s="185"/>
-      <c r="G56" s="185"/>
+      <c r="C56" s="186"/>
+      <c r="D56" s="186"/>
+      <c r="E56" s="186"/>
+      <c r="F56" s="186"/>
+      <c r="G56" s="186"/>
     </row>
     <row r="57" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="185" t="s">
+      <c r="B57" s="186" t="s">
         <v>1006</v>
       </c>
-      <c r="C57" s="185"/>
-      <c r="D57" s="185"/>
-      <c r="E57" s="185"/>
-      <c r="F57" s="185"/>
-      <c r="G57" s="185"/>
+      <c r="C57" s="186"/>
+      <c r="D57" s="186"/>
+      <c r="E57" s="186"/>
+      <c r="F57" s="186"/>
+      <c r="G57" s="186"/>
     </row>
     <row r="58" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="185" t="s">
+      <c r="B58" s="186" t="s">
         <v>1007</v>
       </c>
-      <c r="C58" s="185"/>
-      <c r="D58" s="185"/>
-      <c r="E58" s="185"/>
-      <c r="F58" s="185"/>
-      <c r="G58" s="185"/>
+      <c r="C58" s="186"/>
+      <c r="D58" s="186"/>
+      <c r="E58" s="186"/>
+      <c r="F58" s="186"/>
+      <c r="G58" s="186"/>
     </row>
     <row r="59" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="185" t="s">
+      <c r="B59" s="186" t="s">
         <v>1008</v>
       </c>
-      <c r="C59" s="185"/>
-      <c r="D59" s="185"/>
-      <c r="E59" s="185"/>
-      <c r="F59" s="185"/>
-      <c r="G59" s="185"/>
+      <c r="C59" s="186"/>
+      <c r="D59" s="186"/>
+      <c r="E59" s="186"/>
+      <c r="F59" s="186"/>
+      <c r="G59" s="186"/>
     </row>
     <row r="60" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="185" t="s">
+      <c r="B60" s="186" t="s">
         <v>1009</v>
       </c>
-      <c r="C60" s="185"/>
-      <c r="D60" s="185"/>
-      <c r="E60" s="185"/>
-      <c r="F60" s="185"/>
-      <c r="G60" s="185"/>
+      <c r="C60" s="186"/>
+      <c r="D60" s="186"/>
+      <c r="E60" s="186"/>
+      <c r="F60" s="186"/>
+      <c r="G60" s="186"/>
     </row>
     <row r="61" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="185" t="s">
+      <c r="B61" s="186" t="s">
         <v>1010</v>
       </c>
-      <c r="C61" s="185"/>
-      <c r="D61" s="185"/>
-      <c r="E61" s="185"/>
-      <c r="F61" s="185"/>
-      <c r="G61" s="185"/>
+      <c r="C61" s="186"/>
+      <c r="D61" s="186"/>
+      <c r="E61" s="186"/>
+      <c r="F61" s="186"/>
+      <c r="G61" s="186"/>
     </row>
     <row r="62" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -45224,11 +45224,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B38:I38"/>
     <mergeCell ref="B60:G60"/>
     <mergeCell ref="B61:G61"/>
     <mergeCell ref="B55:I55"/>
@@ -45236,6 +45231,11 @@
     <mergeCell ref="B57:G57"/>
     <mergeCell ref="B58:G58"/>
     <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B38:I38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -45285,15 +45285,15 @@
     </row>
     <row r="4" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>1033</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
     </row>
     <row r="6" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -45554,15 +45554,15 @@
     </row>
     <row r="16" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="182" t="s">
+      <c r="B17" s="185" t="s">
         <v>1051</v>
       </c>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="182"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="182"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="185"/>
+      <c r="F17" s="185"/>
+      <c r="G17" s="185"/>
+      <c r="H17" s="185"/>
     </row>
     <row r="18" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
@@ -45797,15 +45797,15 @@
     </row>
     <row r="27" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="182" t="s">
+      <c r="B28" s="185" t="s">
         <v>1071</v>
       </c>
-      <c r="C28" s="182"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="182"/>
+      <c r="C28" s="185"/>
+      <c r="D28" s="185"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
     </row>
     <row r="29" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="60" t="s">
@@ -46014,15 +46014,15 @@
     </row>
     <row r="37" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="182" t="s">
+      <c r="B38" s="185" t="s">
         <v>1087</v>
       </c>
-      <c r="C38" s="182"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="182"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="182"/>
+      <c r="C38" s="185"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
+      <c r="F38" s="185"/>
+      <c r="G38" s="185"/>
+      <c r="H38" s="185"/>
     </row>
     <row r="39" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
@@ -46391,15 +46391,15 @@
     </row>
     <row r="56" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="182" t="s">
+      <c r="B57" s="185" t="s">
         <v>1092</v>
       </c>
-      <c r="C57" s="182"/>
-      <c r="D57" s="182"/>
-      <c r="E57" s="182"/>
-      <c r="F57" s="182"/>
-      <c r="G57" s="182"/>
-      <c r="H57" s="182"/>
+      <c r="C57" s="185"/>
+      <c r="D57" s="185"/>
+      <c r="E57" s="185"/>
+      <c r="F57" s="185"/>
+      <c r="G57" s="185"/>
+      <c r="H57" s="185"/>
     </row>
     <row r="58" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="60" t="s">
@@ -46608,15 +46608,15 @@
     </row>
     <row r="66" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="182" t="s">
+      <c r="B67" s="185" t="s">
         <v>1110</v>
       </c>
-      <c r="C67" s="182"/>
-      <c r="D67" s="182"/>
-      <c r="E67" s="182"/>
-      <c r="F67" s="182"/>
-      <c r="G67" s="182"/>
-      <c r="H67" s="182"/>
+      <c r="C67" s="185"/>
+      <c r="D67" s="185"/>
+      <c r="E67" s="185"/>
+      <c r="F67" s="185"/>
+      <c r="G67" s="185"/>
+      <c r="H67" s="185"/>
     </row>
     <row r="68" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="60" t="s">
@@ -46799,15 +46799,15 @@
     </row>
     <row r="75" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="182" t="s">
+      <c r="B76" s="185" t="s">
         <v>1125</v>
       </c>
-      <c r="C76" s="182"/>
-      <c r="D76" s="182"/>
-      <c r="E76" s="182"/>
-      <c r="F76" s="182"/>
-      <c r="G76" s="182"/>
-      <c r="H76" s="182"/>
+      <c r="C76" s="185"/>
+      <c r="D76" s="185"/>
+      <c r="E76" s="185"/>
+      <c r="F76" s="185"/>
+      <c r="G76" s="185"/>
+      <c r="H76" s="185"/>
     </row>
     <row r="77" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="60" t="s">
@@ -47068,15 +47068,15 @@
     </row>
     <row r="87" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="88" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="182" t="s">
+      <c r="B88" s="185" t="s">
         <v>1152</v>
       </c>
-      <c r="C88" s="182"/>
-      <c r="D88" s="182"/>
-      <c r="E88" s="182"/>
-      <c r="F88" s="182"/>
-      <c r="G88" s="182"/>
-      <c r="H88" s="182"/>
+      <c r="C88" s="185"/>
+      <c r="D88" s="185"/>
+      <c r="E88" s="185"/>
+      <c r="F88" s="185"/>
+      <c r="G88" s="185"/>
+      <c r="H88" s="185"/>
     </row>
     <row r="89" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="60" t="s">
@@ -49690,16 +49690,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B88:H88"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B88:H88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -49750,16 +49750,16 @@
     </row>
     <row r="4" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>1388</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
     </row>
     <row r="6" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -50033,16 +50033,16 @@
     <row r="16" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="182" t="s">
+      <c r="B18" s="185" t="s">
         <v>1405</v>
       </c>
-      <c r="C18" s="182"/>
-      <c r="D18" s="182"/>
-      <c r="E18" s="182"/>
-      <c r="F18" s="182"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="182"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="185"/>
+      <c r="F18" s="185"/>
+      <c r="G18" s="185"/>
+      <c r="H18" s="185"/>
+      <c r="I18" s="185"/>
     </row>
     <row r="19" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="60" t="s">
@@ -50316,16 +50316,16 @@
     <row r="29" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="182" t="s">
+      <c r="B31" s="185" t="s">
         <v>1406</v>
       </c>
-      <c r="C31" s="182"/>
-      <c r="D31" s="182"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="182"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="182"/>
-      <c r="I31" s="182"/>
+      <c r="C31" s="185"/>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
     </row>
     <row r="32" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
@@ -50599,16 +50599,16 @@
     <row r="42" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="182" t="s">
+      <c r="B44" s="185" t="s">
         <v>1407</v>
       </c>
-      <c r="C44" s="182"/>
-      <c r="D44" s="182"/>
-      <c r="E44" s="182"/>
-      <c r="F44" s="182"/>
-      <c r="G44" s="182"/>
-      <c r="H44" s="182"/>
-      <c r="I44" s="182"/>
+      <c r="C44" s="185"/>
+      <c r="D44" s="185"/>
+      <c r="E44" s="185"/>
+      <c r="F44" s="185"/>
+      <c r="G44" s="185"/>
+      <c r="H44" s="185"/>
+      <c r="I44" s="185"/>
     </row>
     <row r="45" spans="2:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="60" t="s">
@@ -50806,15 +50806,15 @@
     </row>
     <row r="4" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>1418</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
     </row>
     <row r="6" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -51127,15 +51127,15 @@
     </row>
     <row r="18" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="182" t="s">
+      <c r="B19" s="185" t="s">
         <v>1451</v>
       </c>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="182"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="185"/>
+      <c r="G19" s="185"/>
+      <c r="H19" s="185"/>
     </row>
     <row r="20" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="60" t="s">
@@ -51393,15 +51393,15 @@
     </row>
     <row r="30" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="182" t="s">
+      <c r="B31" s="185" t="s">
         <v>1474</v>
       </c>
-      <c r="C31" s="182"/>
-      <c r="D31" s="182"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="182"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="182"/>
+      <c r="C31" s="185"/>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
     </row>
     <row r="32" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
@@ -51691,15 +51691,15 @@
     </row>
     <row r="44" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="182" t="s">
+      <c r="B45" s="185" t="s">
         <v>1505</v>
       </c>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="182"/>
-      <c r="F45" s="182"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="182"/>
+      <c r="C45" s="185"/>
+      <c r="D45" s="185"/>
+      <c r="E45" s="185"/>
+      <c r="F45" s="185"/>
+      <c r="G45" s="185"/>
+      <c r="H45" s="185"/>
     </row>
     <row r="46" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="60" t="s">
@@ -51886,15 +51886,15 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="182" t="s">
+      <c r="B55" s="185" t="s">
         <v>1537</v>
       </c>
-      <c r="C55" s="182"/>
-      <c r="D55" s="182"/>
-      <c r="E55" s="182"/>
-      <c r="F55" s="182"/>
-      <c r="G55" s="182"/>
-      <c r="H55" s="182"/>
+      <c r="C55" s="185"/>
+      <c r="D55" s="185"/>
+      <c r="E55" s="185"/>
+      <c r="F55" s="185"/>
+      <c r="G55" s="185"/>
+      <c r="H55" s="185"/>
     </row>
     <row r="56" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="60" t="s">
@@ -52043,15 +52043,15 @@
     </row>
     <row r="4" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>1553</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
     </row>
     <row r="6" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="60" t="s">
@@ -52255,15 +52255,15 @@
     </row>
     <row r="16" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="182" t="s">
+      <c r="B17" s="185" t="s">
         <v>1610</v>
       </c>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="182"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="182"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="185"/>
+      <c r="F17" s="185"/>
+      <c r="G17" s="185"/>
+      <c r="H17" s="185"/>
     </row>
     <row r="18" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
@@ -52454,15 +52454,15 @@
     </row>
     <row r="29" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="182" t="s">
+      <c r="B30" s="185" t="s">
         <v>1662</v>
       </c>
-      <c r="C30" s="182"/>
-      <c r="D30" s="182"/>
-      <c r="E30" s="182"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="182"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="185"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
     </row>
     <row r="31" spans="2:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="60" t="s">
